--- a/db/A7XLK-1111-HouseApp1.xlsx
+++ b/db/A7XLK-1111-HouseApp1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangtaizhong/Documents/92_WebSite/A7Xinlinkou/db/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBE7639B-15F6-F94F-90DE-CB692D12E5FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B7DD66A-2A02-F44E-9506-40AD0D459519}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3520" yWindow="580" windowWidth="27320" windowHeight="16380" xr2:uid="{33D194D6-A429-7949-A97B-0894189945E2}"/>
+    <workbookView xWindow="640" yWindow="580" windowWidth="27320" windowHeight="16380" xr2:uid="{33D194D6-A429-7949-A97B-0894189945E2}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2127" uniqueCount="1122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2165" uniqueCount="1143">
   <si>
     <t>No</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -3714,10 +3714,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>37.57%%</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>地上28層，地下5層</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -4340,6 +4336,93 @@
   </si>
   <si>
     <t>fig/AiCity-939-豐邑氧森.jpg</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>君邑羅浮</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>fig/AiCity-939-君邑羅浮.jpg</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>玄泰T1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>fig/AiCity-939-玄泰T1.webp</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://newhouse.591.com.tw/home/housing/detail?hid=128089</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>378/595</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>34~38 萬/坪</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>160~230萬</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026年第一季度</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026Q1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>三房(36~42坪) 、 3+1房(45~49坪)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">桃園市龜山區善捷段62地號 </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>桃園市龜山區文化一路、樂善二路</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> 群泰開發有限公司</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>群泰開發</t>
+  </si>
+  <si>
+    <t>益盛營造股份有限公司</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>天湛廣告</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1幢，4棟，264戶住家，7戶店面，294戶事務所，30戶一般</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>地上25層，地下5層</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>平面式596個</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1848.19坪</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>110桃市都建執照字第00311-01號</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -4801,7 +4884,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F05EA98-B5B7-7547-BED4-A618D76058F2}">
-  <dimension ref="A1:BQ54"/>
+  <dimension ref="A1:BQ56"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="8.83203125" style="10"/>
@@ -5075,7 +5158,7 @@
         <v>70</v>
       </c>
       <c r="D2" s="12" t="str">
-        <f>CONCATENATE(A2," ",C2)</f>
+        <f t="shared" ref="D2:D56" si="0">CONCATENATE(A2," ",C2)</f>
         <v>101 和發大境</v>
       </c>
       <c r="E2" s="9" t="s">
@@ -5106,11 +5189,11 @@
         <v>29</v>
       </c>
       <c r="N2" s="15">
-        <f>(L2+M2)/2</f>
+        <f t="shared" ref="N2:N8" si="1">(L2+M2)/2</f>
         <v>28.5</v>
       </c>
       <c r="O2" s="15">
-        <f>M2-N2</f>
+        <f t="shared" ref="O2:O8" si="2">M2-N2</f>
         <v>0.5</v>
       </c>
       <c r="P2" s="9" t="s">
@@ -5123,11 +5206,11 @@
         <v>36</v>
       </c>
       <c r="S2" s="15">
-        <f>R2-Q2</f>
+        <f t="shared" ref="S2:S8" si="3">R2-Q2</f>
         <v>2</v>
       </c>
       <c r="T2" s="15">
-        <f>(Q2+R2)/2</f>
+        <f t="shared" ref="T2:T56" si="4">(Q2+R2)/2</f>
         <v>35</v>
       </c>
       <c r="Y2" s="9" t="s">
@@ -5277,7 +5360,7 @@
         <v>106</v>
       </c>
       <c r="D3" s="12" t="str">
-        <f>CONCATENATE(A3," ",C3)</f>
+        <f t="shared" si="0"/>
         <v>102 鴻典</v>
       </c>
       <c r="E3" s="12" t="s">
@@ -5308,11 +5391,11 @@
         <v>26</v>
       </c>
       <c r="N3" s="15">
-        <f>(L3+M3)/2</f>
+        <f t="shared" si="1"/>
         <v>26</v>
       </c>
       <c r="O3" s="15">
-        <f>M3-N3</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="P3" s="9" t="s">
@@ -5325,11 +5408,11 @@
         <v>29</v>
       </c>
       <c r="S3" s="15">
-        <f>R3-Q3</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="T3" s="15">
-        <f>(Q3+R3)/2</f>
+        <f t="shared" si="4"/>
         <v>29</v>
       </c>
       <c r="Y3" s="9" t="s">
@@ -5479,7 +5562,7 @@
         <v>135</v>
       </c>
       <c r="D4" s="12" t="str">
-        <f>CONCATENATE(A4," ",C4)</f>
+        <f t="shared" si="0"/>
         <v>103 樂捷市</v>
       </c>
       <c r="E4" s="9" t="s">
@@ -5510,11 +5593,11 @@
         <v>26</v>
       </c>
       <c r="N4" s="15">
-        <f>(L4+M4)/2</f>
+        <f t="shared" si="1"/>
         <v>26</v>
       </c>
       <c r="O4" s="15">
-        <f>M4-N4</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="P4" s="9" t="s">
@@ -5527,11 +5610,11 @@
         <v>26</v>
       </c>
       <c r="S4" s="15">
-        <f>R4-Q4</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="T4" s="15">
-        <f>(Q4+R4)/2</f>
+        <f t="shared" si="4"/>
         <v>26</v>
       </c>
       <c r="U4" s="15" t="s">
@@ -5690,7 +5773,7 @@
         <v>159</v>
       </c>
       <c r="D5" s="12" t="str">
-        <f>CONCATENATE(A5," ",C5)</f>
+        <f t="shared" si="0"/>
         <v>104 奇幻莊園</v>
       </c>
       <c r="E5" s="12" t="s">
@@ -5719,11 +5802,11 @@
         <v>25.5</v>
       </c>
       <c r="N5" s="15">
-        <f>(L5+M5)/2</f>
+        <f t="shared" si="1"/>
         <v>25</v>
       </c>
       <c r="O5" s="15">
-        <f>M5-N5</f>
+        <f t="shared" si="2"/>
         <v>0.5</v>
       </c>
       <c r="P5" s="9" t="s">
@@ -5736,11 +5819,11 @@
         <v>25.5</v>
       </c>
       <c r="S5" s="15">
-        <f>R5-Q5</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="T5" s="15">
-        <f>(Q5+R5)/2</f>
+        <f t="shared" si="4"/>
         <v>25</v>
       </c>
       <c r="U5" s="15" t="s">
@@ -5899,7 +5982,7 @@
         <v>183</v>
       </c>
       <c r="D6" s="12" t="str">
-        <f>CONCATENATE(A6," ",C6)</f>
+        <f t="shared" si="0"/>
         <v>105 樂田田</v>
       </c>
       <c r="E6" s="9" t="s">
@@ -5930,11 +6013,11 @@
         <v>26</v>
       </c>
       <c r="N6" s="15">
-        <f>(L6+M6)/2</f>
+        <f t="shared" si="1"/>
         <v>25.5</v>
       </c>
       <c r="O6" s="15">
-        <f>M6-N6</f>
+        <f t="shared" si="2"/>
         <v>0.5</v>
       </c>
       <c r="P6" s="9" t="s">
@@ -5947,11 +6030,11 @@
         <v>26</v>
       </c>
       <c r="S6" s="15">
-        <f>R6-Q6</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="T6" s="15">
-        <f>(Q6+R6)/2</f>
+        <f t="shared" si="4"/>
         <v>26</v>
       </c>
       <c r="U6" s="15" t="s">
@@ -6104,7 +6187,7 @@
         <v>206</v>
       </c>
       <c r="D7" s="12" t="str">
-        <f>CONCATENATE(A7," ",C7)</f>
+        <f t="shared" si="0"/>
         <v>106 玉子園</v>
       </c>
       <c r="E7" s="12" t="s">
@@ -6135,11 +6218,11 @@
         <v>28</v>
       </c>
       <c r="N7" s="15">
-        <f>(L7+M7)/2</f>
+        <f t="shared" si="1"/>
         <v>27</v>
       </c>
       <c r="O7" s="15">
-        <f>M7-N7</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="P7" s="9" t="s">
@@ -6152,11 +6235,11 @@
         <v>28</v>
       </c>
       <c r="S7" s="15">
-        <f>R7-Q7</f>
+        <f t="shared" si="3"/>
         <v>2</v>
       </c>
       <c r="T7" s="15">
-        <f>(Q7+R7)/2</f>
+        <f t="shared" si="4"/>
         <v>27</v>
       </c>
       <c r="U7" s="15" t="s">
@@ -6309,7 +6392,7 @@
         <v>228</v>
       </c>
       <c r="D8" s="12" t="str">
-        <f>CONCATENATE(A8," ",C8)</f>
+        <f t="shared" si="0"/>
         <v>107 台北國際村</v>
       </c>
       <c r="E8" s="12" t="s">
@@ -6340,11 +6423,11 @@
         <v>26</v>
       </c>
       <c r="N8" s="15">
-        <f>(L8+M8)/2</f>
+        <f t="shared" si="1"/>
         <v>25.5</v>
       </c>
       <c r="O8" s="15">
-        <f>M8-N8</f>
+        <f t="shared" si="2"/>
         <v>0.5</v>
       </c>
       <c r="P8" s="9" t="s">
@@ -6357,11 +6440,11 @@
         <v>29</v>
       </c>
       <c r="S8" s="15">
-        <f>R8-Q8</f>
+        <f t="shared" si="3"/>
         <v>2</v>
       </c>
       <c r="T8" s="15">
-        <f>(Q8+R8)/2</f>
+        <f t="shared" si="4"/>
         <v>28</v>
       </c>
       <c r="V8" s="9" t="s">
@@ -6517,11 +6600,11 @@
         <v>250</v>
       </c>
       <c r="D9" s="12" t="str">
-        <f>CONCATENATE(A9," ",C9)</f>
+        <f t="shared" si="0"/>
         <v>108 豐邑氧森</v>
       </c>
       <c r="E9" s="12" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
       <c r="F9" s="20" t="s">
         <v>251</v>
@@ -6548,7 +6631,7 @@
         <v>41</v>
       </c>
       <c r="T9" s="15">
-        <f>(Q9+R9)/2</f>
+        <f t="shared" si="4"/>
         <v>41</v>
       </c>
       <c r="Y9" s="9" t="s">
@@ -6683,7 +6766,7 @@
         <v>277</v>
       </c>
       <c r="D10" s="12" t="str">
-        <f>CONCATENATE(A10," ",C10)</f>
+        <f t="shared" si="0"/>
         <v>201 富宇上城</v>
       </c>
       <c r="E10" s="12" t="s">
@@ -6706,11 +6789,11 @@
         <v>35</v>
       </c>
       <c r="N10" s="15">
-        <f>(L10+M10)/2</f>
+        <f t="shared" ref="N10:N43" si="5">(L10+M10)/2</f>
         <v>32.5</v>
       </c>
       <c r="O10" s="15">
-        <f>M10-N10</f>
+        <f t="shared" ref="O10:O43" si="6">M10-N10</f>
         <v>2.5</v>
       </c>
       <c r="P10" s="9" t="s">
@@ -6723,11 +6806,11 @@
         <v>49</v>
       </c>
       <c r="S10" s="15">
-        <f>R10-Q10</f>
+        <f t="shared" ref="S10:S43" si="7">R10-Q10</f>
         <v>5</v>
       </c>
       <c r="T10" s="15">
-        <f>(Q10+R10)/2</f>
+        <f t="shared" si="4"/>
         <v>46.5</v>
       </c>
       <c r="Y10" s="9" t="s">
@@ -6877,7 +6960,7 @@
         <v>304</v>
       </c>
       <c r="D11" s="12" t="str">
-        <f>CONCATENATE(A11," ",C11)</f>
+        <f t="shared" si="0"/>
         <v>202 禾悅花園</v>
       </c>
       <c r="E11" s="12" t="s">
@@ -6908,11 +6991,11 @@
         <v>29</v>
       </c>
       <c r="N11" s="15">
-        <f>(L11+M11)/2</f>
+        <f t="shared" si="5"/>
         <v>28.5</v>
       </c>
       <c r="O11" s="15">
-        <f>M11-N11</f>
+        <f t="shared" si="6"/>
         <v>0.5</v>
       </c>
       <c r="P11" s="9" t="s">
@@ -6925,11 +7008,11 @@
         <v>37</v>
       </c>
       <c r="S11" s="15">
-        <f>R11-Q11</f>
+        <f t="shared" si="7"/>
         <v>2</v>
       </c>
       <c r="T11" s="15">
-        <f>(Q11+R11)/2</f>
+        <f t="shared" si="4"/>
         <v>36</v>
       </c>
       <c r="Y11" s="9" t="s">
@@ -7079,7 +7162,7 @@
         <v>329</v>
       </c>
       <c r="D12" s="12" t="str">
-        <f>CONCATENATE(A12," ",C12)</f>
+        <f t="shared" si="0"/>
         <v>203 耀台北</v>
       </c>
       <c r="E12" s="12" t="s">
@@ -7110,11 +7193,11 @@
         <v>28</v>
       </c>
       <c r="N12" s="15">
-        <f>(L12+M12)/2</f>
+        <f t="shared" si="5"/>
         <v>27</v>
       </c>
       <c r="O12" s="15">
-        <f>M12-N12</f>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="P12" s="9" t="s">
@@ -7127,11 +7210,11 @@
         <v>28</v>
       </c>
       <c r="S12" s="15">
-        <f>R12-Q12</f>
+        <f t="shared" si="7"/>
         <v>2</v>
       </c>
       <c r="T12" s="15">
-        <f>(Q12+R12)/2</f>
+        <f t="shared" si="4"/>
         <v>27</v>
       </c>
       <c r="U12" s="15" t="s">
@@ -7284,7 +7367,7 @@
         <v>346</v>
       </c>
       <c r="D13" s="12" t="str">
-        <f>CONCATENATE(A13," ",C13)</f>
+        <f t="shared" si="0"/>
         <v>204 皇普MVP</v>
       </c>
       <c r="E13" s="12" t="s">
@@ -7315,11 +7398,11 @@
         <v>26</v>
       </c>
       <c r="N13" s="15">
-        <f>(L13+M13)/2</f>
+        <f t="shared" si="5"/>
         <v>25.5</v>
       </c>
       <c r="O13" s="15">
-        <f>M13-N13</f>
+        <f t="shared" si="6"/>
         <v>0.5</v>
       </c>
       <c r="P13" s="9" t="s">
@@ -7332,11 +7415,11 @@
         <v>28</v>
       </c>
       <c r="S13" s="15">
-        <f>R13-Q13</f>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="T13" s="15">
-        <f>(Q13+R13)/2</f>
+        <f t="shared" si="4"/>
         <v>27.5</v>
       </c>
       <c r="V13" s="9" t="s">
@@ -7483,7 +7566,7 @@
         <v>370</v>
       </c>
       <c r="D14" s="12" t="str">
-        <f>CONCATENATE(A14," ",C14)</f>
+        <f t="shared" si="0"/>
         <v>205 富宇敦峰</v>
       </c>
       <c r="E14" s="12" t="s">
@@ -7514,11 +7597,11 @@
         <v>32</v>
       </c>
       <c r="N14" s="15">
-        <f>(L14+M14)/2</f>
+        <f t="shared" si="5"/>
         <v>31</v>
       </c>
       <c r="O14" s="15">
-        <f>M14-N14</f>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="P14" s="9" t="s">
@@ -7531,11 +7614,11 @@
         <v>42</v>
       </c>
       <c r="S14" s="15">
-        <f>R14-Q14</f>
+        <f t="shared" si="7"/>
         <v>4</v>
       </c>
       <c r="T14" s="15">
-        <f>(Q14+R14)/2</f>
+        <f t="shared" si="4"/>
         <v>40</v>
       </c>
       <c r="V14" s="9" t="s">
@@ -7691,7 +7774,7 @@
         <v>391</v>
       </c>
       <c r="D15" s="12" t="str">
-        <f>CONCATENATE(A15," ",C15)</f>
+        <f t="shared" si="0"/>
         <v>206 玄泰V1</v>
       </c>
       <c r="E15" s="23" t="s">
@@ -7720,11 +7803,11 @@
         <v>29</v>
       </c>
       <c r="N15" s="15">
-        <f>(L15+M15)/2</f>
+        <f t="shared" si="5"/>
         <v>28</v>
       </c>
       <c r="O15" s="15">
-        <f>M15-N15</f>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="P15" s="9" t="s">
@@ -7737,11 +7820,11 @@
         <v>29</v>
       </c>
       <c r="S15" s="15">
-        <f>R15-Q15</f>
+        <f t="shared" si="7"/>
         <v>2</v>
       </c>
       <c r="T15" s="15">
-        <f>(Q15+R15)/2</f>
+        <f t="shared" si="4"/>
         <v>28</v>
       </c>
       <c r="U15" s="15" t="s">
@@ -7894,7 +7977,7 @@
         <v>417</v>
       </c>
       <c r="D16" s="12" t="str">
-        <f>CONCATENATE(A16," ",C16)</f>
+        <f t="shared" si="0"/>
         <v>207 和耀恆美</v>
       </c>
       <c r="E16" s="23" t="s">
@@ -7925,11 +8008,11 @@
         <v>33</v>
       </c>
       <c r="N16" s="15">
-        <f>(L16+M16)/2</f>
+        <f t="shared" si="5"/>
         <v>30.5</v>
       </c>
       <c r="O16" s="15">
-        <f>M16-N16</f>
+        <f t="shared" si="6"/>
         <v>2.5</v>
       </c>
       <c r="P16" s="9" t="s">
@@ -7942,11 +8025,11 @@
         <v>40</v>
       </c>
       <c r="S16" s="15">
-        <f>R16-Q16</f>
+        <f t="shared" si="7"/>
         <v>5</v>
       </c>
       <c r="T16" s="15">
-        <f>(Q16+R16)/2</f>
+        <f t="shared" si="4"/>
         <v>37.5</v>
       </c>
       <c r="Y16" s="9" t="s">
@@ -8087,7 +8170,7 @@
         <v>440</v>
       </c>
       <c r="D17" s="12" t="str">
-        <f>CONCATENATE(A17," ",C17)</f>
+        <f t="shared" si="0"/>
         <v>301 允將大作</v>
       </c>
       <c r="E17" s="12" t="s">
@@ -8110,11 +8193,11 @@
         <v>38</v>
       </c>
       <c r="N17" s="15">
-        <f>(L17+M17)/2</f>
+        <f t="shared" si="5"/>
         <v>36.5</v>
       </c>
       <c r="O17" s="15">
-        <f>M17-N17</f>
+        <f t="shared" si="6"/>
         <v>1.5</v>
       </c>
       <c r="P17" s="9" t="s">
@@ -8127,11 +8210,11 @@
         <v>43</v>
       </c>
       <c r="S17" s="15">
-        <f>R17-Q17</f>
+        <f t="shared" si="7"/>
         <v>5</v>
       </c>
       <c r="T17" s="15">
-        <f>(Q17+R17)/2</f>
+        <f t="shared" si="4"/>
         <v>40.5</v>
       </c>
       <c r="Y17" s="9" t="s">
@@ -8281,7 +8364,7 @@
         <v>463</v>
       </c>
       <c r="D18" s="12" t="str">
-        <f>CONCATENATE(A18," ",C18)</f>
+        <f t="shared" si="0"/>
         <v>302 欣時代</v>
       </c>
       <c r="E18" s="12" t="s">
@@ -8310,11 +8393,11 @@
         <v>29</v>
       </c>
       <c r="N18" s="15">
-        <f>(L18+M18)/2</f>
+        <f t="shared" si="5"/>
         <v>28</v>
       </c>
       <c r="O18" s="15">
-        <f>M18-N18</f>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="P18" s="9" t="s">
@@ -8327,11 +8410,11 @@
         <v>29</v>
       </c>
       <c r="S18" s="15">
-        <f>R18-Q18</f>
+        <f t="shared" si="7"/>
         <v>2</v>
       </c>
       <c r="T18" s="15">
-        <f>(Q18+R18)/2</f>
+        <f t="shared" si="4"/>
         <v>28</v>
       </c>
       <c r="U18" s="15" t="s">
@@ -8484,7 +8567,7 @@
         <v>485</v>
       </c>
       <c r="D19" s="12" t="str">
-        <f>CONCATENATE(A19," ",C19)</f>
+        <f t="shared" si="0"/>
         <v>303 新潤翡麗</v>
       </c>
       <c r="E19" s="12" t="s">
@@ -8515,11 +8598,11 @@
         <v>28</v>
       </c>
       <c r="N19" s="15">
-        <f>(L19+M19)/2</f>
+        <f t="shared" si="5"/>
         <v>27</v>
       </c>
       <c r="O19" s="15">
-        <f>M19-N19</f>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="P19" s="9" t="s">
@@ -8532,11 +8615,11 @@
         <v>36</v>
       </c>
       <c r="S19" s="15">
-        <f>R19-Q19</f>
+        <f t="shared" si="7"/>
         <v>3</v>
       </c>
       <c r="T19" s="15">
-        <f>(Q19+R19)/2</f>
+        <f t="shared" si="4"/>
         <v>34.5</v>
       </c>
       <c r="Y19" s="9" t="s">
@@ -8686,7 +8769,7 @@
         <v>507</v>
       </c>
       <c r="D20" s="12" t="str">
-        <f>CONCATENATE(A20," ",C20)</f>
+        <f t="shared" si="0"/>
         <v>304 新潤鉑麗</v>
       </c>
       <c r="E20" s="12" t="s">
@@ -8717,11 +8800,11 @@
         <v>29</v>
       </c>
       <c r="N20" s="15">
-        <f>(L20+M20)/2</f>
+        <f t="shared" si="5"/>
         <v>28</v>
       </c>
       <c r="O20" s="15">
-        <f>M20-N20</f>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="P20" s="9" t="s">
@@ -8734,11 +8817,11 @@
         <v>29</v>
       </c>
       <c r="S20" s="15">
-        <f>R20-Q20</f>
+        <f t="shared" si="7"/>
         <v>2</v>
       </c>
       <c r="T20" s="15">
-        <f>(Q20+R20)/2</f>
+        <f t="shared" si="4"/>
         <v>28</v>
       </c>
       <c r="U20" s="15" t="s">
@@ -8897,7 +8980,7 @@
         <v>528</v>
       </c>
       <c r="D21" s="12" t="str">
-        <f>CONCATENATE(A21," ",C21)</f>
+        <f t="shared" si="0"/>
         <v>305 根津苑</v>
       </c>
       <c r="E21" s="12" t="s">
@@ -8928,11 +9011,11 @@
         <v>26</v>
       </c>
       <c r="N21" s="15">
-        <f>(L21+M21)/2</f>
+        <f t="shared" si="5"/>
         <v>25</v>
       </c>
       <c r="O21" s="15">
-        <f>M21-N21</f>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="P21" s="9" t="s">
@@ -8945,11 +9028,11 @@
         <v>28</v>
       </c>
       <c r="S21" s="15">
-        <f>R21-Q21</f>
+        <f t="shared" si="7"/>
         <v>2</v>
       </c>
       <c r="T21" s="15">
-        <f>(Q21+R21)/2</f>
+        <f t="shared" si="4"/>
         <v>27</v>
       </c>
       <c r="V21" s="9" t="s">
@@ -9105,7 +9188,7 @@
         <v>545</v>
       </c>
       <c r="D22" s="12" t="str">
-        <f>CONCATENATE(A22," ",C22)</f>
+        <f t="shared" si="0"/>
         <v>306 華悅城</v>
       </c>
       <c r="E22" s="12" t="s">
@@ -9134,11 +9217,11 @@
         <v>30</v>
       </c>
       <c r="N22" s="15">
-        <f>(L22+M22)/2</f>
+        <f t="shared" si="5"/>
         <v>28</v>
       </c>
       <c r="O22" s="15">
-        <f>M22-N22</f>
+        <f t="shared" si="6"/>
         <v>2</v>
       </c>
       <c r="P22" s="9" t="s">
@@ -9151,11 +9234,11 @@
         <v>30</v>
       </c>
       <c r="S22" s="15">
-        <f>R22-Q22</f>
+        <f t="shared" si="7"/>
         <v>4</v>
       </c>
       <c r="T22" s="15">
-        <f>(Q22+R22)/2</f>
+        <f t="shared" si="4"/>
         <v>28</v>
       </c>
       <c r="Y22" s="9" t="s">
@@ -9305,7 +9388,7 @@
         <v>565</v>
       </c>
       <c r="D23" s="12" t="str">
-        <f>CONCATENATE(A23," ",C23)</f>
+        <f t="shared" si="0"/>
         <v>307 富宇悅峰</v>
       </c>
       <c r="E23" s="12" t="s">
@@ -9336,11 +9419,11 @@
         <v>32</v>
       </c>
       <c r="N23" s="15">
-        <f>(L23+M23)/2</f>
+        <f t="shared" si="5"/>
         <v>30</v>
       </c>
       <c r="O23" s="15">
-        <f>M23-N23</f>
+        <f t="shared" si="6"/>
         <v>2</v>
       </c>
       <c r="P23" s="9" t="s">
@@ -9353,11 +9436,11 @@
         <v>36</v>
       </c>
       <c r="S23" s="15">
-        <f>R23-Q23</f>
+        <f t="shared" si="7"/>
         <v>2</v>
       </c>
       <c r="T23" s="15">
-        <f>(Q23+R23)/2</f>
+        <f t="shared" si="4"/>
         <v>35</v>
       </c>
       <c r="Y23" s="9" t="s">
@@ -9507,7 +9590,7 @@
         <v>586</v>
       </c>
       <c r="D24" s="12" t="str">
-        <f>CONCATENATE(A24," ",C24)</f>
+        <f t="shared" si="0"/>
         <v>308 合遠新天地</v>
       </c>
       <c r="E24" s="9" t="s">
@@ -9532,11 +9615,11 @@
         <v>26</v>
       </c>
       <c r="N24" s="15">
-        <f>(L24+M24)/2</f>
+        <f t="shared" si="5"/>
         <v>25</v>
       </c>
       <c r="O24" s="15">
-        <f>M24-N24</f>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="P24" s="9" t="s">
@@ -9549,11 +9632,11 @@
         <v>26</v>
       </c>
       <c r="S24" s="15">
-        <f>R24-Q24</f>
+        <f t="shared" si="7"/>
         <v>2</v>
       </c>
       <c r="T24" s="15">
-        <f>(Q24+R24)/2</f>
+        <f t="shared" si="4"/>
         <v>25</v>
       </c>
       <c r="U24" s="15" t="s">
@@ -9706,7 +9789,7 @@
         <v>602</v>
       </c>
       <c r="D25" s="12" t="str">
-        <f>CONCATENATE(A25," ",C25)</f>
+        <f t="shared" si="0"/>
         <v>309 友文化</v>
       </c>
       <c r="E25" s="12" t="s">
@@ -9737,11 +9820,11 @@
         <v>31</v>
       </c>
       <c r="N25" s="15">
-        <f>(L25+M25)/2</f>
+        <f t="shared" si="5"/>
         <v>30.5</v>
       </c>
       <c r="O25" s="15">
-        <f>M25-N25</f>
+        <f t="shared" si="6"/>
         <v>0.5</v>
       </c>
       <c r="P25" s="9" t="s">
@@ -9754,11 +9837,11 @@
         <v>28</v>
       </c>
       <c r="S25" s="15">
-        <f>R25-Q25</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="T25" s="15">
-        <f>(Q25+R25)/2</f>
+        <f t="shared" si="4"/>
         <v>28</v>
       </c>
       <c r="V25" s="9" t="s">
@@ -9914,7 +9997,7 @@
         <v>623</v>
       </c>
       <c r="D26" s="12" t="str">
-        <f>CONCATENATE(A26," ",C26)</f>
+        <f t="shared" si="0"/>
         <v>310 水悅青青</v>
       </c>
       <c r="E26" s="12" t="s">
@@ -9945,11 +10028,11 @@
         <v>31</v>
       </c>
       <c r="N26" s="15">
-        <f>(L26+M26)/2</f>
+        <f t="shared" si="5"/>
         <v>30</v>
       </c>
       <c r="O26" s="15">
-        <f>M26-N26</f>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="P26" s="9" t="s">
@@ -9962,11 +10045,11 @@
         <v>39</v>
       </c>
       <c r="S26" s="15">
-        <f>R26-Q26</f>
+        <f t="shared" si="7"/>
         <v>5</v>
       </c>
       <c r="T26" s="15">
-        <f>(Q26+R26)/2</f>
+        <f t="shared" si="4"/>
         <v>36.5</v>
       </c>
       <c r="Y26" s="9" t="s">
@@ -10113,7 +10196,7 @@
         <v>642</v>
       </c>
       <c r="D27" s="12" t="str">
-        <f>CONCATENATE(A27," ",C27)</f>
+        <f t="shared" si="0"/>
         <v>311 文華天際</v>
       </c>
       <c r="E27" s="12" t="s">
@@ -10144,11 +10227,11 @@
         <v>27</v>
       </c>
       <c r="N27" s="15">
-        <f>(L27+M27)/2</f>
+        <f t="shared" si="5"/>
         <v>27</v>
       </c>
       <c r="O27" s="15">
-        <f>M27-N27</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="P27" s="9" t="s">
@@ -10161,11 +10244,11 @@
         <v>34</v>
       </c>
       <c r="S27" s="15">
-        <f>R27-Q27</f>
+        <f t="shared" si="7"/>
         <v>2</v>
       </c>
       <c r="T27" s="15">
-        <f>(Q27+R27)/2</f>
+        <f t="shared" si="4"/>
         <v>33</v>
       </c>
       <c r="Y27" s="9" t="s">
@@ -10303,283 +10386,111 @@
     </row>
     <row r="28" spans="1:69">
       <c r="A28" s="10">
-        <v>401</v>
+        <v>312</v>
       </c>
       <c r="B28" s="11" t="s">
-        <v>663</v>
+        <v>439</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>664</v>
+        <v>1121</v>
       </c>
       <c r="D28" s="12" t="str">
-        <f>CONCATENATE(A28," ",C28)</f>
-        <v>401 竹城甲子園</v>
+        <f t="shared" si="0"/>
+        <v>312 君邑羅浮</v>
       </c>
       <c r="E28" s="12" t="s">
-        <v>665</v>
-      </c>
-      <c r="F28" s="13" t="s">
-        <v>666</v>
-      </c>
-      <c r="G28" s="14">
-        <v>26.45</v>
-      </c>
-      <c r="H28" s="13" t="s">
-        <v>667</v>
-      </c>
-      <c r="I28" s="14">
-        <v>28.89</v>
-      </c>
-      <c r="J28" s="14">
-        <v>22.46</v>
-      </c>
-      <c r="K28" s="9" t="s">
-        <v>209</v>
-      </c>
-      <c r="L28" s="15">
-        <v>26</v>
-      </c>
-      <c r="M28" s="15">
-        <v>28</v>
-      </c>
-      <c r="N28" s="15">
-        <f>(L28+M28)/2</f>
-        <v>27</v>
-      </c>
-      <c r="O28" s="15">
-        <f>M28-N28</f>
-        <v>1</v>
-      </c>
-      <c r="P28" s="9" t="s">
-        <v>668</v>
-      </c>
-      <c r="Q28" s="15">
-        <v>38</v>
-      </c>
-      <c r="R28" s="15">
-        <v>41</v>
-      </c>
-      <c r="S28" s="15">
-        <f>R28-Q28</f>
-        <v>3</v>
-      </c>
-      <c r="T28" s="15">
-        <f>(Q28+R28)/2</f>
-        <v>39.5</v>
-      </c>
-      <c r="V28" s="9" t="s">
-        <v>669</v>
-      </c>
-      <c r="W28" s="20" t="s">
-        <v>670</v>
-      </c>
-      <c r="AB28" s="9" t="s">
-        <v>112</v>
-      </c>
-      <c r="AC28" s="9" t="s">
-        <v>77</v>
-      </c>
-      <c r="AD28" s="9" t="s">
-        <v>671</v>
-      </c>
-      <c r="AE28" s="10">
-        <v>2021</v>
-      </c>
-      <c r="AF28" s="9" t="s">
-        <v>212</v>
-      </c>
-      <c r="AG28" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="AH28" s="9" t="s">
-        <v>672</v>
-      </c>
+        <v>1122</v>
+      </c>
+      <c r="F28" s="20"/>
+      <c r="G28" s="21"/>
+      <c r="H28" s="22"/>
+      <c r="I28" s="21"/>
+      <c r="J28" s="21"/>
+      <c r="P28" s="9"/>
       <c r="AI28" s="9" t="s">
-        <v>116</v>
+        <v>258</v>
       </c>
       <c r="AJ28" s="9" t="s">
         <v>83</v>
       </c>
-      <c r="AK28" s="9" t="s">
-        <v>117</v>
-      </c>
-      <c r="AL28" s="9" t="s">
-        <v>471</v>
-      </c>
-      <c r="AM28" s="9" t="s">
-        <v>673</v>
-      </c>
-      <c r="AN28" s="9" t="s">
-        <v>674</v>
-      </c>
-      <c r="AO28" s="9" t="s">
-        <v>675</v>
-      </c>
-      <c r="AP28" s="9" t="s">
-        <v>675</v>
-      </c>
-      <c r="AQ28" s="9" t="s">
-        <v>676</v>
-      </c>
-      <c r="AR28" s="9" t="s">
-        <v>677</v>
-      </c>
-      <c r="AS28" s="9" t="s">
-        <v>678</v>
-      </c>
-      <c r="AT28" s="9" t="s">
-        <v>679</v>
-      </c>
-      <c r="AU28" s="18">
-        <v>0.32500000000000001</v>
-      </c>
-      <c r="AV28" s="9" t="s">
-        <v>680</v>
-      </c>
-      <c r="AW28" s="9">
-        <v>1144</v>
-      </c>
-      <c r="AX28" s="9">
-        <v>30</v>
-      </c>
-      <c r="AY28" s="9" t="s">
-        <v>681</v>
-      </c>
-      <c r="AZ28" s="18">
-        <v>0.50209999999999999</v>
-      </c>
-      <c r="BA28" s="9" t="s">
-        <v>296</v>
-      </c>
-      <c r="BB28" s="9">
-        <v>24</v>
-      </c>
-      <c r="BC28" s="9" t="s">
-        <v>682</v>
-      </c>
-      <c r="BD28" s="9" t="s">
-        <v>96</v>
-      </c>
-      <c r="BE28" s="11" t="s">
-        <v>683</v>
-      </c>
-      <c r="BF28" s="19">
-        <v>0.88</v>
-      </c>
-      <c r="BG28" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="BH28" s="9" t="s">
-        <v>684</v>
-      </c>
-      <c r="BI28" s="9">
-        <v>4352.46</v>
-      </c>
-      <c r="BJ28" s="9" t="s">
-        <v>100</v>
-      </c>
-      <c r="BK28" s="9" t="s">
-        <v>414</v>
-      </c>
-      <c r="BL28" s="9" t="s">
-        <v>102</v>
-      </c>
-      <c r="BM28" s="9" t="s">
-        <v>102</v>
-      </c>
-      <c r="BN28" s="9" t="s">
-        <v>685</v>
-      </c>
-      <c r="BO28" s="9" t="s">
-        <v>601</v>
-      </c>
-      <c r="BP28" s="9" t="s">
-        <v>102</v>
-      </c>
+      <c r="AT28" s="17"/>
+      <c r="AY28" s="18"/>
+      <c r="BI28" s="9"/>
       <c r="BQ28" s="9" t="s">
         <v>134</v>
       </c>
     </row>
     <row r="29" spans="1:69">
       <c r="A29" s="10">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="B29" s="11" t="s">
         <v>663</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>686</v>
+        <v>664</v>
       </c>
       <c r="D29" s="12" t="str">
-        <f>CONCATENATE(A29," ",C29)</f>
-        <v>402 金捷市</v>
+        <f t="shared" si="0"/>
+        <v>401 竹城甲子園</v>
       </c>
       <c r="E29" s="12" t="s">
-        <v>687</v>
+        <v>665</v>
       </c>
       <c r="F29" s="13" t="s">
-        <v>688</v>
+        <v>666</v>
       </c>
       <c r="G29" s="14">
-        <v>26.46</v>
-      </c>
-      <c r="H29" s="13">
-        <v>24.18</v>
+        <v>26.45</v>
+      </c>
+      <c r="H29" s="13" t="s">
+        <v>667</v>
       </c>
       <c r="I29" s="14">
-        <v>29.57</v>
+        <v>28.89</v>
       </c>
       <c r="J29" s="14">
-        <v>21.5</v>
+        <v>22.46</v>
       </c>
       <c r="K29" s="9" t="s">
-        <v>689</v>
+        <v>209</v>
       </c>
       <c r="L29" s="15">
-        <v>30.5</v>
+        <v>26</v>
       </c>
       <c r="M29" s="15">
-        <v>30.5</v>
+        <v>28</v>
       </c>
       <c r="N29" s="15">
-        <f>(L29+M29)/2</f>
-        <v>30.5</v>
+        <f t="shared" si="5"/>
+        <v>27</v>
       </c>
       <c r="O29" s="15">
-        <f>M29-N29</f>
-        <v>0</v>
+        <f t="shared" si="6"/>
+        <v>1</v>
       </c>
       <c r="P29" s="9" t="s">
-        <v>689</v>
+        <v>668</v>
       </c>
       <c r="Q29" s="15">
-        <v>30.5</v>
+        <v>38</v>
       </c>
       <c r="R29" s="15">
-        <v>30.5</v>
+        <v>41</v>
       </c>
       <c r="S29" s="15">
-        <f>R29-Q29</f>
-        <v>0</v>
+        <f t="shared" si="7"/>
+        <v>3</v>
       </c>
       <c r="T29" s="15">
-        <f>(Q29+R29)/2</f>
-        <v>30.5</v>
+        <f t="shared" si="4"/>
+        <v>39.5</v>
       </c>
       <c r="V29" s="9" t="s">
-        <v>690</v>
+        <v>669</v>
       </c>
       <c r="W29" s="20" t="s">
-        <v>691</v>
-      </c>
-      <c r="Y29" s="9" t="s">
-        <v>692</v>
-      </c>
-      <c r="Z29" s="16">
-        <v>140</v>
-      </c>
-      <c r="AA29" s="16">
-        <v>215</v>
+        <v>670</v>
       </c>
       <c r="AB29" s="9" t="s">
         <v>112</v>
@@ -10588,19 +10499,19 @@
         <v>77</v>
       </c>
       <c r="AD29" s="9" t="s">
-        <v>143</v>
+        <v>671</v>
       </c>
       <c r="AE29" s="10">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="AF29" s="9" t="s">
-        <v>167</v>
+        <v>212</v>
       </c>
       <c r="AG29" s="9" t="s">
         <v>80</v>
       </c>
       <c r="AH29" s="9" t="s">
-        <v>693</v>
+        <v>672</v>
       </c>
       <c r="AI29" s="9" t="s">
         <v>116</v>
@@ -10612,76 +10523,76 @@
         <v>117</v>
       </c>
       <c r="AL29" s="9" t="s">
-        <v>694</v>
+        <v>471</v>
       </c>
       <c r="AM29" s="9" t="s">
-        <v>694</v>
+        <v>673</v>
       </c>
       <c r="AN29" s="9" t="s">
-        <v>119</v>
+        <v>674</v>
       </c>
       <c r="AO29" s="9" t="s">
-        <v>120</v>
+        <v>675</v>
       </c>
       <c r="AP29" s="9" t="s">
-        <v>89</v>
+        <v>675</v>
       </c>
       <c r="AQ29" s="9" t="s">
-        <v>121</v>
+        <v>676</v>
       </c>
       <c r="AR29" s="9" t="s">
-        <v>695</v>
+        <v>677</v>
       </c>
       <c r="AS29" s="9" t="s">
-        <v>150</v>
+        <v>678</v>
       </c>
       <c r="AT29" s="9" t="s">
-        <v>407</v>
+        <v>679</v>
       </c>
       <c r="AU29" s="18">
-        <v>0.31900000000000001</v>
+        <v>0.32500000000000001</v>
       </c>
       <c r="AV29" s="9" t="s">
-        <v>696</v>
+        <v>680</v>
       </c>
       <c r="AW29" s="9">
-        <v>754</v>
+        <v>1144</v>
       </c>
       <c r="AX29" s="9">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="AY29" s="9" t="s">
-        <v>697</v>
+        <v>681</v>
       </c>
       <c r="AZ29" s="18">
-        <v>0.50739999999999996</v>
+        <v>0.50209999999999999</v>
       </c>
       <c r="BA29" s="9" t="s">
-        <v>698</v>
+        <v>296</v>
       </c>
       <c r="BB29" s="9">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="BC29" s="9" t="s">
-        <v>699</v>
+        <v>682</v>
       </c>
       <c r="BD29" s="9" t="s">
         <v>96</v>
       </c>
       <c r="BE29" s="11" t="s">
-        <v>700</v>
+        <v>683</v>
       </c>
       <c r="BF29" s="19">
-        <v>1.06</v>
+        <v>0.88</v>
       </c>
       <c r="BG29" s="9" t="s">
         <v>98</v>
       </c>
       <c r="BH29" s="9" t="s">
-        <v>701</v>
+        <v>684</v>
       </c>
       <c r="BI29" s="9">
-        <v>2090.31</v>
+        <v>4352.46</v>
       </c>
       <c r="BJ29" s="9" t="s">
         <v>100</v>
@@ -10696,10 +10607,10 @@
         <v>102</v>
       </c>
       <c r="BN29" s="9" t="s">
-        <v>702</v>
+        <v>685</v>
       </c>
       <c r="BO29" s="9" t="s">
-        <v>703</v>
+        <v>601</v>
       </c>
       <c r="BP29" s="9" t="s">
         <v>102</v>
@@ -10710,70 +10621,84 @@
     </row>
     <row r="30" spans="1:69">
       <c r="A30" s="10">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B30" s="11" t="s">
         <v>663</v>
       </c>
       <c r="C30" s="9" t="s">
-        <v>704</v>
+        <v>686</v>
       </c>
       <c r="D30" s="12" t="str">
-        <f>CONCATENATE(A30," ",C30)</f>
-        <v>403 捷市達</v>
+        <f t="shared" si="0"/>
+        <v>402 金捷市</v>
       </c>
       <c r="E30" s="12" t="s">
-        <v>705</v>
+        <v>687</v>
       </c>
       <c r="F30" s="13" t="s">
-        <v>706</v>
-      </c>
-      <c r="G30" s="14"/>
-      <c r="H30" s="13"/>
-      <c r="I30" s="14"/>
-      <c r="J30" s="14"/>
+        <v>688</v>
+      </c>
+      <c r="G30" s="14">
+        <v>26.46</v>
+      </c>
+      <c r="H30" s="13">
+        <v>24.18</v>
+      </c>
+      <c r="I30" s="14">
+        <v>29.57</v>
+      </c>
+      <c r="J30" s="14">
+        <v>21.5</v>
+      </c>
       <c r="K30" s="9" t="s">
-        <v>707</v>
+        <v>689</v>
       </c>
       <c r="L30" s="15">
-        <v>35</v>
+        <v>30.5</v>
       </c>
       <c r="M30" s="15">
-        <v>38</v>
+        <v>30.5</v>
       </c>
       <c r="N30" s="15">
-        <f>(L30+M30)/2</f>
-        <v>36.5</v>
+        <f t="shared" si="5"/>
+        <v>30.5</v>
       </c>
       <c r="O30" s="15">
-        <f>M30-N30</f>
-        <v>1.5</v>
+        <f t="shared" si="6"/>
+        <v>0</v>
       </c>
       <c r="P30" s="9" t="s">
-        <v>708</v>
+        <v>689</v>
       </c>
       <c r="Q30" s="15">
-        <v>45</v>
+        <v>30.5</v>
       </c>
       <c r="R30" s="15">
-        <v>48</v>
+        <v>30.5</v>
       </c>
       <c r="S30" s="15">
-        <f>R30-Q30</f>
-        <v>3</v>
+        <f t="shared" si="7"/>
+        <v>0</v>
       </c>
       <c r="T30" s="15">
-        <f>(Q30+R30)/2</f>
-        <v>46.5</v>
+        <f t="shared" si="4"/>
+        <v>30.5</v>
+      </c>
+      <c r="V30" s="9" t="s">
+        <v>690</v>
+      </c>
+      <c r="W30" s="20" t="s">
+        <v>691</v>
       </c>
       <c r="Y30" s="9" t="s">
-        <v>709</v>
+        <v>692</v>
       </c>
       <c r="Z30" s="16">
-        <v>175</v>
+        <v>140</v>
       </c>
       <c r="AA30" s="16">
-        <v>205</v>
+        <v>215</v>
       </c>
       <c r="AB30" s="9" t="s">
         <v>112</v>
@@ -10781,20 +10706,20 @@
       <c r="AC30" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="AD30" s="25" t="s">
-        <v>710</v>
+      <c r="AD30" s="9" t="s">
+        <v>143</v>
       </c>
       <c r="AE30" s="10">
-        <v>2025</v>
-      </c>
-      <c r="AF30" s="25" t="s">
-        <v>256</v>
+        <v>2020</v>
+      </c>
+      <c r="AF30" s="9" t="s">
+        <v>167</v>
       </c>
       <c r="AG30" s="9" t="s">
         <v>80</v>
       </c>
       <c r="AH30" s="9" t="s">
-        <v>711</v>
+        <v>693</v>
       </c>
       <c r="AI30" s="9" t="s">
         <v>116</v>
@@ -10806,10 +10731,10 @@
         <v>117</v>
       </c>
       <c r="AL30" s="9" t="s">
-        <v>712</v>
+        <v>694</v>
       </c>
       <c r="AM30" s="9" t="s">
-        <v>713</v>
+        <v>694</v>
       </c>
       <c r="AN30" s="9" t="s">
         <v>119</v>
@@ -10824,58 +10749,58 @@
         <v>121</v>
       </c>
       <c r="AR30" s="9" t="s">
-        <v>714</v>
+        <v>695</v>
       </c>
       <c r="AS30" s="9" t="s">
-        <v>715</v>
+        <v>150</v>
       </c>
       <c r="AT30" s="9" t="s">
-        <v>124</v>
+        <v>407</v>
       </c>
       <c r="AU30" s="18">
-        <v>0.32</v>
+        <v>0.31900000000000001</v>
       </c>
       <c r="AV30" s="9" t="s">
-        <v>716</v>
+        <v>696</v>
       </c>
       <c r="AW30" s="9">
-        <v>771</v>
+        <v>754</v>
       </c>
       <c r="AX30" s="9">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="AY30" s="9" t="s">
-        <v>717</v>
+        <v>697</v>
       </c>
       <c r="AZ30" s="18">
-        <v>0.49530000000000002</v>
+        <v>0.50739999999999996</v>
       </c>
       <c r="BA30" s="9" t="s">
-        <v>718</v>
+        <v>698</v>
       </c>
       <c r="BB30" s="9">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BC30" s="9" t="s">
-        <v>719</v>
+        <v>699</v>
       </c>
       <c r="BD30" s="9" t="s">
         <v>96</v>
       </c>
       <c r="BE30" s="11" t="s">
-        <v>720</v>
+        <v>700</v>
       </c>
       <c r="BF30" s="19">
-        <v>0.97</v>
+        <v>1.06</v>
       </c>
       <c r="BG30" s="9" t="s">
         <v>98</v>
       </c>
       <c r="BH30" s="9" t="s">
-        <v>721</v>
+        <v>701</v>
       </c>
       <c r="BI30" s="9">
-        <v>2067.2399999999998</v>
+        <v>2090.31</v>
       </c>
       <c r="BJ30" s="9" t="s">
         <v>100</v>
@@ -10890,10 +10815,10 @@
         <v>102</v>
       </c>
       <c r="BN30" s="9" t="s">
-        <v>722</v>
+        <v>702</v>
       </c>
       <c r="BO30" s="9" t="s">
-        <v>133</v>
+        <v>703</v>
       </c>
       <c r="BP30" s="9" t="s">
         <v>102</v>
@@ -10904,78 +10829,67 @@
     </row>
     <row r="31" spans="1:69">
       <c r="A31" s="10">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="B31" s="11" t="s">
         <v>663</v>
       </c>
       <c r="C31" s="9" t="s">
-        <v>723</v>
+        <v>704</v>
       </c>
       <c r="D31" s="12" t="str">
-        <f>CONCATENATE(A31," ",C31)</f>
-        <v>404 詠勝市中欣</v>
+        <f t="shared" si="0"/>
+        <v>403 捷市達</v>
       </c>
       <c r="E31" s="12" t="s">
-        <v>724</v>
+        <v>705</v>
       </c>
       <c r="F31" s="13" t="s">
-        <v>725</v>
-      </c>
-      <c r="G31" s="14">
-        <v>21.19</v>
-      </c>
-      <c r="H31" s="13">
-        <v>32.74</v>
-      </c>
-      <c r="I31" s="14">
-        <v>48.58</v>
-      </c>
-      <c r="J31" s="14">
-        <v>19.559999999999999</v>
-      </c>
+        <v>706</v>
+      </c>
+      <c r="G31" s="14"/>
+      <c r="H31" s="13"/>
+      <c r="I31" s="14"/>
+      <c r="J31" s="14"/>
       <c r="K31" s="9" t="s">
-        <v>726</v>
+        <v>707</v>
       </c>
       <c r="L31" s="15">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="M31" s="15">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="N31" s="15">
-        <f>(L31+M31)/2</f>
-        <v>29.5</v>
+        <f t="shared" si="5"/>
+        <v>36.5</v>
       </c>
       <c r="O31" s="15">
-        <f>M31-N31</f>
-        <v>2.5</v>
+        <f t="shared" si="6"/>
+        <v>1.5</v>
       </c>
       <c r="P31" s="9" t="s">
-        <v>727</v>
+        <v>708</v>
       </c>
       <c r="Q31" s="15">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="R31" s="15">
-        <v>25</v>
+        <v>48</v>
       </c>
       <c r="S31" s="15">
-        <f>R31-Q31</f>
-        <v>1</v>
+        <f t="shared" si="7"/>
+        <v>3</v>
       </c>
       <c r="T31" s="15">
-        <f>(Q31+R31)/2</f>
-        <v>24.5</v>
-      </c>
-      <c r="U31" s="15" t="s">
-        <v>138</v>
+        <f t="shared" si="4"/>
+        <v>46.5</v>
       </c>
       <c r="Y31" s="9" t="s">
-        <v>728</v>
+        <v>709</v>
       </c>
       <c r="Z31" s="16">
-        <v>155</v>
+        <v>175</v>
       </c>
       <c r="AA31" s="16">
         <v>205</v>
@@ -10987,22 +10901,22 @@
         <v>77</v>
       </c>
       <c r="AD31" s="25" t="s">
-        <v>729</v>
+        <v>710</v>
       </c>
       <c r="AE31" s="10">
-        <v>2023</v>
-      </c>
-      <c r="AF31" s="9" t="s">
-        <v>397</v>
+        <v>2025</v>
+      </c>
+      <c r="AF31" s="25" t="s">
+        <v>256</v>
       </c>
       <c r="AG31" s="9" t="s">
         <v>80</v>
       </c>
       <c r="AH31" s="9" t="s">
-        <v>730</v>
+        <v>711</v>
       </c>
       <c r="AI31" s="9" t="s">
-        <v>146</v>
+        <v>116</v>
       </c>
       <c r="AJ31" s="9" t="s">
         <v>83</v>
@@ -11011,76 +10925,76 @@
         <v>117</v>
       </c>
       <c r="AL31" s="9" t="s">
-        <v>731</v>
+        <v>712</v>
       </c>
       <c r="AM31" s="9" t="s">
-        <v>732</v>
+        <v>713</v>
       </c>
       <c r="AN31" s="9" t="s">
-        <v>733</v>
+        <v>119</v>
       </c>
       <c r="AO31" s="9" t="s">
-        <v>734</v>
+        <v>120</v>
       </c>
       <c r="AP31" s="9" t="s">
-        <v>734</v>
+        <v>89</v>
       </c>
       <c r="AQ31" s="9" t="s">
-        <v>735</v>
+        <v>121</v>
       </c>
       <c r="AR31" s="9" t="s">
-        <v>736</v>
+        <v>714</v>
       </c>
       <c r="AS31" s="9" t="s">
-        <v>737</v>
+        <v>715</v>
       </c>
       <c r="AT31" s="9" t="s">
-        <v>738</v>
+        <v>124</v>
       </c>
       <c r="AU31" s="18">
-        <v>0.33</v>
+        <v>0.32</v>
       </c>
       <c r="AV31" s="9" t="s">
-        <v>739</v>
+        <v>716</v>
       </c>
       <c r="AW31" s="9">
-        <v>257</v>
+        <v>771</v>
       </c>
       <c r="AX31" s="9">
-        <v>7</v>
+        <v>31</v>
       </c>
       <c r="AY31" s="9" t="s">
-        <v>740</v>
+        <v>717</v>
       </c>
       <c r="AZ31" s="18">
-        <v>0.53259999999999996</v>
+        <v>0.49530000000000002</v>
       </c>
       <c r="BA31" s="9" t="s">
-        <v>741</v>
+        <v>718</v>
       </c>
       <c r="BB31" s="9">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="BC31" s="9" t="s">
-        <v>742</v>
+        <v>719</v>
       </c>
       <c r="BD31" s="9" t="s">
         <v>96</v>
       </c>
       <c r="BE31" s="11" t="s">
-        <v>343</v>
+        <v>720</v>
       </c>
       <c r="BF31" s="19">
-        <v>1.01</v>
+        <v>0.97</v>
       </c>
       <c r="BG31" s="9" t="s">
         <v>98</v>
       </c>
       <c r="BH31" s="9" t="s">
-        <v>743</v>
+        <v>721</v>
       </c>
       <c r="BI31" s="9">
-        <v>926.66</v>
+        <v>2067.2399999999998</v>
       </c>
       <c r="BJ31" s="9" t="s">
         <v>100</v>
@@ -11095,10 +11009,10 @@
         <v>102</v>
       </c>
       <c r="BN31" s="9" t="s">
-        <v>744</v>
+        <v>722</v>
       </c>
       <c r="BO31" s="9" t="s">
-        <v>416</v>
+        <v>133</v>
       </c>
       <c r="BP31" s="9" t="s">
         <v>102</v>
@@ -11109,78 +11023,81 @@
     </row>
     <row r="32" spans="1:69">
       <c r="A32" s="10">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="B32" s="11" t="s">
         <v>663</v>
       </c>
       <c r="C32" s="9" t="s">
-        <v>745</v>
+        <v>723</v>
       </c>
       <c r="D32" s="12" t="str">
-        <f>CONCATENATE(A32," ",C32)</f>
-        <v>405 新A7</v>
+        <f t="shared" si="0"/>
+        <v>404 詠勝市中欣</v>
       </c>
       <c r="E32" s="12" t="s">
-        <v>746</v>
-      </c>
-      <c r="F32" s="20" t="s">
-        <v>747</v>
-      </c>
-      <c r="G32" s="21">
-        <v>26.59</v>
-      </c>
-      <c r="H32" s="22" t="s">
-        <v>748</v>
-      </c>
-      <c r="I32" s="21">
-        <v>31.65</v>
-      </c>
-      <c r="J32" s="21">
-        <v>24.01</v>
+        <v>724</v>
+      </c>
+      <c r="F32" s="13" t="s">
+        <v>725</v>
+      </c>
+      <c r="G32" s="14">
+        <v>21.19</v>
+      </c>
+      <c r="H32" s="13">
+        <v>32.74</v>
+      </c>
+      <c r="I32" s="14">
+        <v>48.58</v>
+      </c>
+      <c r="J32" s="14">
+        <v>19.559999999999999</v>
       </c>
       <c r="K32" s="9" t="s">
-        <v>749</v>
+        <v>726</v>
       </c>
       <c r="L32" s="15">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="M32" s="15">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="N32" s="15">
-        <f>(L32+M32)/2</f>
-        <v>32</v>
+        <f t="shared" si="5"/>
+        <v>29.5</v>
       </c>
       <c r="O32" s="15">
-        <f>M32-N32</f>
+        <f t="shared" si="6"/>
+        <v>2.5</v>
+      </c>
+      <c r="P32" s="9" t="s">
+        <v>727</v>
+      </c>
+      <c r="Q32" s="15">
+        <v>24</v>
+      </c>
+      <c r="R32" s="15">
+        <v>25</v>
+      </c>
+      <c r="S32" s="15">
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
-      <c r="P32" s="9" t="s">
-        <v>750</v>
-      </c>
-      <c r="Q32" s="15">
-        <v>32</v>
-      </c>
-      <c r="R32" s="15">
-        <v>35</v>
-      </c>
-      <c r="S32" s="15">
-        <f>R32-Q32</f>
-        <v>3</v>
-      </c>
       <c r="T32" s="15">
-        <f>(Q32+R32)/2</f>
-        <v>33.5</v>
+        <f t="shared" si="4"/>
+        <v>24.5</v>
+      </c>
+      <c r="U32" s="15" t="s">
+        <v>138</v>
       </c>
       <c r="Y32" s="9" t="s">
-        <v>751</v>
+        <v>728</v>
       </c>
       <c r="Z32" s="16">
-        <v>180</v>
+        <v>155</v>
       </c>
       <c r="AA32" s="16">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="AB32" s="9" t="s">
         <v>112</v>
@@ -11188,23 +11105,23 @@
       <c r="AC32" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="AD32" s="9" t="s">
-        <v>752</v>
+      <c r="AD32" s="25" t="s">
+        <v>729</v>
       </c>
       <c r="AE32" s="10">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="AF32" s="9" t="s">
-        <v>79</v>
+        <v>397</v>
       </c>
       <c r="AG32" s="9" t="s">
         <v>80</v>
       </c>
       <c r="AH32" s="9" t="s">
-        <v>753</v>
+        <v>730</v>
       </c>
       <c r="AI32" s="9" t="s">
-        <v>258</v>
+        <v>146</v>
       </c>
       <c r="AJ32" s="9" t="s">
         <v>83</v>
@@ -11213,82 +11130,82 @@
         <v>117</v>
       </c>
       <c r="AL32" s="9" t="s">
-        <v>754</v>
+        <v>731</v>
       </c>
       <c r="AM32" s="9" t="s">
-        <v>755</v>
+        <v>732</v>
       </c>
       <c r="AN32" s="9" t="s">
-        <v>756</v>
+        <v>733</v>
       </c>
       <c r="AO32" s="9" t="s">
-        <v>757</v>
+        <v>734</v>
       </c>
       <c r="AP32" s="9" t="s">
-        <v>89</v>
+        <v>734</v>
       </c>
       <c r="AQ32" s="9" t="s">
-        <v>90</v>
+        <v>735</v>
       </c>
       <c r="AR32" s="9" t="s">
-        <v>758</v>
+        <v>736</v>
       </c>
       <c r="AS32" s="9" t="s">
-        <v>759</v>
-      </c>
-      <c r="AT32" s="17">
-        <v>0.32</v>
+        <v>737</v>
+      </c>
+      <c r="AT32" s="9" t="s">
+        <v>738</v>
       </c>
       <c r="AU32" s="18">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="AV32" s="9" t="s">
-        <v>760</v>
+        <v>739</v>
       </c>
       <c r="AW32" s="9">
-        <v>371</v>
+        <v>257</v>
       </c>
       <c r="AX32" s="9">
-        <v>3</v>
-      </c>
-      <c r="AY32" s="18">
-        <v>0.46450000000000002</v>
+        <v>7</v>
+      </c>
+      <c r="AY32" s="9" t="s">
+        <v>740</v>
       </c>
       <c r="AZ32" s="18">
-        <v>0.46450000000000002</v>
+        <v>0.53259999999999996</v>
       </c>
       <c r="BA32" s="9" t="s">
-        <v>94</v>
+        <v>741</v>
       </c>
       <c r="BB32" s="9">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="BC32" s="9" t="s">
-        <v>761</v>
+        <v>742</v>
       </c>
       <c r="BD32" s="9" t="s">
         <v>96</v>
       </c>
       <c r="BE32" s="11" t="s">
-        <v>155</v>
+        <v>343</v>
       </c>
       <c r="BF32" s="19">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="BG32" s="9" t="s">
         <v>98</v>
       </c>
       <c r="BH32" s="9" t="s">
-        <v>762</v>
+        <v>743</v>
       </c>
       <c r="BI32" s="9">
-        <v>1538.68</v>
+        <v>926.66</v>
       </c>
       <c r="BJ32" s="9" t="s">
         <v>100</v>
       </c>
       <c r="BK32" s="9" t="s">
-        <v>367</v>
+        <v>414</v>
       </c>
       <c r="BL32" s="9" t="s">
         <v>102</v>
@@ -11297,10 +11214,10 @@
         <v>102</v>
       </c>
       <c r="BN32" s="9" t="s">
-        <v>763</v>
+        <v>744</v>
       </c>
       <c r="BO32" s="9" t="s">
-        <v>764</v>
+        <v>416</v>
       </c>
       <c r="BP32" s="9" t="s">
         <v>102</v>
@@ -11311,81 +11228,75 @@
     </row>
     <row r="33" spans="1:69">
       <c r="A33" s="10">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B33" s="11" t="s">
         <v>663</v>
       </c>
       <c r="C33" s="9" t="s">
-        <v>765</v>
+        <v>745</v>
       </c>
       <c r="D33" s="12" t="str">
-        <f>CONCATENATE(A33," ",C33)</f>
-        <v>406 富御捷境</v>
+        <f t="shared" si="0"/>
+        <v>405 新A7</v>
       </c>
       <c r="E33" s="12" t="s">
-        <v>766</v>
-      </c>
-      <c r="F33" s="13" t="s">
-        <v>767</v>
-      </c>
-      <c r="G33" s="14">
-        <v>25.73</v>
-      </c>
-      <c r="H33" s="13">
-        <v>23.14</v>
-      </c>
-      <c r="I33" s="14">
-        <v>31.69</v>
-      </c>
-      <c r="J33" s="14">
-        <v>19.95</v>
+        <v>746</v>
+      </c>
+      <c r="F33" s="20" t="s">
+        <v>747</v>
+      </c>
+      <c r="G33" s="21">
+        <v>26.59</v>
+      </c>
+      <c r="H33" s="22" t="s">
+        <v>748</v>
+      </c>
+      <c r="I33" s="21">
+        <v>31.65</v>
+      </c>
+      <c r="J33" s="21">
+        <v>24.01</v>
       </c>
       <c r="K33" s="9" t="s">
-        <v>394</v>
+        <v>749</v>
       </c>
       <c r="L33" s="15">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="M33" s="15">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="N33" s="15">
-        <f>(L33+M33)/2</f>
-        <v>28</v>
+        <f t="shared" si="5"/>
+        <v>32</v>
       </c>
       <c r="O33" s="15">
-        <f>M33-N33</f>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="P33" s="9" t="s">
-        <v>768</v>
+        <v>750</v>
       </c>
       <c r="Q33" s="15">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="R33" s="15">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="S33" s="15">
-        <f>R33-Q33</f>
-        <v>2</v>
+        <f t="shared" si="7"/>
+        <v>3</v>
       </c>
       <c r="T33" s="15">
-        <f>(Q33+R33)/2</f>
-        <v>31</v>
-      </c>
-      <c r="V33" s="9" t="s">
-        <v>769</v>
-      </c>
-      <c r="W33" s="20" t="s">
-        <v>770</v>
+        <f t="shared" si="4"/>
+        <v>33.5</v>
       </c>
       <c r="Y33" s="9" t="s">
-        <v>771</v>
+        <v>751</v>
       </c>
       <c r="Z33" s="16">
-        <v>195</v>
+        <v>180</v>
       </c>
       <c r="AA33" s="16">
         <v>200</v>
@@ -11397,22 +11308,22 @@
         <v>77</v>
       </c>
       <c r="AD33" s="9" t="s">
-        <v>143</v>
+        <v>752</v>
       </c>
       <c r="AE33" s="10">
-        <v>2020</v>
+        <v>2022</v>
       </c>
       <c r="AF33" s="9" t="s">
-        <v>167</v>
+        <v>79</v>
       </c>
       <c r="AG33" s="9" t="s">
         <v>80</v>
       </c>
       <c r="AH33" s="9" t="s">
-        <v>772</v>
+        <v>753</v>
       </c>
       <c r="AI33" s="9" t="s">
-        <v>146</v>
+        <v>258</v>
       </c>
       <c r="AJ33" s="9" t="s">
         <v>83</v>
@@ -11421,82 +11332,82 @@
         <v>117</v>
       </c>
       <c r="AL33" s="9" t="s">
-        <v>773</v>
+        <v>754</v>
       </c>
       <c r="AM33" s="9" t="s">
-        <v>774</v>
+        <v>755</v>
       </c>
       <c r="AN33" s="9" t="s">
-        <v>775</v>
+        <v>756</v>
       </c>
       <c r="AO33" s="9" t="s">
-        <v>776</v>
+        <v>757</v>
       </c>
       <c r="AP33" s="9" t="s">
         <v>89</v>
       </c>
       <c r="AQ33" s="9" t="s">
-        <v>121</v>
+        <v>90</v>
       </c>
       <c r="AR33" s="9" t="s">
-        <v>777</v>
+        <v>758</v>
       </c>
       <c r="AS33" s="9" t="s">
-        <v>778</v>
-      </c>
-      <c r="AT33" s="9" t="s">
-        <v>151</v>
+        <v>759</v>
+      </c>
+      <c r="AT33" s="17">
+        <v>0.32</v>
       </c>
       <c r="AU33" s="18">
-        <v>0.315</v>
+        <v>0.32</v>
       </c>
       <c r="AV33" s="9" t="s">
-        <v>779</v>
+        <v>760</v>
       </c>
       <c r="AW33" s="9">
-        <v>337</v>
+        <v>371</v>
       </c>
       <c r="AX33" s="9">
-        <v>2</v>
-      </c>
-      <c r="AY33" s="9" t="s">
-        <v>780</v>
+        <v>3</v>
+      </c>
+      <c r="AY33" s="18">
+        <v>0.46450000000000002</v>
       </c>
       <c r="AZ33" s="18">
-        <v>0.47499999999999998</v>
+        <v>0.46450000000000002</v>
       </c>
       <c r="BA33" s="9" t="s">
-        <v>322</v>
+        <v>94</v>
       </c>
       <c r="BB33" s="9">
         <v>15</v>
       </c>
       <c r="BC33" s="9" t="s">
-        <v>781</v>
+        <v>761</v>
       </c>
       <c r="BD33" s="9" t="s">
         <v>96</v>
       </c>
       <c r="BE33" s="11" t="s">
-        <v>782</v>
+        <v>155</v>
       </c>
       <c r="BF33" s="19">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="BG33" s="9" t="s">
         <v>98</v>
       </c>
       <c r="BH33" s="9" t="s">
-        <v>783</v>
+        <v>762</v>
       </c>
       <c r="BI33" s="9">
-        <v>1359.03</v>
+        <v>1538.68</v>
       </c>
       <c r="BJ33" s="9" t="s">
         <v>100</v>
       </c>
       <c r="BK33" s="9" t="s">
-        <v>524</v>
+        <v>367</v>
       </c>
       <c r="BL33" s="9" t="s">
         <v>102</v>
@@ -11505,10 +11416,10 @@
         <v>102</v>
       </c>
       <c r="BN33" s="9" t="s">
-        <v>784</v>
+        <v>763</v>
       </c>
       <c r="BO33" s="9" t="s">
-        <v>133</v>
+        <v>764</v>
       </c>
       <c r="BP33" s="9" t="s">
         <v>102</v>
@@ -11519,78 +11430,84 @@
     </row>
     <row r="34" spans="1:69">
       <c r="A34" s="10">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="B34" s="11" t="s">
         <v>663</v>
       </c>
       <c r="C34" s="9" t="s">
-        <v>785</v>
+        <v>765</v>
       </c>
       <c r="D34" s="12" t="str">
-        <f>CONCATENATE(A34," ",C34)</f>
-        <v>407 富宇哈佛苑</v>
+        <f t="shared" si="0"/>
+        <v>406 富御捷境</v>
       </c>
       <c r="E34" s="12" t="s">
-        <v>786</v>
+        <v>766</v>
       </c>
       <c r="F34" s="13" t="s">
-        <v>787</v>
+        <v>767</v>
       </c>
       <c r="G34" s="14">
-        <v>34.08</v>
-      </c>
-      <c r="H34" s="13" t="s">
-        <v>788</v>
+        <v>25.73</v>
+      </c>
+      <c r="H34" s="13">
+        <v>23.14</v>
       </c>
       <c r="I34" s="14">
-        <v>41.77</v>
+        <v>31.69</v>
       </c>
       <c r="J34" s="14">
-        <v>22.76</v>
+        <v>19.95</v>
       </c>
       <c r="K34" s="9" t="s">
-        <v>789</v>
+        <v>394</v>
       </c>
       <c r="L34" s="15">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="M34" s="15">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="N34" s="15">
-        <f>(L34+M34)/2</f>
-        <v>35.5</v>
+        <f t="shared" si="5"/>
+        <v>28</v>
       </c>
       <c r="O34" s="15">
-        <f>M34-N34</f>
-        <v>2.5</v>
+        <f t="shared" si="6"/>
+        <v>1</v>
       </c>
       <c r="P34" s="9" t="s">
-        <v>281</v>
+        <v>768</v>
       </c>
       <c r="Q34" s="15">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="R34" s="15">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="S34" s="15">
-        <f>R34-Q34</f>
-        <v>5</v>
+        <f t="shared" si="7"/>
+        <v>2</v>
       </c>
       <c r="T34" s="15">
-        <f>(Q34+R34)/2</f>
-        <v>46.5</v>
+        <f t="shared" si="4"/>
+        <v>31</v>
+      </c>
+      <c r="V34" s="9" t="s">
+        <v>769</v>
+      </c>
+      <c r="W34" s="20" t="s">
+        <v>770</v>
       </c>
       <c r="Y34" s="9" t="s">
-        <v>790</v>
+        <v>771</v>
       </c>
       <c r="Z34" s="16">
-        <v>180</v>
+        <v>195</v>
       </c>
       <c r="AA34" s="16">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="AB34" s="9" t="s">
         <v>112</v>
@@ -11599,22 +11516,22 @@
         <v>77</v>
       </c>
       <c r="AD34" s="9" t="s">
-        <v>791</v>
+        <v>143</v>
       </c>
       <c r="AE34" s="10">
-        <v>2023</v>
+        <v>2020</v>
       </c>
       <c r="AF34" s="9" t="s">
-        <v>468</v>
+        <v>167</v>
       </c>
       <c r="AG34" s="9" t="s">
         <v>80</v>
       </c>
       <c r="AH34" s="9" t="s">
-        <v>792</v>
+        <v>772</v>
       </c>
       <c r="AI34" s="9" t="s">
-        <v>116</v>
+        <v>146</v>
       </c>
       <c r="AJ34" s="9" t="s">
         <v>83</v>
@@ -11623,82 +11540,82 @@
         <v>117</v>
       </c>
       <c r="AL34" s="9" t="s">
-        <v>793</v>
+        <v>773</v>
       </c>
       <c r="AM34" s="9" t="s">
-        <v>794</v>
+        <v>774</v>
       </c>
       <c r="AN34" s="9" t="s">
-        <v>288</v>
+        <v>775</v>
       </c>
       <c r="AO34" s="9" t="s">
-        <v>289</v>
+        <v>776</v>
       </c>
       <c r="AP34" s="9" t="s">
-        <v>289</v>
+        <v>89</v>
       </c>
       <c r="AQ34" s="9" t="s">
-        <v>290</v>
+        <v>121</v>
       </c>
       <c r="AR34" s="9" t="s">
-        <v>291</v>
+        <v>777</v>
       </c>
       <c r="AS34" s="9" t="s">
-        <v>339</v>
+        <v>778</v>
       </c>
       <c r="AT34" s="9" t="s">
-        <v>293</v>
+        <v>151</v>
       </c>
       <c r="AU34" s="18">
-        <v>0.33500000000000002</v>
+        <v>0.315</v>
       </c>
       <c r="AV34" s="9" t="s">
-        <v>795</v>
+        <v>779</v>
       </c>
       <c r="AW34" s="9">
-        <v>483</v>
+        <v>337</v>
       </c>
       <c r="AX34" s="9">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="AY34" s="9" t="s">
-        <v>796</v>
+        <v>780</v>
       </c>
       <c r="AZ34" s="18">
-        <v>0.44180000000000003</v>
+        <v>0.47499999999999998</v>
       </c>
       <c r="BA34" s="9" t="s">
-        <v>296</v>
+        <v>322</v>
       </c>
       <c r="BB34" s="9">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="BC34" s="9" t="s">
-        <v>797</v>
+        <v>781</v>
       </c>
       <c r="BD34" s="9" t="s">
-        <v>580</v>
+        <v>96</v>
       </c>
       <c r="BE34" s="11" t="s">
-        <v>343</v>
+        <v>782</v>
       </c>
       <c r="BF34" s="19">
-        <v>1.01</v>
+        <v>0.9</v>
       </c>
       <c r="BG34" s="9" t="s">
         <v>98</v>
       </c>
       <c r="BH34" s="9" t="s">
-        <v>798</v>
+        <v>783</v>
       </c>
       <c r="BI34" s="9">
-        <v>2155.85</v>
+        <v>1359.03</v>
       </c>
       <c r="BJ34" s="9" t="s">
         <v>100</v>
       </c>
       <c r="BK34" s="9" t="s">
-        <v>367</v>
+        <v>524</v>
       </c>
       <c r="BL34" s="9" t="s">
         <v>102</v>
@@ -11707,10 +11624,10 @@
         <v>102</v>
       </c>
       <c r="BN34" s="9" t="s">
-        <v>799</v>
+        <v>784</v>
       </c>
       <c r="BO34" s="9" t="s">
-        <v>303</v>
+        <v>133</v>
       </c>
       <c r="BP34" s="9" t="s">
         <v>102</v>
@@ -11719,78 +11636,80 @@
         <v>134</v>
       </c>
     </row>
-    <row r="35" spans="1:69" ht="21">
+    <row r="35" spans="1:69">
       <c r="A35" s="10">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B35" s="11" t="s">
         <v>663</v>
       </c>
-      <c r="C35" s="12" t="s">
-        <v>800</v>
+      <c r="C35" s="9" t="s">
+        <v>785</v>
       </c>
       <c r="D35" s="12" t="str">
-        <f>CONCATENATE(A35," ",C35)</f>
-        <v>408 頤昌豐岳</v>
+        <f t="shared" si="0"/>
+        <v>407 富宇哈佛苑</v>
       </c>
       <c r="E35" s="12" t="s">
-        <v>801</v>
-      </c>
-      <c r="F35" s="20" t="s">
-        <v>802</v>
-      </c>
-      <c r="G35" s="21"/>
-      <c r="H35" s="22">
-        <v>24.99</v>
-      </c>
-      <c r="I35" s="21">
-        <v>27.76</v>
-      </c>
-      <c r="J35" s="21">
-        <v>22.52</v>
+        <v>786</v>
+      </c>
+      <c r="F35" s="13" t="s">
+        <v>787</v>
+      </c>
+      <c r="G35" s="14">
+        <v>34.08</v>
+      </c>
+      <c r="H35" s="13" t="s">
+        <v>788</v>
+      </c>
+      <c r="I35" s="14">
+        <v>41.77</v>
+      </c>
+      <c r="J35" s="14">
+        <v>22.76</v>
       </c>
       <c r="K35" s="9" t="s">
-        <v>803</v>
+        <v>789</v>
       </c>
       <c r="L35" s="15">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="M35" s="15">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="N35" s="15">
-        <f>(L35+M35)/2</f>
-        <v>30</v>
+        <f t="shared" si="5"/>
+        <v>35.5</v>
       </c>
       <c r="O35" s="15">
-        <f>M35-N35</f>
-        <v>0</v>
+        <f t="shared" si="6"/>
+        <v>2.5</v>
       </c>
       <c r="P35" s="9" t="s">
-        <v>803</v>
+        <v>281</v>
       </c>
       <c r="Q35" s="15">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="R35" s="15">
-        <v>30</v>
+        <v>49</v>
       </c>
       <c r="S35" s="15">
-        <f>R35-Q35</f>
-        <v>0</v>
+        <f t="shared" si="7"/>
+        <v>5</v>
       </c>
       <c r="T35" s="15">
-        <f>(Q35+R35)/2</f>
-        <v>30</v>
+        <f t="shared" si="4"/>
+        <v>46.5</v>
       </c>
       <c r="Y35" s="9" t="s">
-        <v>804</v>
+        <v>790</v>
       </c>
       <c r="Z35" s="16">
-        <v>160</v>
+        <v>180</v>
       </c>
       <c r="AA35" s="16">
-        <v>190</v>
+        <v>205</v>
       </c>
       <c r="AB35" s="9" t="s">
         <v>112</v>
@@ -11799,22 +11718,22 @@
         <v>77</v>
       </c>
       <c r="AD35" s="9" t="s">
-        <v>805</v>
+        <v>791</v>
       </c>
       <c r="AE35" s="10">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="AF35" s="9" t="s">
-        <v>114</v>
+        <v>468</v>
       </c>
       <c r="AG35" s="9" t="s">
         <v>80</v>
       </c>
       <c r="AH35" s="9" t="s">
-        <v>806</v>
+        <v>792</v>
       </c>
       <c r="AI35" s="9" t="s">
-        <v>258</v>
+        <v>116</v>
       </c>
       <c r="AJ35" s="9" t="s">
         <v>83</v>
@@ -11823,82 +11742,82 @@
         <v>117</v>
       </c>
       <c r="AL35" s="9" t="s">
-        <v>807</v>
-      </c>
-      <c r="AM35" s="26" t="s">
-        <v>807</v>
+        <v>793</v>
+      </c>
+      <c r="AM35" s="9" t="s">
+        <v>794</v>
       </c>
       <c r="AN35" s="9" t="s">
-        <v>808</v>
+        <v>288</v>
       </c>
       <c r="AO35" s="9" t="s">
-        <v>809</v>
+        <v>289</v>
       </c>
       <c r="AP35" s="9" t="s">
-        <v>809</v>
+        <v>289</v>
       </c>
       <c r="AQ35" s="9" t="s">
-        <v>810</v>
+        <v>290</v>
       </c>
       <c r="AR35" s="9" t="s">
-        <v>811</v>
+        <v>291</v>
       </c>
       <c r="AS35" s="9" t="s">
-        <v>812</v>
-      </c>
-      <c r="AT35" s="17">
-        <v>0.32</v>
+        <v>339</v>
+      </c>
+      <c r="AT35" s="9" t="s">
+        <v>293</v>
       </c>
       <c r="AU35" s="18">
-        <v>0.32</v>
+        <v>0.33500000000000002</v>
       </c>
       <c r="AV35" s="9" t="s">
-        <v>813</v>
+        <v>795</v>
       </c>
       <c r="AW35" s="9">
-        <v>154</v>
+        <v>483</v>
       </c>
       <c r="AX35" s="9">
-        <v>9</v>
-      </c>
-      <c r="AY35" s="18">
-        <v>0.4622</v>
+        <v>8</v>
+      </c>
+      <c r="AY35" s="9" t="s">
+        <v>796</v>
       </c>
       <c r="AZ35" s="18">
-        <v>0.4622</v>
+        <v>0.44180000000000003</v>
       </c>
       <c r="BA35" s="9" t="s">
-        <v>94</v>
+        <v>296</v>
       </c>
       <c r="BB35" s="9">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="BC35" s="9" t="s">
-        <v>814</v>
+        <v>797</v>
       </c>
       <c r="BD35" s="9" t="s">
-        <v>96</v>
+        <v>580</v>
       </c>
       <c r="BE35" s="11" t="s">
-        <v>815</v>
+        <v>343</v>
       </c>
       <c r="BF35" s="19">
-        <v>1.17</v>
+        <v>1.01</v>
       </c>
       <c r="BG35" s="9" t="s">
         <v>98</v>
       </c>
       <c r="BH35" s="9" t="s">
-        <v>816</v>
+        <v>798</v>
       </c>
       <c r="BI35" s="9">
-        <v>933.78</v>
+        <v>2155.85</v>
       </c>
       <c r="BJ35" s="9" t="s">
         <v>100</v>
       </c>
       <c r="BK35" s="9" t="s">
-        <v>817</v>
+        <v>367</v>
       </c>
       <c r="BL35" s="9" t="s">
         <v>102</v>
@@ -11907,10 +11826,10 @@
         <v>102</v>
       </c>
       <c r="BN35" s="9" t="s">
-        <v>818</v>
+        <v>799</v>
       </c>
       <c r="BO35" s="9" t="s">
-        <v>819</v>
+        <v>303</v>
       </c>
       <c r="BP35" s="9" t="s">
         <v>102</v>
@@ -11919,99 +11838,99 @@
         <v>134</v>
       </c>
     </row>
-    <row r="36" spans="1:69">
+    <row r="36" spans="1:69" ht="21">
       <c r="A36" s="10">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B36" s="11" t="s">
         <v>663</v>
       </c>
       <c r="C36" s="12" t="s">
-        <v>820</v>
+        <v>800</v>
       </c>
       <c r="D36" s="12" t="str">
-        <f>CONCATENATE(A36," ",C36)</f>
-        <v>409 新未來2</v>
+        <f t="shared" si="0"/>
+        <v>408 頤昌豐岳</v>
       </c>
       <c r="E36" s="12" t="s">
-        <v>821</v>
+        <v>801</v>
       </c>
       <c r="F36" s="20" t="s">
-        <v>822</v>
+        <v>802</v>
       </c>
       <c r="G36" s="21"/>
       <c r="H36" s="22">
-        <v>26.39</v>
+        <v>24.99</v>
       </c>
       <c r="I36" s="21">
-        <v>29.56</v>
+        <v>27.76</v>
       </c>
       <c r="J36" s="21">
-        <v>23.12</v>
+        <v>22.52</v>
       </c>
       <c r="K36" s="9" t="s">
-        <v>823</v>
+        <v>803</v>
       </c>
       <c r="L36" s="15">
         <v>30</v>
       </c>
       <c r="M36" s="15">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="N36" s="15">
-        <f>(L36+M36)/2</f>
-        <v>31</v>
+        <f t="shared" si="5"/>
+        <v>30</v>
       </c>
       <c r="O36" s="15">
-        <f>M36-N36</f>
-        <v>1</v>
+        <f t="shared" si="6"/>
+        <v>0</v>
       </c>
       <c r="P36" s="9" t="s">
-        <v>823</v>
+        <v>803</v>
       </c>
       <c r="Q36" s="15">
         <v>30</v>
       </c>
       <c r="R36" s="15">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="S36" s="15">
-        <f>R36-Q36</f>
-        <v>2</v>
+        <f t="shared" si="7"/>
+        <v>0</v>
       </c>
       <c r="T36" s="15">
-        <f>(Q36+R36)/2</f>
-        <v>31</v>
+        <f t="shared" si="4"/>
+        <v>30</v>
       </c>
       <c r="Y36" s="9" t="s">
-        <v>824</v>
+        <v>804</v>
       </c>
       <c r="Z36" s="16">
-        <v>180</v>
+        <v>160</v>
       </c>
       <c r="AA36" s="16">
-        <v>210</v>
-      </c>
-      <c r="AB36" s="17">
-        <v>0.75</v>
+        <v>190</v>
+      </c>
+      <c r="AB36" s="9" t="s">
+        <v>112</v>
       </c>
       <c r="AC36" s="9" t="s">
         <v>77</v>
       </c>
       <c r="AD36" s="9" t="s">
-        <v>825</v>
+        <v>805</v>
       </c>
       <c r="AE36" s="10">
         <v>2022</v>
       </c>
       <c r="AF36" s="9" t="s">
-        <v>425</v>
+        <v>114</v>
       </c>
       <c r="AG36" s="9" t="s">
         <v>80</v>
       </c>
       <c r="AH36" s="9" t="s">
-        <v>826</v>
+        <v>806</v>
       </c>
       <c r="AI36" s="9" t="s">
         <v>258</v>
@@ -12023,82 +11942,82 @@
         <v>117</v>
       </c>
       <c r="AL36" s="9" t="s">
-        <v>827</v>
-      </c>
-      <c r="AM36" s="9" t="s">
-        <v>828</v>
+        <v>807</v>
+      </c>
+      <c r="AM36" s="26" t="s">
+        <v>807</v>
       </c>
       <c r="AN36" s="9" t="s">
-        <v>829</v>
+        <v>808</v>
       </c>
       <c r="AO36" s="9" t="s">
-        <v>830</v>
+        <v>809</v>
       </c>
       <c r="AP36" s="9" t="s">
-        <v>830</v>
+        <v>809</v>
       </c>
       <c r="AQ36" s="9" t="s">
-        <v>831</v>
+        <v>810</v>
       </c>
       <c r="AR36" s="9" t="s">
-        <v>832</v>
+        <v>811</v>
       </c>
       <c r="AS36" s="9" t="s">
-        <v>759</v>
-      </c>
-      <c r="AT36" s="18">
-        <v>0.33</v>
+        <v>812</v>
+      </c>
+      <c r="AT36" s="17">
+        <v>0.32</v>
       </c>
       <c r="AU36" s="18">
-        <v>0.33</v>
+        <v>0.32</v>
       </c>
       <c r="AV36" s="9" t="s">
-        <v>833</v>
+        <v>813</v>
       </c>
       <c r="AW36" s="9">
-        <v>376</v>
+        <v>154</v>
       </c>
       <c r="AX36" s="9">
         <v>9</v>
       </c>
       <c r="AY36" s="18">
-        <v>0.36220000000000002</v>
+        <v>0.4622</v>
       </c>
       <c r="AZ36" s="18">
-        <v>0.36220000000000002</v>
+        <v>0.4622</v>
       </c>
       <c r="BA36" s="9" t="s">
-        <v>658</v>
+        <v>94</v>
       </c>
       <c r="BB36" s="9">
-        <v>22</v>
-      </c>
-      <c r="BC36" s="18" t="s">
-        <v>834</v>
+        <v>15</v>
+      </c>
+      <c r="BC36" s="9" t="s">
+        <v>814</v>
       </c>
       <c r="BD36" s="9" t="s">
-        <v>269</v>
+        <v>96</v>
       </c>
       <c r="BE36" s="11" t="s">
-        <v>270</v>
+        <v>815</v>
       </c>
       <c r="BF36" s="19">
-        <v>1.1399999999999999</v>
+        <v>1.17</v>
       </c>
       <c r="BG36" s="9" t="s">
         <v>98</v>
       </c>
       <c r="BH36" s="9" t="s">
-        <v>835</v>
+        <v>816</v>
       </c>
       <c r="BI36" s="9">
-        <v>1955.56</v>
+        <v>933.78</v>
       </c>
       <c r="BJ36" s="9" t="s">
         <v>100</v>
       </c>
       <c r="BK36" s="9" t="s">
-        <v>367</v>
+        <v>817</v>
       </c>
       <c r="BL36" s="9" t="s">
         <v>102</v>
@@ -12107,10 +12026,10 @@
         <v>102</v>
       </c>
       <c r="BN36" s="9" t="s">
-        <v>836</v>
+        <v>818</v>
       </c>
       <c r="BO36" s="9" t="s">
-        <v>837</v>
+        <v>819</v>
       </c>
       <c r="BP36" s="9" t="s">
         <v>102</v>
@@ -12119,101 +12038,99 @@
         <v>134</v>
       </c>
     </row>
-    <row r="37" spans="1:69" ht="16">
+    <row r="37" spans="1:69">
       <c r="A37" s="10">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B37" s="11" t="s">
         <v>663</v>
       </c>
-      <c r="C37" s="23" t="s">
-        <v>838</v>
+      <c r="C37" s="12" t="s">
+        <v>820</v>
       </c>
       <c r="D37" s="12" t="str">
-        <f>CONCATENATE(A37," ",C37)</f>
-        <v>410 新未來3</v>
+        <f t="shared" si="0"/>
+        <v>409 新未來2</v>
       </c>
       <c r="E37" s="12" t="s">
-        <v>839</v>
+        <v>821</v>
       </c>
       <c r="F37" s="20" t="s">
-        <v>840</v>
-      </c>
-      <c r="G37" s="21">
-        <v>30.02</v>
-      </c>
+        <v>822</v>
+      </c>
+      <c r="G37" s="21"/>
       <c r="H37" s="22">
-        <v>29.48</v>
+        <v>26.39</v>
       </c>
       <c r="I37" s="21">
+        <v>29.56</v>
+      </c>
+      <c r="J37" s="21">
+        <v>23.12</v>
+      </c>
+      <c r="K37" s="9" t="s">
+        <v>823</v>
+      </c>
+      <c r="L37" s="15">
+        <v>30</v>
+      </c>
+      <c r="M37" s="15">
         <v>32</v>
       </c>
-      <c r="J37" s="21">
-        <v>25.65</v>
-      </c>
-      <c r="K37" s="9" t="s">
-        <v>841</v>
-      </c>
-      <c r="L37" s="15">
-        <v>33</v>
-      </c>
-      <c r="M37" s="15">
-        <v>38</v>
-      </c>
       <c r="N37" s="15">
-        <f>(L37+M37)/2</f>
-        <v>35.5</v>
+        <f t="shared" si="5"/>
+        <v>31</v>
       </c>
       <c r="O37" s="15">
-        <f>M37-N37</f>
-        <v>2.5</v>
+        <f t="shared" si="6"/>
+        <v>1</v>
       </c>
       <c r="P37" s="9" t="s">
-        <v>841</v>
+        <v>823</v>
       </c>
       <c r="Q37" s="15">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="R37" s="15">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="S37" s="15">
-        <f>R37-Q37</f>
-        <v>5</v>
+        <f t="shared" si="7"/>
+        <v>2</v>
       </c>
       <c r="T37" s="15">
-        <f>(Q37+R37)/2</f>
-        <v>35.5</v>
+        <f t="shared" si="4"/>
+        <v>31</v>
       </c>
       <c r="Y37" s="9" t="s">
-        <v>842</v>
+        <v>824</v>
       </c>
       <c r="Z37" s="16">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="AA37" s="16">
-        <v>190</v>
-      </c>
-      <c r="AB37" s="9" t="s">
-        <v>112</v>
+        <v>210</v>
+      </c>
+      <c r="AB37" s="17">
+        <v>0.75</v>
       </c>
       <c r="AC37" s="9" t="s">
         <v>77</v>
       </c>
       <c r="AD37" s="9" t="s">
-        <v>843</v>
+        <v>825</v>
       </c>
       <c r="AE37" s="10">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="AF37" s="9" t="s">
-        <v>468</v>
+        <v>425</v>
       </c>
       <c r="AG37" s="9" t="s">
         <v>80</v>
       </c>
       <c r="AH37" s="9" t="s">
-        <v>844</v>
+        <v>826</v>
       </c>
       <c r="AI37" s="9" t="s">
         <v>258</v>
@@ -12225,7 +12142,7 @@
         <v>117</v>
       </c>
       <c r="AL37" s="9" t="s">
-        <v>845</v>
+        <v>827</v>
       </c>
       <c r="AM37" s="9" t="s">
         <v>828</v>
@@ -12249,52 +12166,52 @@
         <v>759</v>
       </c>
       <c r="AT37" s="18">
-        <v>0.3327</v>
+        <v>0.33</v>
       </c>
       <c r="AU37" s="18">
-        <v>0.3327</v>
+        <v>0.33</v>
       </c>
       <c r="AV37" s="9" t="s">
-        <v>846</v>
+        <v>833</v>
       </c>
       <c r="AW37" s="9">
-        <v>582</v>
+        <v>376</v>
       </c>
       <c r="AX37" s="9">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="AY37" s="18">
-        <v>0.38300000000000001</v>
+        <v>0.36220000000000002</v>
       </c>
       <c r="AZ37" s="18">
-        <v>0.38300000000000001</v>
+        <v>0.36220000000000002</v>
       </c>
       <c r="BA37" s="9" t="s">
-        <v>847</v>
+        <v>658</v>
       </c>
       <c r="BB37" s="9">
         <v>22</v>
       </c>
       <c r="BC37" s="18" t="s">
-        <v>848</v>
+        <v>834</v>
       </c>
       <c r="BD37" s="9" t="s">
         <v>269</v>
       </c>
       <c r="BE37" s="11" t="s">
-        <v>155</v>
+        <v>270</v>
       </c>
       <c r="BF37" s="19">
-        <v>1</v>
+        <v>1.1399999999999999</v>
       </c>
       <c r="BG37" s="9" t="s">
         <v>98</v>
       </c>
       <c r="BH37" s="9" t="s">
-        <v>849</v>
+        <v>835</v>
       </c>
       <c r="BI37" s="9">
-        <v>2513.2199999999998</v>
+        <v>1955.56</v>
       </c>
       <c r="BJ37" s="9" t="s">
         <v>100</v>
@@ -12309,10 +12226,10 @@
         <v>102</v>
       </c>
       <c r="BN37" s="9" t="s">
-        <v>850</v>
+        <v>836</v>
       </c>
       <c r="BO37" s="9" t="s">
-        <v>851</v>
+        <v>837</v>
       </c>
       <c r="BP37" s="9" t="s">
         <v>102</v>
@@ -12321,74 +12238,80 @@
         <v>134</v>
       </c>
     </row>
-    <row r="38" spans="1:69">
+    <row r="38" spans="1:69" ht="16">
       <c r="A38" s="10">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="B38" s="11" t="s">
         <v>663</v>
       </c>
-      <c r="C38" s="9" t="s">
-        <v>852</v>
+      <c r="C38" s="23" t="s">
+        <v>838</v>
       </c>
       <c r="D38" s="12" t="str">
-        <f>CONCATENATE(A38," ",C38)</f>
-        <v>411 和洲金剛</v>
+        <f t="shared" si="0"/>
+        <v>410 新未來3</v>
       </c>
       <c r="E38" s="12" t="s">
-        <v>853</v>
-      </c>
-      <c r="F38" s="13" t="s">
-        <v>854</v>
-      </c>
-      <c r="G38" s="14">
-        <v>26.33</v>
-      </c>
-      <c r="H38" s="13" t="s">
-        <v>855</v>
-      </c>
-      <c r="I38" s="14">
-        <v>28.67</v>
-      </c>
-      <c r="J38" s="14">
-        <v>21.01</v>
+        <v>839</v>
+      </c>
+      <c r="F38" s="20" t="s">
+        <v>840</v>
+      </c>
+      <c r="G38" s="21">
+        <v>30.02</v>
+      </c>
+      <c r="H38" s="22">
+        <v>29.48</v>
+      </c>
+      <c r="I38" s="21">
+        <v>32</v>
+      </c>
+      <c r="J38" s="21">
+        <v>25.65</v>
       </c>
       <c r="K38" s="9" t="s">
-        <v>856</v>
+        <v>841</v>
       </c>
       <c r="L38" s="15">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="M38" s="15">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="N38" s="15">
-        <f>(L38+M38)/2</f>
-        <v>26</v>
+        <f t="shared" si="5"/>
+        <v>35.5</v>
       </c>
       <c r="O38" s="15">
-        <f>M38-N38</f>
-        <v>1</v>
+        <f t="shared" si="6"/>
+        <v>2.5</v>
       </c>
       <c r="P38" s="9" t="s">
-        <v>768</v>
+        <v>841</v>
       </c>
       <c r="Q38" s="15">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="R38" s="15">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="S38" s="15">
-        <f>R38-Q38</f>
-        <v>2</v>
+        <f t="shared" si="7"/>
+        <v>5</v>
       </c>
       <c r="T38" s="15">
-        <f>(Q38+R38)/2</f>
-        <v>31</v>
+        <f t="shared" si="4"/>
+        <v>35.5</v>
       </c>
       <c r="Y38" s="9" t="s">
-        <v>269</v>
+        <v>842</v>
+      </c>
+      <c r="Z38" s="16">
+        <v>190</v>
+      </c>
+      <c r="AA38" s="16">
+        <v>190</v>
       </c>
       <c r="AB38" s="9" t="s">
         <v>112</v>
@@ -12397,22 +12320,22 @@
         <v>77</v>
       </c>
       <c r="AD38" s="9" t="s">
-        <v>211</v>
+        <v>843</v>
       </c>
       <c r="AE38" s="10">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="AF38" s="9" t="s">
-        <v>114</v>
+        <v>468</v>
       </c>
       <c r="AG38" s="9" t="s">
         <v>80</v>
       </c>
       <c r="AH38" s="9" t="s">
-        <v>857</v>
+        <v>844</v>
       </c>
       <c r="AI38" s="9" t="s">
-        <v>116</v>
+        <v>258</v>
       </c>
       <c r="AJ38" s="9" t="s">
         <v>83</v>
@@ -12421,94 +12344,94 @@
         <v>117</v>
       </c>
       <c r="AL38" s="9" t="s">
-        <v>858</v>
+        <v>845</v>
       </c>
       <c r="AM38" s="9" t="s">
-        <v>859</v>
+        <v>828</v>
       </c>
       <c r="AN38" s="9" t="s">
-        <v>860</v>
+        <v>829</v>
       </c>
       <c r="AO38" s="9" t="s">
-        <v>861</v>
+        <v>830</v>
       </c>
       <c r="AP38" s="9" t="s">
-        <v>89</v>
+        <v>830</v>
       </c>
       <c r="AQ38" s="9" t="s">
-        <v>121</v>
+        <v>831</v>
       </c>
       <c r="AR38" s="9" t="s">
-        <v>862</v>
+        <v>832</v>
       </c>
       <c r="AS38" s="9" t="s">
-        <v>150</v>
-      </c>
-      <c r="AT38" s="9" t="s">
-        <v>124</v>
+        <v>759</v>
+      </c>
+      <c r="AT38" s="18">
+        <v>0.3327</v>
       </c>
       <c r="AU38" s="18">
-        <v>0.32</v>
+        <v>0.3327</v>
       </c>
       <c r="AV38" s="9" t="s">
-        <v>863</v>
+        <v>846</v>
       </c>
       <c r="AW38" s="9">
-        <v>210</v>
+        <v>582</v>
       </c>
       <c r="AX38" s="9">
-        <v>11</v>
-      </c>
-      <c r="AY38" s="9" t="s">
-        <v>864</v>
+        <v>16</v>
+      </c>
+      <c r="AY38" s="18">
+        <v>0.38300000000000001</v>
       </c>
       <c r="AZ38" s="18">
-        <v>0.45540000000000003</v>
+        <v>0.38300000000000001</v>
       </c>
       <c r="BA38" s="9" t="s">
-        <v>865</v>
+        <v>847</v>
       </c>
       <c r="BB38" s="9">
-        <v>15</v>
-      </c>
-      <c r="BC38" s="9" t="s">
-        <v>866</v>
+        <v>22</v>
+      </c>
+      <c r="BC38" s="18" t="s">
+        <v>848</v>
       </c>
       <c r="BD38" s="9" t="s">
-        <v>96</v>
+        <v>269</v>
       </c>
       <c r="BE38" s="11" t="s">
-        <v>325</v>
+        <v>155</v>
       </c>
       <c r="BF38" s="19">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="BG38" s="9" t="s">
         <v>98</v>
       </c>
       <c r="BH38" s="9" t="s">
-        <v>783</v>
+        <v>849</v>
       </c>
       <c r="BI38" s="9">
-        <v>1359.03</v>
+        <v>2513.2199999999998</v>
       </c>
       <c r="BJ38" s="9" t="s">
         <v>100</v>
       </c>
       <c r="BK38" s="9" t="s">
-        <v>867</v>
+        <v>367</v>
       </c>
       <c r="BL38" s="9" t="s">
-        <v>868</v>
+        <v>102</v>
       </c>
       <c r="BM38" s="9" t="s">
         <v>102</v>
       </c>
       <c r="BN38" s="9" t="s">
-        <v>869</v>
+        <v>850</v>
       </c>
       <c r="BO38" s="9" t="s">
-        <v>133</v>
+        <v>851</v>
       </c>
       <c r="BP38" s="9" t="s">
         <v>102</v>
@@ -12519,78 +12442,72 @@
     </row>
     <row r="39" spans="1:69">
       <c r="A39" s="10">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B39" s="11" t="s">
         <v>663</v>
       </c>
       <c r="C39" s="9" t="s">
-        <v>870</v>
+        <v>852</v>
       </c>
       <c r="D39" s="12" t="str">
-        <f>CONCATENATE(A39," ",C39)</f>
-        <v>412 君邑丘比特</v>
+        <f t="shared" si="0"/>
+        <v>411 和洲金剛</v>
       </c>
       <c r="E39" s="12" t="s">
-        <v>871</v>
+        <v>853</v>
       </c>
       <c r="F39" s="13" t="s">
-        <v>872</v>
+        <v>854</v>
       </c>
       <c r="G39" s="14">
-        <v>27.47</v>
+        <v>26.33</v>
       </c>
       <c r="H39" s="13" t="s">
-        <v>873</v>
+        <v>855</v>
       </c>
       <c r="I39" s="14">
-        <v>32.229999999999997</v>
+        <v>28.67</v>
       </c>
       <c r="J39" s="14">
-        <v>22.94</v>
+        <v>21.01</v>
       </c>
       <c r="K39" s="9" t="s">
-        <v>874</v>
+        <v>856</v>
       </c>
       <c r="L39" s="15">
-        <v>27.8</v>
+        <v>25</v>
       </c>
       <c r="M39" s="15">
+        <v>27</v>
+      </c>
+      <c r="N39" s="15">
+        <f t="shared" si="5"/>
+        <v>26</v>
+      </c>
+      <c r="O39" s="15">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="P39" s="9" t="s">
+        <v>768</v>
+      </c>
+      <c r="Q39" s="15">
+        <v>30</v>
+      </c>
+      <c r="R39" s="15">
         <v>32</v>
       </c>
-      <c r="N39" s="15">
-        <f>(L39+M39)/2</f>
-        <v>29.9</v>
-      </c>
-      <c r="O39" s="15">
-        <f>M39-N39</f>
-        <v>2.1000000000000014</v>
-      </c>
-      <c r="P39" s="9" t="s">
-        <v>875</v>
-      </c>
-      <c r="Q39" s="15">
-        <v>29.8</v>
-      </c>
-      <c r="R39" s="15">
-        <v>38.200000000000003</v>
-      </c>
       <c r="S39" s="15">
-        <f>R39-Q39</f>
-        <v>8.4000000000000021</v>
+        <f t="shared" si="7"/>
+        <v>2</v>
       </c>
       <c r="T39" s="15">
-        <f>(Q39+R39)/2</f>
-        <v>34</v>
+        <f t="shared" si="4"/>
+        <v>31</v>
       </c>
       <c r="Y39" s="9" t="s">
-        <v>876</v>
-      </c>
-      <c r="Z39" s="16">
-        <v>180</v>
-      </c>
-      <c r="AA39" s="16">
-        <v>230</v>
+        <v>269</v>
       </c>
       <c r="AB39" s="9" t="s">
         <v>112</v>
@@ -12599,100 +12516,100 @@
         <v>77</v>
       </c>
       <c r="AD39" s="9" t="s">
-        <v>877</v>
+        <v>211</v>
       </c>
       <c r="AE39" s="10">
         <v>2022</v>
       </c>
       <c r="AF39" s="9" t="s">
-        <v>425</v>
+        <v>114</v>
       </c>
       <c r="AG39" s="9" t="s">
         <v>80</v>
       </c>
       <c r="AH39" s="9" t="s">
-        <v>878</v>
+        <v>857</v>
       </c>
       <c r="AI39" s="9" t="s">
-        <v>258</v>
+        <v>116</v>
       </c>
       <c r="AJ39" s="9" t="s">
         <v>83</v>
       </c>
       <c r="AK39" s="9" t="s">
-        <v>879</v>
+        <v>117</v>
       </c>
       <c r="AL39" s="9" t="s">
-        <v>880</v>
+        <v>858</v>
       </c>
       <c r="AM39" s="9" t="s">
-        <v>881</v>
+        <v>859</v>
       </c>
       <c r="AN39" s="9" t="s">
-        <v>882</v>
+        <v>860</v>
       </c>
       <c r="AO39" s="9" t="s">
-        <v>883</v>
+        <v>861</v>
       </c>
       <c r="AP39" s="9" t="s">
-        <v>883</v>
+        <v>89</v>
       </c>
       <c r="AQ39" s="9" t="s">
-        <v>884</v>
+        <v>121</v>
       </c>
       <c r="AR39" s="9" t="s">
-        <v>884</v>
+        <v>862</v>
       </c>
       <c r="AS39" s="9" t="s">
-        <v>885</v>
+        <v>150</v>
       </c>
       <c r="AT39" s="9" t="s">
-        <v>886</v>
+        <v>124</v>
       </c>
       <c r="AU39" s="18">
-        <v>0.33129999999999998</v>
+        <v>0.32</v>
       </c>
       <c r="AV39" s="9" t="s">
-        <v>887</v>
+        <v>863</v>
       </c>
       <c r="AW39" s="9">
-        <v>173</v>
+        <v>210</v>
       </c>
       <c r="AX39" s="9">
-        <v>5</v>
-      </c>
-      <c r="AY39" s="18">
-        <v>0.46150000000000002</v>
+        <v>11</v>
+      </c>
+      <c r="AY39" s="9" t="s">
+        <v>864</v>
       </c>
       <c r="AZ39" s="18">
-        <v>0.46150000000000002</v>
+        <v>0.45540000000000003</v>
       </c>
       <c r="BA39" s="9" t="s">
-        <v>888</v>
+        <v>865</v>
       </c>
       <c r="BB39" s="9">
         <v>15</v>
       </c>
       <c r="BC39" s="9" t="s">
-        <v>889</v>
+        <v>866</v>
       </c>
       <c r="BD39" s="9" t="s">
         <v>96</v>
       </c>
       <c r="BE39" s="11" t="s">
-        <v>890</v>
+        <v>325</v>
       </c>
       <c r="BF39" s="19">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="BG39" s="9" t="s">
         <v>98</v>
       </c>
       <c r="BH39" s="9" t="s">
-        <v>891</v>
+        <v>783</v>
       </c>
       <c r="BI39" s="9">
-        <v>1030.74</v>
+        <v>1359.03</v>
       </c>
       <c r="BJ39" s="9" t="s">
         <v>100</v>
@@ -12701,16 +12618,16 @@
         <v>867</v>
       </c>
       <c r="BL39" s="9" t="s">
-        <v>102</v>
+        <v>868</v>
       </c>
       <c r="BM39" s="9" t="s">
         <v>102</v>
       </c>
       <c r="BN39" s="9" t="s">
-        <v>892</v>
+        <v>869</v>
       </c>
       <c r="BO39" s="9" t="s">
-        <v>893</v>
+        <v>133</v>
       </c>
       <c r="BP39" s="9" t="s">
         <v>102</v>
@@ -12721,93 +12638,99 @@
     </row>
     <row r="40" spans="1:69">
       <c r="A40" s="10">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B40" s="11" t="s">
         <v>663</v>
       </c>
       <c r="C40" s="9" t="s">
-        <v>894</v>
+        <v>870</v>
       </c>
       <c r="D40" s="12" t="str">
-        <f>CONCATENATE(A40," ",C40)</f>
-        <v>413 頤昌璞岳</v>
+        <f t="shared" si="0"/>
+        <v>412 君邑丘比特</v>
       </c>
       <c r="E40" s="12" t="s">
-        <v>895</v>
+        <v>871</v>
       </c>
       <c r="F40" s="13" t="s">
-        <v>896</v>
+        <v>872</v>
       </c>
       <c r="G40" s="14">
-        <v>27.11</v>
-      </c>
-      <c r="H40" s="13">
-        <v>26.83</v>
+        <v>27.47</v>
+      </c>
+      <c r="H40" s="13" t="s">
+        <v>873</v>
       </c>
       <c r="I40" s="14">
-        <v>34.42</v>
+        <v>32.229999999999997</v>
       </c>
       <c r="J40" s="14">
-        <v>24.79</v>
+        <v>22.94</v>
       </c>
       <c r="K40" s="9" t="s">
-        <v>897</v>
+        <v>874</v>
       </c>
       <c r="L40" s="15">
+        <v>27.8</v>
+      </c>
+      <c r="M40" s="15">
         <v>32</v>
       </c>
-      <c r="M40" s="15">
-        <v>33</v>
-      </c>
       <c r="N40" s="15">
-        <f>(L40+M40)/2</f>
-        <v>32.5</v>
+        <f t="shared" si="5"/>
+        <v>29.9</v>
       </c>
       <c r="O40" s="15">
-        <f>M40-N40</f>
-        <v>0.5</v>
+        <f t="shared" si="6"/>
+        <v>2.1000000000000014</v>
       </c>
       <c r="P40" s="9" t="s">
-        <v>897</v>
+        <v>875</v>
       </c>
       <c r="Q40" s="15">
-        <v>32</v>
+        <v>29.8</v>
       </c>
       <c r="R40" s="15">
-        <v>33</v>
+        <v>38.200000000000003</v>
       </c>
       <c r="S40" s="15">
-        <f>R40-Q40</f>
-        <v>1</v>
+        <f t="shared" si="7"/>
+        <v>8.4000000000000021</v>
       </c>
       <c r="T40" s="15">
-        <f>(Q40+R40)/2</f>
-        <v>32.5</v>
+        <f t="shared" si="4"/>
+        <v>34</v>
       </c>
       <c r="Y40" s="9" t="s">
-        <v>269</v>
-      </c>
-      <c r="AB40" s="24" t="s">
-        <v>96</v>
+        <v>876</v>
+      </c>
+      <c r="Z40" s="16">
+        <v>180</v>
+      </c>
+      <c r="AA40" s="16">
+        <v>230</v>
+      </c>
+      <c r="AB40" s="9" t="s">
+        <v>112</v>
       </c>
       <c r="AC40" s="9" t="s">
-        <v>898</v>
+        <v>77</v>
       </c>
       <c r="AD40" s="9" t="s">
-        <v>899</v>
+        <v>877</v>
       </c>
       <c r="AE40" s="10">
         <v>2022</v>
       </c>
       <c r="AF40" s="9" t="s">
-        <v>900</v>
+        <v>425</v>
       </c>
       <c r="AG40" s="9" t="s">
         <v>80</v>
       </c>
       <c r="AH40" s="9" t="s">
-        <v>901</v>
+        <v>878</v>
       </c>
       <c r="AI40" s="9" t="s">
         <v>258</v>
@@ -12819,76 +12742,76 @@
         <v>879</v>
       </c>
       <c r="AL40" s="9" t="s">
-        <v>902</v>
+        <v>880</v>
       </c>
       <c r="AM40" s="9" t="s">
-        <v>903</v>
+        <v>881</v>
       </c>
       <c r="AN40" s="9" t="s">
-        <v>808</v>
+        <v>882</v>
       </c>
       <c r="AO40" s="9" t="s">
-        <v>809</v>
+        <v>883</v>
       </c>
       <c r="AP40" s="9" t="s">
-        <v>809</v>
+        <v>883</v>
       </c>
       <c r="AQ40" s="9" t="s">
-        <v>904</v>
+        <v>884</v>
       </c>
       <c r="AR40" s="9" t="s">
-        <v>811</v>
+        <v>884</v>
       </c>
       <c r="AS40" s="9" t="s">
-        <v>905</v>
-      </c>
-      <c r="AT40" s="18">
-        <v>0.32100000000000001</v>
+        <v>885</v>
+      </c>
+      <c r="AT40" s="9" t="s">
+        <v>886</v>
       </c>
       <c r="AU40" s="18">
-        <v>0.32100000000000001</v>
+        <v>0.33129999999999998</v>
       </c>
       <c r="AV40" s="9" t="s">
-        <v>906</v>
+        <v>887</v>
       </c>
       <c r="AW40" s="9">
-        <v>124</v>
+        <v>173</v>
       </c>
       <c r="AX40" s="9">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="AY40" s="18">
-        <v>0.51349999999999996</v>
+        <v>0.46150000000000002</v>
       </c>
       <c r="AZ40" s="18">
-        <v>0.51349999999999996</v>
-      </c>
-      <c r="BA40" s="20" t="s">
-        <v>907</v>
-      </c>
-      <c r="BB40" s="20">
-        <v>14</v>
+        <v>0.46150000000000002</v>
+      </c>
+      <c r="BA40" s="9" t="s">
+        <v>888</v>
+      </c>
+      <c r="BB40" s="9">
+        <v>15</v>
       </c>
       <c r="BC40" s="9" t="s">
-        <v>908</v>
+        <v>889</v>
       </c>
       <c r="BD40" s="9" t="s">
-        <v>269</v>
+        <v>96</v>
       </c>
       <c r="BE40" s="11" t="s">
-        <v>436</v>
+        <v>890</v>
       </c>
       <c r="BF40" s="19">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="BG40" s="9" t="s">
         <v>98</v>
       </c>
       <c r="BH40" s="9" t="s">
-        <v>909</v>
+        <v>891</v>
       </c>
       <c r="BI40" s="9">
-        <v>595.29</v>
+        <v>1030.74</v>
       </c>
       <c r="BJ40" s="9" t="s">
         <v>100</v>
@@ -12903,10 +12826,10 @@
         <v>102</v>
       </c>
       <c r="BN40" s="9" t="s">
-        <v>910</v>
+        <v>892</v>
       </c>
       <c r="BO40" s="9" t="s">
-        <v>911</v>
+        <v>893</v>
       </c>
       <c r="BP40" s="9" t="s">
         <v>102</v>
@@ -12917,57 +12840,69 @@
     </row>
     <row r="41" spans="1:69">
       <c r="A41" s="10">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B41" s="11" t="s">
         <v>663</v>
       </c>
       <c r="C41" s="9" t="s">
-        <v>912</v>
+        <v>894</v>
       </c>
       <c r="D41" s="12" t="str">
-        <f>CONCATENATE(A41," ",C41)</f>
-        <v>414 合謙學</v>
+        <f t="shared" si="0"/>
+        <v>413 頤昌璞岳</v>
       </c>
       <c r="E41" s="12" t="s">
-        <v>913</v>
+        <v>895</v>
       </c>
       <c r="F41" s="13" t="s">
-        <v>914</v>
+        <v>896</v>
+      </c>
+      <c r="G41" s="14">
+        <v>27.11</v>
+      </c>
+      <c r="H41" s="13">
+        <v>26.83</v>
+      </c>
+      <c r="I41" s="14">
+        <v>34.42</v>
+      </c>
+      <c r="J41" s="14">
+        <v>24.79</v>
       </c>
       <c r="K41" s="9" t="s">
-        <v>750</v>
+        <v>897</v>
       </c>
       <c r="L41" s="15">
         <v>32</v>
       </c>
       <c r="M41" s="15">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="N41" s="15">
-        <f>(L41+M41)/2</f>
-        <v>33.5</v>
+        <f t="shared" si="5"/>
+        <v>32.5</v>
       </c>
       <c r="O41" s="15">
-        <f>M41-N41</f>
-        <v>1.5</v>
+        <f t="shared" si="6"/>
+        <v>0.5</v>
       </c>
       <c r="P41" s="9" t="s">
-        <v>915</v>
+        <v>897</v>
       </c>
       <c r="Q41" s="15">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="R41" s="15">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="S41" s="15">
-        <f>R41-Q41</f>
-        <v>7</v>
+        <f t="shared" si="7"/>
+        <v>1</v>
       </c>
       <c r="T41" s="15">
-        <f>(Q41+R41)/2</f>
-        <v>38.5</v>
+        <f t="shared" si="4"/>
+        <v>32.5</v>
       </c>
       <c r="Y41" s="9" t="s">
         <v>269</v>
@@ -12976,22 +12911,22 @@
         <v>96</v>
       </c>
       <c r="AC41" s="9" t="s">
-        <v>77</v>
+        <v>898</v>
       </c>
       <c r="AD41" s="9" t="s">
-        <v>424</v>
+        <v>899</v>
       </c>
       <c r="AE41" s="10">
         <v>2022</v>
       </c>
       <c r="AF41" s="9" t="s">
-        <v>425</v>
+        <v>900</v>
       </c>
       <c r="AG41" s="9" t="s">
         <v>80</v>
       </c>
       <c r="AH41" s="9" t="s">
-        <v>916</v>
+        <v>901</v>
       </c>
       <c r="AI41" s="9" t="s">
         <v>258</v>
@@ -13003,82 +12938,97 @@
         <v>879</v>
       </c>
       <c r="AL41" s="9" t="s">
-        <v>917</v>
+        <v>902</v>
       </c>
       <c r="AM41" s="9" t="s">
-        <v>917</v>
+        <v>903</v>
       </c>
       <c r="AN41" s="9" t="s">
-        <v>918</v>
+        <v>808</v>
       </c>
       <c r="AO41" s="9" t="s">
-        <v>919</v>
+        <v>809</v>
       </c>
       <c r="AP41" s="9" t="s">
-        <v>919</v>
+        <v>809</v>
       </c>
       <c r="AQ41" s="9" t="s">
-        <v>920</v>
+        <v>904</v>
       </c>
       <c r="AR41" s="9" t="s">
-        <v>921</v>
+        <v>811</v>
       </c>
       <c r="AS41" s="9" t="s">
-        <v>922</v>
+        <v>905</v>
       </c>
       <c r="AT41" s="18">
-        <v>0.32500000000000001</v>
+        <v>0.32100000000000001</v>
       </c>
       <c r="AU41" s="18">
-        <v>0.32500000000000001</v>
+        <v>0.32100000000000001</v>
       </c>
       <c r="AV41" s="9" t="s">
-        <v>923</v>
+        <v>906</v>
       </c>
       <c r="AW41" s="9">
-        <v>106</v>
+        <v>124</v>
       </c>
       <c r="AX41" s="9">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AY41" s="18">
-        <v>0.45660000000000001</v>
+        <v>0.51349999999999996</v>
       </c>
       <c r="AZ41" s="18">
-        <v>0.45660000000000001</v>
-      </c>
-      <c r="BA41" s="9" t="s">
+        <v>0.51349999999999996</v>
+      </c>
+      <c r="BA41" s="20" t="s">
         <v>907</v>
       </c>
-      <c r="BB41" s="9">
+      <c r="BB41" s="20">
         <v>14</v>
       </c>
-      <c r="BC41" s="18" t="s">
-        <v>924</v>
+      <c r="BC41" s="9" t="s">
+        <v>908</v>
       </c>
       <c r="BD41" s="9" t="s">
-        <v>925</v>
+        <v>269</v>
       </c>
       <c r="BE41" s="11" t="s">
-        <v>926</v>
+        <v>436</v>
       </c>
       <c r="BF41" s="19">
-        <v>0.91</v>
+        <v>1.01</v>
       </c>
       <c r="BG41" s="9" t="s">
         <v>98</v>
       </c>
       <c r="BH41" s="9" t="s">
-        <v>927</v>
+        <v>909</v>
       </c>
       <c r="BI41" s="9">
-        <v>1030.74</v>
+        <v>595.29</v>
       </c>
       <c r="BJ41" s="9" t="s">
-        <v>928</v>
+        <v>100</v>
       </c>
       <c r="BK41" s="9" t="s">
         <v>867</v>
+      </c>
+      <c r="BL41" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="BM41" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="BN41" s="9" t="s">
+        <v>910</v>
+      </c>
+      <c r="BO41" s="9" t="s">
+        <v>911</v>
+      </c>
+      <c r="BP41" s="9" t="s">
+        <v>102</v>
       </c>
       <c r="BQ41" s="9" t="s">
         <v>134</v>
@@ -13086,99 +13036,81 @@
     </row>
     <row r="42" spans="1:69">
       <c r="A42" s="10">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="B42" s="11" t="s">
         <v>663</v>
       </c>
       <c r="C42" s="9" t="s">
-        <v>929</v>
+        <v>912</v>
       </c>
       <c r="D42" s="12" t="str">
-        <f>CONCATENATE(A42," ",C42)</f>
-        <v>415 大亮時代A7</v>
+        <f t="shared" si="0"/>
+        <v>414 合謙學</v>
       </c>
       <c r="E42" s="12" t="s">
-        <v>930</v>
+        <v>913</v>
       </c>
       <c r="F42" s="13" t="s">
-        <v>931</v>
-      </c>
-      <c r="G42" s="14">
-        <v>29.4</v>
-      </c>
-      <c r="H42" s="13" t="s">
-        <v>932</v>
-      </c>
-      <c r="I42" s="14">
-        <v>34.24</v>
-      </c>
-      <c r="J42" s="14">
-        <v>27.17</v>
+        <v>914</v>
       </c>
       <c r="K42" s="9" t="s">
-        <v>933</v>
+        <v>750</v>
       </c>
       <c r="L42" s="15">
+        <v>32</v>
+      </c>
+      <c r="M42" s="15">
         <v>35</v>
       </c>
-      <c r="M42" s="15">
-        <v>36</v>
-      </c>
       <c r="N42" s="15">
-        <f>(L42+M42)/2</f>
-        <v>35.5</v>
+        <f t="shared" si="5"/>
+        <v>33.5</v>
       </c>
       <c r="O42" s="15">
-        <f>M42-N42</f>
-        <v>0.5</v>
+        <f t="shared" si="6"/>
+        <v>1.5</v>
       </c>
       <c r="P42" s="9" t="s">
-        <v>933</v>
+        <v>915</v>
       </c>
       <c r="Q42" s="15">
         <v>35</v>
       </c>
       <c r="R42" s="15">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="S42" s="15">
-        <f>R42-Q42</f>
-        <v>1</v>
+        <f t="shared" si="7"/>
+        <v>7</v>
       </c>
       <c r="T42" s="15">
-        <f>(Q42+R42)/2</f>
-        <v>35.5</v>
+        <f t="shared" si="4"/>
+        <v>38.5</v>
       </c>
       <c r="Y42" s="9" t="s">
-        <v>934</v>
-      </c>
-      <c r="Z42" s="16">
-        <v>148</v>
-      </c>
-      <c r="AA42" s="16">
-        <v>169</v>
-      </c>
-      <c r="AB42" s="9" t="s">
-        <v>112</v>
+        <v>269</v>
+      </c>
+      <c r="AB42" s="24" t="s">
+        <v>96</v>
       </c>
       <c r="AC42" s="9" t="s">
         <v>77</v>
       </c>
       <c r="AD42" s="9" t="s">
-        <v>935</v>
+        <v>424</v>
       </c>
       <c r="AE42" s="10">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="AF42" s="9" t="s">
-        <v>468</v>
+        <v>425</v>
       </c>
       <c r="AG42" s="9" t="s">
         <v>80</v>
       </c>
       <c r="AH42" s="9" t="s">
-        <v>936</v>
+        <v>916</v>
       </c>
       <c r="AI42" s="9" t="s">
         <v>258</v>
@@ -13187,94 +13119,85 @@
         <v>83</v>
       </c>
       <c r="AK42" s="9" t="s">
-        <v>937</v>
+        <v>879</v>
       </c>
       <c r="AL42" s="9" t="s">
-        <v>938</v>
+        <v>917</v>
       </c>
       <c r="AM42" s="9" t="s">
-        <v>939</v>
+        <v>917</v>
       </c>
       <c r="AN42" s="9" t="s">
-        <v>940</v>
+        <v>918</v>
       </c>
       <c r="AO42" s="9" t="s">
-        <v>941</v>
+        <v>919</v>
       </c>
       <c r="AP42" s="9" t="s">
-        <v>941</v>
+        <v>919</v>
       </c>
       <c r="AQ42" s="9" t="s">
-        <v>942</v>
+        <v>920</v>
       </c>
       <c r="AR42" s="9" t="s">
-        <v>940</v>
+        <v>921</v>
       </c>
       <c r="AS42" s="9" t="s">
-        <v>943</v>
+        <v>922</v>
       </c>
       <c r="AT42" s="18">
-        <v>0.33900000000000002</v>
+        <v>0.32500000000000001</v>
       </c>
       <c r="AU42" s="18">
-        <v>0.33900000000000002</v>
+        <v>0.32500000000000001</v>
       </c>
       <c r="AV42" s="9" t="s">
-        <v>944</v>
+        <v>923</v>
       </c>
       <c r="AW42" s="9">
-        <v>87</v>
+        <v>106</v>
       </c>
       <c r="AX42" s="9">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AY42" s="18">
-        <v>0.50270000000000004</v>
+        <v>0.45660000000000001</v>
       </c>
       <c r="AZ42" s="18">
-        <v>0.50270000000000004</v>
+        <v>0.45660000000000001</v>
       </c>
       <c r="BA42" s="9" t="s">
-        <v>94</v>
+        <v>907</v>
       </c>
       <c r="BB42" s="9">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BC42" s="18" t="s">
-        <v>945</v>
+        <v>924</v>
       </c>
       <c r="BD42" s="9" t="s">
-        <v>946</v>
+        <v>925</v>
       </c>
       <c r="BE42" s="11" t="s">
-        <v>947</v>
+        <v>926</v>
       </c>
       <c r="BF42" s="19">
-        <v>0.36</v>
+        <v>0.91</v>
       </c>
       <c r="BG42" s="9" t="s">
         <v>98</v>
       </c>
       <c r="BH42" s="9" t="s">
-        <v>948</v>
+        <v>927</v>
       </c>
       <c r="BI42" s="9">
-        <v>332.5</v>
+        <v>1030.74</v>
       </c>
       <c r="BJ42" s="9" t="s">
-        <v>259</v>
+        <v>928</v>
       </c>
       <c r="BK42" s="9" t="s">
-        <v>461</v>
-      </c>
-      <c r="BN42" s="9" t="s">
-        <v>949</v>
-      </c>
-      <c r="BO42" s="9" t="s">
-        <v>950</v>
-      </c>
-      <c r="BP42" s="9" t="s">
-        <v>102</v>
+        <v>867</v>
       </c>
       <c r="BQ42" s="9" t="s">
         <v>134</v>
@@ -13282,66 +13205,99 @@
     </row>
     <row r="43" spans="1:69">
       <c r="A43" s="10">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="B43" s="11" t="s">
         <v>663</v>
       </c>
       <c r="C43" s="9" t="s">
-        <v>951</v>
+        <v>929</v>
       </c>
       <c r="D43" s="12" t="str">
-        <f>CONCATENATE(A43," ",C43)</f>
-        <v>416 維特魯威</v>
+        <f t="shared" si="0"/>
+        <v>415 大亮時代A7</v>
       </c>
       <c r="E43" s="12" t="s">
-        <v>952</v>
-      </c>
-      <c r="F43" s="20" t="s">
-        <v>953</v>
-      </c>
-      <c r="G43" s="19">
-        <v>31.65</v>
-      </c>
-      <c r="H43" s="9" t="s">
-        <v>954</v>
-      </c>
-      <c r="I43" s="19">
-        <v>38.68</v>
-      </c>
-      <c r="J43" s="19">
-        <v>27.48</v>
-      </c>
-      <c r="P43" s="15" t="s">
-        <v>955</v>
+        <v>930</v>
+      </c>
+      <c r="F43" s="13" t="s">
+        <v>931</v>
+      </c>
+      <c r="G43" s="14">
+        <v>29.4</v>
+      </c>
+      <c r="H43" s="13" t="s">
+        <v>932</v>
+      </c>
+      <c r="I43" s="14">
+        <v>34.24</v>
+      </c>
+      <c r="J43" s="14">
+        <v>27.17</v>
+      </c>
+      <c r="K43" s="9" t="s">
+        <v>933</v>
+      </c>
+      <c r="L43" s="15">
+        <v>35</v>
+      </c>
+      <c r="M43" s="15">
+        <v>36</v>
+      </c>
+      <c r="N43" s="15">
+        <f t="shared" si="5"/>
+        <v>35.5</v>
+      </c>
+      <c r="O43" s="15">
+        <f t="shared" si="6"/>
+        <v>0.5</v>
+      </c>
+      <c r="P43" s="9" t="s">
+        <v>933</v>
       </c>
       <c r="Q43" s="15">
-        <v>37.799999999999997</v>
+        <v>35</v>
       </c>
       <c r="R43" s="15">
-        <v>45.5</v>
+        <v>36</v>
+      </c>
+      <c r="S43" s="15">
+        <f t="shared" si="7"/>
+        <v>1</v>
       </c>
       <c r="T43" s="15">
-        <f>(Q43+R43)/2</f>
-        <v>41.65</v>
+        <f t="shared" si="4"/>
+        <v>35.5</v>
+      </c>
+      <c r="Y43" s="9" t="s">
+        <v>934</v>
+      </c>
+      <c r="Z43" s="16">
+        <v>148</v>
+      </c>
+      <c r="AA43" s="16">
+        <v>169</v>
+      </c>
+      <c r="AB43" s="9" t="s">
+        <v>112</v>
       </c>
       <c r="AC43" s="9" t="s">
         <v>77</v>
       </c>
       <c r="AD43" s="9" t="s">
-        <v>956</v>
+        <v>935</v>
       </c>
       <c r="AE43" s="10">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="AF43" s="9" t="s">
-        <v>957</v>
+        <v>468</v>
       </c>
       <c r="AG43" s="9" t="s">
         <v>80</v>
       </c>
       <c r="AH43" s="9" t="s">
-        <v>958</v>
+        <v>936</v>
       </c>
       <c r="AI43" s="9" t="s">
         <v>258</v>
@@ -13350,88 +13306,94 @@
         <v>83</v>
       </c>
       <c r="AK43" s="9" t="s">
-        <v>259</v>
+        <v>937</v>
       </c>
       <c r="AL43" s="9" t="s">
-        <v>959</v>
+        <v>938</v>
       </c>
       <c r="AM43" s="9" t="s">
-        <v>960</v>
+        <v>939</v>
       </c>
       <c r="AN43" s="9" t="s">
-        <v>961</v>
+        <v>940</v>
       </c>
       <c r="AO43" s="9" t="s">
-        <v>962</v>
+        <v>941</v>
       </c>
       <c r="AP43" s="9" t="s">
-        <v>962</v>
+        <v>941</v>
       </c>
       <c r="AQ43" s="9" t="s">
-        <v>963</v>
+        <v>942</v>
       </c>
       <c r="AR43" s="9" t="s">
-        <v>964</v>
+        <v>940</v>
+      </c>
+      <c r="AS43" s="9" t="s">
+        <v>943</v>
       </c>
       <c r="AT43" s="18">
-        <v>0.33400000000000002</v>
+        <v>0.33900000000000002</v>
       </c>
       <c r="AU43" s="18">
-        <v>0.33400000000000002</v>
+        <v>0.33900000000000002</v>
       </c>
       <c r="AV43" s="9" t="s">
-        <v>965</v>
+        <v>944</v>
       </c>
       <c r="AW43" s="9">
-        <v>123</v>
+        <v>87</v>
       </c>
       <c r="AX43" s="9">
         <v>3</v>
       </c>
       <c r="AY43" s="18">
-        <v>0.37569999999999998</v>
-      </c>
-      <c r="AZ43" s="18" t="s">
-        <v>966</v>
+        <v>0.50270000000000004</v>
+      </c>
+      <c r="AZ43" s="18">
+        <v>0.50270000000000004</v>
       </c>
       <c r="BA43" s="9" t="s">
-        <v>967</v>
+        <v>94</v>
       </c>
       <c r="BB43" s="9">
-        <v>28</v>
-      </c>
-      <c r="BC43" s="9" t="s">
-        <v>968</v>
+        <v>15</v>
+      </c>
+      <c r="BC43" s="18" t="s">
+        <v>945</v>
       </c>
       <c r="BD43" s="9" t="s">
-        <v>969</v>
+        <v>946</v>
       </c>
       <c r="BE43" s="11" t="s">
-        <v>970</v>
+        <v>947</v>
       </c>
       <c r="BF43" s="19">
-        <v>1.02</v>
+        <v>0.36</v>
       </c>
       <c r="BG43" s="9" t="s">
-        <v>271</v>
+        <v>98</v>
       </c>
       <c r="BH43" s="9" t="s">
-        <v>971</v>
-      </c>
-      <c r="BI43" s="19">
-        <v>586.6</v>
+        <v>948</v>
+      </c>
+      <c r="BI43" s="9">
+        <v>332.5</v>
       </c>
       <c r="BJ43" s="9" t="s">
-        <v>100</v>
+        <v>259</v>
       </c>
       <c r="BK43" s="9" t="s">
-        <v>414</v>
+        <v>461</v>
       </c>
       <c r="BN43" s="9" t="s">
-        <v>972</v>
+        <v>949</v>
       </c>
       <c r="BO43" s="9" t="s">
-        <v>369</v>
+        <v>950</v>
+      </c>
+      <c r="BP43" s="9" t="s">
+        <v>102</v>
       </c>
       <c r="BQ43" s="9" t="s">
         <v>134</v>
@@ -13439,72 +13401,66 @@
     </row>
     <row r="44" spans="1:69">
       <c r="A44" s="10">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="B44" s="11" t="s">
         <v>663</v>
       </c>
       <c r="C44" s="9" t="s">
-        <v>973</v>
+        <v>951</v>
       </c>
       <c r="D44" s="12" t="str">
-        <f>CONCATENATE(A44," ",C44)</f>
-        <v>417 頤昌澄岳</v>
-      </c>
-      <c r="E44" s="9" t="s">
-        <v>974</v>
+        <f t="shared" si="0"/>
+        <v>416 維特魯威</v>
+      </c>
+      <c r="E44" s="12" t="s">
+        <v>952</v>
       </c>
       <c r="F44" s="20" t="s">
-        <v>975</v>
-      </c>
-      <c r="H44" s="22">
-        <v>25.41</v>
+        <v>953</v>
+      </c>
+      <c r="G44" s="19">
+        <v>31.65</v>
+      </c>
+      <c r="H44" s="9" t="s">
+        <v>954</v>
       </c>
       <c r="I44" s="19">
-        <v>25.92</v>
+        <v>38.68</v>
       </c>
       <c r="J44" s="19">
-        <v>25.06</v>
+        <v>27.48</v>
       </c>
       <c r="P44" s="15" t="s">
-        <v>976</v>
+        <v>955</v>
       </c>
       <c r="Q44" s="15">
-        <v>39</v>
+        <v>37.799999999999997</v>
       </c>
       <c r="R44" s="15">
-        <v>40</v>
+        <v>45.5</v>
       </c>
       <c r="T44" s="15">
-        <f>(Q44+R44)/2</f>
-        <v>39.5</v>
-      </c>
-      <c r="Y44" s="9" t="s">
-        <v>977</v>
-      </c>
-      <c r="Z44" s="16">
-        <v>175</v>
-      </c>
-      <c r="AA44" s="16">
-        <v>210</v>
+        <f t="shared" si="4"/>
+        <v>41.65</v>
       </c>
       <c r="AC44" s="9" t="s">
         <v>77</v>
       </c>
       <c r="AD44" s="9" t="s">
-        <v>650</v>
+        <v>956</v>
       </c>
       <c r="AE44" s="10">
         <v>2024</v>
       </c>
       <c r="AF44" s="9" t="s">
-        <v>651</v>
+        <v>957</v>
       </c>
       <c r="AG44" s="9" t="s">
         <v>80</v>
       </c>
       <c r="AH44" s="9" t="s">
-        <v>978</v>
+        <v>958</v>
       </c>
       <c r="AI44" s="9" t="s">
         <v>258</v>
@@ -13516,85 +13472,85 @@
         <v>259</v>
       </c>
       <c r="AL44" s="9" t="s">
-        <v>979</v>
+        <v>959</v>
       </c>
       <c r="AM44" s="9" t="s">
-        <v>980</v>
+        <v>960</v>
       </c>
       <c r="AN44" s="9" t="s">
-        <v>808</v>
+        <v>961</v>
       </c>
       <c r="AO44" s="9" t="s">
-        <v>809</v>
+        <v>962</v>
       </c>
       <c r="AP44" s="9" t="s">
-        <v>809</v>
+        <v>962</v>
       </c>
       <c r="AQ44" s="9" t="s">
-        <v>904</v>
+        <v>963</v>
       </c>
       <c r="AR44" s="9" t="s">
-        <v>361</v>
+        <v>964</v>
       </c>
       <c r="AT44" s="18">
-        <v>0.33</v>
+        <v>0.33400000000000002</v>
       </c>
       <c r="AU44" s="18">
-        <v>0.33</v>
+        <v>0.33400000000000002</v>
       </c>
       <c r="AV44" s="9" t="s">
-        <v>981</v>
+        <v>965</v>
       </c>
       <c r="AW44" s="9">
-        <v>140</v>
+        <v>123</v>
       </c>
       <c r="AX44" s="9">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="AY44" s="18">
-        <v>0.38429999999999997</v>
+        <v>0.37569999999999998</v>
       </c>
       <c r="AZ44" s="18">
-        <v>0.38429999999999997</v>
+        <v>0.37569999999999998</v>
       </c>
       <c r="BA44" s="9" t="s">
-        <v>94</v>
+        <v>966</v>
       </c>
       <c r="BB44" s="9">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="BC44" s="9" t="s">
-        <v>982</v>
+        <v>967</v>
       </c>
       <c r="BD44" s="9" t="s">
-        <v>269</v>
+        <v>968</v>
       </c>
       <c r="BE44" s="11" t="s">
-        <v>983</v>
+        <v>969</v>
       </c>
       <c r="BF44" s="19">
-        <v>0.97</v>
+        <v>1.02</v>
       </c>
       <c r="BG44" s="9" t="s">
         <v>271</v>
       </c>
       <c r="BH44" s="9" t="s">
-        <v>984</v>
+        <v>970</v>
       </c>
       <c r="BI44" s="19">
-        <v>665.31</v>
+        <v>586.6</v>
       </c>
       <c r="BJ44" s="9" t="s">
         <v>100</v>
       </c>
       <c r="BK44" s="9" t="s">
-        <v>367</v>
+        <v>414</v>
       </c>
       <c r="BN44" s="9" t="s">
-        <v>985</v>
+        <v>971</v>
       </c>
       <c r="BO44" s="9" t="s">
-        <v>819</v>
+        <v>369</v>
       </c>
       <c r="BQ44" s="9" t="s">
         <v>134</v>
@@ -13602,99 +13558,72 @@
     </row>
     <row r="45" spans="1:69">
       <c r="A45" s="10">
-        <v>501</v>
+        <v>417</v>
       </c>
       <c r="B45" s="11" t="s">
-        <v>986</v>
+        <v>663</v>
       </c>
       <c r="C45" s="9" t="s">
-        <v>987</v>
+        <v>972</v>
       </c>
       <c r="D45" s="12" t="str">
-        <f>CONCATENATE(A45," ",C45)</f>
-        <v>501 新未來1</v>
-      </c>
-      <c r="E45" s="12" t="s">
-        <v>988</v>
+        <f t="shared" si="0"/>
+        <v>417 頤昌澄岳</v>
+      </c>
+      <c r="E45" s="9" t="s">
+        <v>973</v>
       </c>
       <c r="F45" s="20" t="s">
-        <v>989</v>
-      </c>
-      <c r="G45" s="14">
-        <v>34.36</v>
-      </c>
-      <c r="H45" s="13">
-        <v>30.58</v>
-      </c>
-      <c r="I45" s="14">
-        <v>37.549999999999997</v>
-      </c>
-      <c r="J45" s="14">
-        <v>26.75</v>
-      </c>
-      <c r="K45" s="9" t="s">
-        <v>841</v>
-      </c>
-      <c r="L45" s="15">
-        <v>33</v>
-      </c>
-      <c r="M45" s="15">
-        <v>38</v>
-      </c>
-      <c r="N45" s="15">
-        <f>(L45+M45)/2</f>
-        <v>35.5</v>
-      </c>
-      <c r="O45" s="15">
-        <f>M45-N45</f>
-        <v>2.5</v>
-      </c>
-      <c r="P45" s="9" t="s">
-        <v>841</v>
+        <v>974</v>
+      </c>
+      <c r="H45" s="22">
+        <v>25.41</v>
+      </c>
+      <c r="I45" s="19">
+        <v>25.92</v>
+      </c>
+      <c r="J45" s="19">
+        <v>25.06</v>
+      </c>
+      <c r="P45" s="15" t="s">
+        <v>975</v>
       </c>
       <c r="Q45" s="15">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="R45" s="15">
-        <v>38</v>
-      </c>
-      <c r="S45" s="15">
-        <f>R45-Q45</f>
-        <v>5</v>
+        <v>40</v>
       </c>
       <c r="T45" s="15">
-        <f>(Q45+R45)/2</f>
-        <v>35.5</v>
-      </c>
-      <c r="U45" s="15" t="s">
-        <v>138</v>
-      </c>
-      <c r="V45" s="9" t="s">
-        <v>990</v>
-      </c>
-      <c r="W45" s="9" t="s">
-        <v>991</v>
-      </c>
-      <c r="AB45" s="9" t="s">
-        <v>112</v>
+        <f t="shared" si="4"/>
+        <v>39.5</v>
+      </c>
+      <c r="Y45" s="9" t="s">
+        <v>976</v>
+      </c>
+      <c r="Z45" s="16">
+        <v>175</v>
+      </c>
+      <c r="AA45" s="16">
+        <v>210</v>
       </c>
       <c r="AC45" s="9" t="s">
-        <v>898</v>
+        <v>77</v>
       </c>
       <c r="AD45" s="9" t="s">
-        <v>550</v>
+        <v>650</v>
       </c>
       <c r="AE45" s="10">
-        <v>2021</v>
+        <v>2024</v>
       </c>
       <c r="AF45" s="9" t="s">
-        <v>212</v>
+        <v>651</v>
       </c>
       <c r="AG45" s="9" t="s">
         <v>80</v>
       </c>
       <c r="AH45" s="9" t="s">
-        <v>992</v>
+        <v>977</v>
       </c>
       <c r="AI45" s="9" t="s">
         <v>258</v>
@@ -13703,192 +13632,163 @@
         <v>83</v>
       </c>
       <c r="AK45" s="9" t="s">
-        <v>117</v>
+        <v>259</v>
       </c>
       <c r="AL45" s="9" t="s">
-        <v>828</v>
+        <v>978</v>
       </c>
       <c r="AM45" s="9" t="s">
-        <v>828</v>
+        <v>979</v>
       </c>
       <c r="AN45" s="9" t="s">
-        <v>829</v>
+        <v>808</v>
       </c>
       <c r="AO45" s="9" t="s">
-        <v>830</v>
+        <v>809</v>
       </c>
       <c r="AP45" s="9" t="s">
-        <v>830</v>
+        <v>809</v>
       </c>
       <c r="AQ45" s="9" t="s">
-        <v>993</v>
+        <v>904</v>
       </c>
       <c r="AR45" s="9" t="s">
-        <v>994</v>
-      </c>
-      <c r="AS45" s="9" t="s">
-        <v>617</v>
-      </c>
-      <c r="AT45" s="17">
+        <v>361</v>
+      </c>
+      <c r="AT45" s="18">
         <v>0.33</v>
       </c>
       <c r="AU45" s="18">
         <v>0.33</v>
       </c>
       <c r="AV45" s="9" t="s">
-        <v>995</v>
+        <v>980</v>
       </c>
       <c r="AW45" s="9">
-        <v>807</v>
+        <v>140</v>
       </c>
       <c r="AX45" s="9">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="AY45" s="18">
-        <v>0.57020000000000004</v>
+        <v>0.38429999999999997</v>
       </c>
       <c r="AZ45" s="18">
-        <v>0.57020000000000004</v>
+        <v>0.38429999999999997</v>
       </c>
       <c r="BA45" s="9" t="s">
-        <v>967</v>
+        <v>94</v>
       </c>
       <c r="BB45" s="9">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="BC45" s="9" t="s">
-        <v>996</v>
+        <v>981</v>
       </c>
       <c r="BD45" s="9" t="s">
-        <v>969</v>
+        <v>269</v>
       </c>
       <c r="BE45" s="11" t="s">
-        <v>997</v>
+        <v>982</v>
       </c>
       <c r="BF45" s="19">
-        <v>0.89</v>
+        <v>0.97</v>
       </c>
       <c r="BG45" s="9" t="s">
-        <v>98</v>
+        <v>271</v>
       </c>
       <c r="BH45" s="9" t="s">
-        <v>998</v>
-      </c>
-      <c r="BI45" s="9">
-        <v>2890</v>
+        <v>983</v>
+      </c>
+      <c r="BI45" s="19">
+        <v>665.31</v>
       </c>
       <c r="BJ45" s="9" t="s">
         <v>100</v>
       </c>
       <c r="BK45" s="9" t="s">
-        <v>461</v>
-      </c>
-      <c r="BL45" s="9" t="s">
-        <v>102</v>
-      </c>
-      <c r="BM45" s="9" t="s">
-        <v>102</v>
+        <v>367</v>
       </c>
       <c r="BN45" s="9" t="s">
-        <v>999</v>
+        <v>984</v>
       </c>
       <c r="BO45" s="9" t="s">
-        <v>1000</v>
-      </c>
-      <c r="BP45" s="9" t="s">
-        <v>102</v>
+        <v>819</v>
       </c>
       <c r="BQ45" s="9" t="s">
-        <v>1001</v>
+        <v>134</v>
       </c>
     </row>
-    <row r="46" spans="1:69" ht="16">
+    <row r="46" spans="1:69">
       <c r="A46" s="10">
-        <v>502</v>
+        <v>418</v>
       </c>
       <c r="B46" s="11" t="s">
-        <v>986</v>
-      </c>
-      <c r="C46" s="23" t="s">
-        <v>1002</v>
+        <v>663</v>
+      </c>
+      <c r="C46" s="9" t="s">
+        <v>1123</v>
       </c>
       <c r="D46" s="12" t="str">
-        <f>CONCATENATE(A46," ",C46)</f>
-        <v>502 富宇天匯</v>
+        <f t="shared" si="0"/>
+        <v>418 玄泰T1</v>
       </c>
       <c r="E46" s="12" t="s">
-        <v>1003</v>
+        <v>1124</v>
       </c>
       <c r="F46" s="20" t="s">
-        <v>1004</v>
-      </c>
-      <c r="G46" s="21"/>
-      <c r="H46" s="22"/>
-      <c r="I46" s="21"/>
-      <c r="J46" s="21"/>
-      <c r="K46" s="9" t="s">
-        <v>1005</v>
-      </c>
-      <c r="L46" s="15">
-        <v>39</v>
-      </c>
-      <c r="M46" s="15">
-        <v>43</v>
-      </c>
-      <c r="N46" s="15">
-        <f>(L46+M46)/2</f>
-        <v>41</v>
-      </c>
-      <c r="O46" s="15">
-        <f>M46-N46</f>
-        <v>2</v>
+        <v>1125</v>
+      </c>
+      <c r="G46" s="19">
+        <v>27.3</v>
+      </c>
+      <c r="H46" s="22" t="s">
+        <v>1126</v>
+      </c>
+      <c r="I46" s="19">
+        <v>36.26</v>
+      </c>
+      <c r="J46" s="19">
+        <v>21.25</v>
       </c>
       <c r="P46" s="9" t="s">
-        <v>1006</v>
+        <v>1127</v>
       </c>
       <c r="Q46" s="15">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="R46" s="15">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="S46" s="15">
-        <f>R46-Q46</f>
-        <v>5</v>
-      </c>
-      <c r="T46" s="15">
-        <f>(Q46+R46)/2</f>
-        <v>47.5</v>
+        <v>36</v>
       </c>
       <c r="Y46" s="9" t="s">
-        <v>1007</v>
+        <v>1128</v>
       </c>
       <c r="Z46" s="16">
         <v>160</v>
       </c>
       <c r="AA46" s="16">
-        <v>205</v>
-      </c>
-      <c r="AB46" s="9" t="s">
-        <v>112</v>
+        <v>230</v>
       </c>
       <c r="AC46" s="9" t="s">
         <v>77</v>
       </c>
       <c r="AD46" s="9" t="s">
-        <v>1008</v>
+        <v>1129</v>
       </c>
       <c r="AE46" s="10">
-        <v>2023</v>
+        <v>2026</v>
       </c>
       <c r="AF46" s="9" t="s">
-        <v>1009</v>
+        <v>1130</v>
       </c>
       <c r="AG46" s="9" t="s">
         <v>80</v>
       </c>
       <c r="AH46" s="9" t="s">
-        <v>1010</v>
+        <v>1131</v>
       </c>
       <c r="AI46" s="9" t="s">
         <v>258</v>
@@ -13897,197 +13797,188 @@
         <v>83</v>
       </c>
       <c r="AK46" s="9" t="s">
-        <v>117</v>
+        <v>259</v>
       </c>
       <c r="AL46" s="9" t="s">
-        <v>1011</v>
+        <v>1132</v>
       </c>
       <c r="AM46" s="9" t="s">
-        <v>1012</v>
+        <v>1133</v>
       </c>
       <c r="AN46" s="9" t="s">
-        <v>1013</v>
+        <v>1134</v>
       </c>
       <c r="AO46" s="9" t="s">
-        <v>1014</v>
+        <v>1135</v>
       </c>
       <c r="AP46" s="9" t="s">
-        <v>289</v>
+        <v>1135</v>
       </c>
       <c r="AQ46" s="9" t="s">
-        <v>1015</v>
+        <v>1136</v>
       </c>
       <c r="AR46" s="9" t="s">
-        <v>1016</v>
-      </c>
-      <c r="AS46" s="9" t="s">
-        <v>617</v>
+        <v>1137</v>
       </c>
       <c r="AT46" s="18">
-        <v>0.33500000000000002</v>
+        <v>0.33</v>
       </c>
       <c r="AU46" s="18">
-        <v>0.33500000000000002</v>
+        <v>0.33</v>
       </c>
       <c r="AV46" s="9" t="s">
-        <v>1017</v>
+        <v>1138</v>
       </c>
       <c r="AW46" s="9">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="AX46" s="9">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AY46" s="18">
-        <v>0.49540000000000001</v>
+        <v>0.59189999999999998</v>
       </c>
       <c r="AZ46" s="18">
-        <v>0.49540000000000001</v>
+        <v>0.59189999999999998</v>
       </c>
       <c r="BA46" s="9" t="s">
-        <v>94</v>
+        <v>1139</v>
       </c>
       <c r="BB46" s="9">
-        <v>15</v>
-      </c>
-      <c r="BC46" s="18" t="s">
-        <v>1018</v>
+        <v>25</v>
+      </c>
+      <c r="BC46" s="9" t="s">
+        <v>1140</v>
       </c>
       <c r="BD46" s="9" t="s">
-        <v>925</v>
+        <v>459</v>
       </c>
       <c r="BE46" s="11" t="s">
-        <v>1019</v>
+        <v>155</v>
       </c>
       <c r="BF46" s="19">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="BG46" s="9" t="s">
-        <v>98</v>
+        <v>271</v>
       </c>
       <c r="BH46" s="9" t="s">
-        <v>1020</v>
-      </c>
-      <c r="BI46" s="9">
-        <v>1471.38</v>
+        <v>1141</v>
+      </c>
+      <c r="BI46" s="19">
+        <v>1848.19</v>
       </c>
       <c r="BJ46" s="9" t="s">
         <v>100</v>
       </c>
       <c r="BK46" s="9" t="s">
-        <v>817</v>
-      </c>
-      <c r="BL46" s="9" t="s">
-        <v>102</v>
-      </c>
-      <c r="BM46" s="9" t="s">
-        <v>102</v>
+        <v>414</v>
       </c>
       <c r="BN46" s="9" t="s">
-        <v>1021</v>
-      </c>
-      <c r="BO46" s="9" t="s">
-        <v>1022</v>
-      </c>
-      <c r="BP46" s="9" t="s">
-        <v>102</v>
+        <v>1142</v>
       </c>
       <c r="BQ46" s="9" t="s">
-        <v>1001</v>
+        <v>134</v>
       </c>
     </row>
     <row r="47" spans="1:69">
       <c r="A47" s="10">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="B47" s="11" t="s">
+        <v>985</v>
+      </c>
+      <c r="C47" s="9" t="s">
         <v>986</v>
       </c>
-      <c r="C47" s="9" t="s">
-        <v>1023</v>
-      </c>
       <c r="D47" s="12" t="str">
-        <f>CONCATENATE(A47," ",C47)</f>
-        <v>503 竹城明治</v>
+        <f t="shared" si="0"/>
+        <v>501 新未來1</v>
       </c>
       <c r="E47" s="12" t="s">
-        <v>1024</v>
-      </c>
-      <c r="F47" s="13" t="s">
-        <v>1025</v>
+        <v>987</v>
+      </c>
+      <c r="F47" s="20" t="s">
+        <v>988</v>
       </c>
       <c r="G47" s="14">
-        <v>26.56</v>
+        <v>34.36</v>
       </c>
       <c r="H47" s="13">
-        <v>26.09</v>
+        <v>30.58</v>
       </c>
       <c r="I47" s="14">
-        <v>33.130000000000003</v>
+        <v>37.549999999999997</v>
       </c>
       <c r="J47" s="14">
-        <v>22.2</v>
+        <v>26.75</v>
       </c>
       <c r="K47" s="9" t="s">
-        <v>1026</v>
+        <v>841</v>
       </c>
       <c r="L47" s="15">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="M47" s="15">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="N47" s="15">
         <f>(L47+M47)/2</f>
-        <v>29</v>
+        <v>35.5</v>
       </c>
       <c r="O47" s="15">
         <f>M47-N47</f>
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="P47" s="9" t="s">
-        <v>1026</v>
+        <v>841</v>
       </c>
       <c r="Q47" s="15">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="R47" s="15">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="S47" s="15">
         <f>R47-Q47</f>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T47" s="15">
-        <f>(Q47+R47)/2</f>
-        <v>29</v>
+        <f t="shared" si="4"/>
+        <v>35.5</v>
       </c>
       <c r="U47" s="15" t="s">
         <v>138</v>
       </c>
+      <c r="V47" s="9" t="s">
+        <v>989</v>
+      </c>
+      <c r="W47" s="9" t="s">
+        <v>990</v>
+      </c>
       <c r="AB47" s="9" t="s">
         <v>112</v>
       </c>
       <c r="AC47" s="9" t="s">
-        <v>77</v>
+        <v>898</v>
       </c>
       <c r="AD47" s="9" t="s">
-        <v>143</v>
+        <v>550</v>
       </c>
       <c r="AE47" s="10">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="AF47" s="9" t="s">
-        <v>1027</v>
+        <v>212</v>
       </c>
       <c r="AG47" s="9" t="s">
         <v>80</v>
       </c>
       <c r="AH47" s="9" t="s">
-        <v>1028</v>
+        <v>991</v>
       </c>
       <c r="AI47" s="9" t="s">
-        <v>146</v>
+        <v>258</v>
       </c>
       <c r="AJ47" s="9" t="s">
         <v>83</v>
@@ -14096,82 +13987,82 @@
         <v>117</v>
       </c>
       <c r="AL47" s="9" t="s">
-        <v>1029</v>
+        <v>828</v>
       </c>
       <c r="AM47" s="9" t="s">
-        <v>1030</v>
+        <v>828</v>
       </c>
       <c r="AN47" s="9" t="s">
-        <v>674</v>
+        <v>829</v>
       </c>
       <c r="AO47" s="9" t="s">
-        <v>675</v>
+        <v>830</v>
       </c>
       <c r="AP47" s="9" t="s">
-        <v>675</v>
+        <v>830</v>
       </c>
       <c r="AQ47" s="9" t="s">
-        <v>676</v>
+        <v>992</v>
       </c>
       <c r="AR47" s="9" t="s">
-        <v>1031</v>
+        <v>993</v>
       </c>
       <c r="AS47" s="9" t="s">
-        <v>173</v>
+        <v>617</v>
       </c>
       <c r="AT47" s="17">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="AU47" s="18">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="AV47" s="9" t="s">
-        <v>1032</v>
+        <v>994</v>
       </c>
       <c r="AW47" s="9">
-        <v>168</v>
+        <v>807</v>
       </c>
       <c r="AX47" s="9">
-        <v>5</v>
-      </c>
-      <c r="AY47" s="9" t="s">
-        <v>1033</v>
+        <v>14</v>
+      </c>
+      <c r="AY47" s="18">
+        <v>0.57020000000000004</v>
       </c>
       <c r="AZ47" s="18">
-        <v>0.4556</v>
+        <v>0.57020000000000004</v>
       </c>
       <c r="BA47" s="9" t="s">
-        <v>1034</v>
+        <v>966</v>
       </c>
       <c r="BB47" s="9">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="BC47" s="9" t="s">
-        <v>1035</v>
+        <v>995</v>
       </c>
       <c r="BD47" s="9" t="s">
-        <v>96</v>
+        <v>968</v>
       </c>
       <c r="BE47" s="11" t="s">
-        <v>581</v>
+        <v>996</v>
       </c>
       <c r="BF47" s="19">
-        <v>0.86</v>
+        <v>0.89</v>
       </c>
       <c r="BG47" s="9" t="s">
         <v>98</v>
       </c>
       <c r="BH47" s="9" t="s">
-        <v>1036</v>
+        <v>997</v>
       </c>
       <c r="BI47" s="9">
-        <v>961.25</v>
+        <v>2890</v>
       </c>
       <c r="BJ47" s="9" t="s">
         <v>100</v>
       </c>
       <c r="BK47" s="9" t="s">
-        <v>867</v>
+        <v>461</v>
       </c>
       <c r="BL47" s="9" t="s">
         <v>102</v>
@@ -14180,117 +14071,108 @@
         <v>102</v>
       </c>
       <c r="BN47" s="9" t="s">
-        <v>1037</v>
+        <v>998</v>
       </c>
       <c r="BO47" s="9" t="s">
-        <v>584</v>
+        <v>999</v>
       </c>
       <c r="BP47" s="9" t="s">
-        <v>1038</v>
+        <v>102</v>
       </c>
       <c r="BQ47" s="9" t="s">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="48" spans="1:69" ht="16">
+      <c r="A48" s="10">
+        <v>502</v>
+      </c>
+      <c r="B48" s="11" t="s">
+        <v>985</v>
+      </c>
+      <c r="C48" s="23" t="s">
         <v>1001</v>
       </c>
-    </row>
-    <row r="48" spans="1:69" ht="19">
-      <c r="A48" s="10">
-        <v>504</v>
-      </c>
-      <c r="B48" s="11" t="s">
-        <v>986</v>
-      </c>
-      <c r="C48" s="9" t="s">
-        <v>1039</v>
-      </c>
       <c r="D48" s="12" t="str">
-        <f>CONCATENATE(A48," ",C48)</f>
-        <v>504 竹城宇治</v>
+        <f t="shared" si="0"/>
+        <v>502 富宇天匯</v>
       </c>
       <c r="E48" s="12" t="s">
-        <v>1040</v>
-      </c>
-      <c r="F48" s="13" t="s">
-        <v>1041</v>
-      </c>
-      <c r="G48" s="14"/>
-      <c r="H48" s="13">
-        <v>24.13</v>
-      </c>
-      <c r="I48" s="14">
-        <v>29.39</v>
-      </c>
-      <c r="J48" s="14">
-        <v>22.11</v>
-      </c>
+        <v>1002</v>
+      </c>
+      <c r="F48" s="20" t="s">
+        <v>1003</v>
+      </c>
+      <c r="G48" s="21"/>
+      <c r="H48" s="22"/>
+      <c r="I48" s="21"/>
+      <c r="J48" s="21"/>
       <c r="K48" s="9" t="s">
-        <v>1042</v>
+        <v>1004</v>
       </c>
       <c r="L48" s="15">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="M48" s="15">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="N48" s="15">
         <f>(L48+M48)/2</f>
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="O48" s="15">
         <f>M48-N48</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P48" s="9" t="s">
-        <v>1042</v>
+        <v>1005</v>
       </c>
       <c r="Q48" s="15">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="R48" s="15">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="S48" s="15">
         <f>R48-Q48</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="T48" s="15">
-        <f>(Q48+R48)/2</f>
-        <v>30</v>
-      </c>
-      <c r="U48" s="15" t="s">
-        <v>138</v>
+        <f t="shared" si="4"/>
+        <v>47.5</v>
       </c>
       <c r="Y48" s="9" t="s">
-        <v>1043</v>
+        <v>1006</v>
       </c>
       <c r="Z48" s="16">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="AA48" s="16">
-        <v>185</v>
+        <v>205</v>
       </c>
       <c r="AB48" s="9" t="s">
         <v>112</v>
       </c>
       <c r="AC48" s="9" t="s">
-        <v>898</v>
+        <v>77</v>
       </c>
       <c r="AD48" s="9" t="s">
-        <v>143</v>
+        <v>1007</v>
       </c>
       <c r="AE48" s="10">
-        <v>2019</v>
+        <v>2023</v>
       </c>
       <c r="AF48" s="9" t="s">
-        <v>144</v>
+        <v>1008</v>
       </c>
       <c r="AG48" s="9" t="s">
         <v>80</v>
       </c>
       <c r="AH48" s="9" t="s">
-        <v>1044</v>
+        <v>1009</v>
       </c>
       <c r="AI48" s="9" t="s">
-        <v>146</v>
+        <v>258</v>
       </c>
       <c r="AJ48" s="9" t="s">
         <v>83</v>
@@ -14299,203 +14181,194 @@
         <v>117</v>
       </c>
       <c r="AL48" s="9" t="s">
-        <v>1045</v>
+        <v>1010</v>
       </c>
       <c r="AM48" s="9" t="s">
-        <v>1045</v>
+        <v>1011</v>
       </c>
       <c r="AN48" s="9" t="s">
-        <v>1046</v>
+        <v>1012</v>
       </c>
       <c r="AO48" s="9" t="s">
-        <v>675</v>
+        <v>1013</v>
       </c>
       <c r="AP48" s="9" t="s">
-        <v>675</v>
+        <v>289</v>
       </c>
       <c r="AQ48" s="9" t="s">
-        <v>1047</v>
+        <v>1014</v>
       </c>
       <c r="AR48" s="9" t="s">
-        <v>1046</v>
+        <v>1015</v>
       </c>
       <c r="AS48" s="9" t="s">
-        <v>1048</v>
+        <v>617</v>
       </c>
       <c r="AT48" s="18">
-        <v>0.315</v>
+        <v>0.33500000000000002</v>
       </c>
       <c r="AU48" s="18">
-        <v>0.315</v>
+        <v>0.33500000000000002</v>
       </c>
       <c r="AV48" s="9" t="s">
-        <v>1049</v>
+        <v>1016</v>
       </c>
       <c r="AW48" s="9">
-        <v>103</v>
+        <v>266</v>
       </c>
       <c r="AX48" s="9">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AY48" s="18">
-        <v>0.45700000000000002</v>
+        <v>0.49540000000000001</v>
       </c>
       <c r="AZ48" s="18">
-        <v>0.45700000000000002</v>
+        <v>0.49540000000000001</v>
       </c>
       <c r="BA48" s="9" t="s">
-        <v>1050</v>
+        <v>94</v>
       </c>
       <c r="BB48" s="9">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="BC48" s="18" t="s">
-        <v>1051</v>
+        <v>1017</v>
       </c>
       <c r="BD48" s="9" t="s">
-        <v>459</v>
+        <v>925</v>
       </c>
       <c r="BE48" s="11" t="s">
-        <v>1052</v>
+        <v>1018</v>
       </c>
       <c r="BF48" s="19">
-        <v>0.75</v>
+        <v>1.03</v>
       </c>
       <c r="BG48" s="9" t="s">
         <v>98</v>
       </c>
       <c r="BH48" s="9" t="s">
-        <v>1053</v>
+        <v>1019</v>
       </c>
       <c r="BI48" s="9">
-        <v>638.13</v>
+        <v>1471.38</v>
       </c>
       <c r="BJ48" s="9" t="s">
         <v>100</v>
       </c>
       <c r="BK48" s="9" t="s">
-        <v>867</v>
-      </c>
-      <c r="BN48" s="27" t="s">
-        <v>1054</v>
+        <v>817</v>
+      </c>
+      <c r="BL48" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="BM48" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="BN48" s="9" t="s">
+        <v>1020</v>
       </c>
       <c r="BO48" s="9" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="BP48" s="9" t="s">
-        <v>1055</v>
+        <v>102</v>
       </c>
       <c r="BQ48" s="9" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="49" spans="1:69">
       <c r="A49" s="10">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="B49" s="11" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="C49" s="9" t="s">
-        <v>1056</v>
+        <v>1022</v>
       </c>
       <c r="D49" s="12" t="str">
-        <f>CONCATENATE(A49," ",C49)</f>
-        <v>505 櫻花澍</v>
+        <f t="shared" si="0"/>
+        <v>503 竹城明治</v>
       </c>
       <c r="E49" s="12" t="s">
-        <v>1057</v>
-      </c>
-      <c r="F49" s="20" t="s">
-        <v>1058</v>
-      </c>
-      <c r="G49" s="21">
-        <v>26.2</v>
-      </c>
-      <c r="H49" s="22">
+        <v>1023</v>
+      </c>
+      <c r="F49" s="13" t="s">
+        <v>1024</v>
+      </c>
+      <c r="G49" s="14">
+        <v>26.56</v>
+      </c>
+      <c r="H49" s="13">
         <v>26.09</v>
       </c>
-      <c r="I49" s="21">
-        <v>28.35</v>
-      </c>
-      <c r="J49" s="21">
-        <v>24.04</v>
+      <c r="I49" s="14">
+        <v>33.130000000000003</v>
+      </c>
+      <c r="J49" s="14">
+        <v>22.2</v>
       </c>
       <c r="K49" s="9" t="s">
-        <v>1059</v>
+        <v>1025</v>
       </c>
       <c r="L49" s="15">
         <v>28</v>
       </c>
       <c r="M49" s="15">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="N49" s="15">
         <f>(L49+M49)/2</f>
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="O49" s="15">
         <f>M49-N49</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P49" s="9" t="s">
-        <v>1059</v>
+        <v>1025</v>
       </c>
       <c r="Q49" s="15">
         <v>28</v>
       </c>
       <c r="R49" s="15">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="S49" s="15">
         <f>R49-Q49</f>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T49" s="15">
-        <f>(Q49+R49)/2</f>
-        <v>30</v>
+        <f t="shared" si="4"/>
+        <v>29</v>
       </c>
       <c r="U49" s="15" t="s">
         <v>138</v>
       </c>
-      <c r="V49" s="9" t="s">
-        <v>1060</v>
-      </c>
-      <c r="W49" s="20" t="s">
-        <v>1061</v>
-      </c>
-      <c r="Y49" s="9" t="s">
-        <v>1062</v>
-      </c>
-      <c r="Z49" s="16">
-        <v>165</v>
-      </c>
-      <c r="AA49" s="16">
-        <v>195</v>
-      </c>
       <c r="AB49" s="9" t="s">
         <v>112</v>
       </c>
       <c r="AC49" s="9" t="s">
-        <v>898</v>
+        <v>77</v>
       </c>
       <c r="AD49" s="9" t="s">
-        <v>752</v>
+        <v>143</v>
       </c>
       <c r="AE49" s="10">
-        <v>2022</v>
+        <v>2020</v>
       </c>
       <c r="AF49" s="9" t="s">
-        <v>79</v>
+        <v>1026</v>
       </c>
       <c r="AG49" s="9" t="s">
         <v>80</v>
       </c>
       <c r="AH49" s="9" t="s">
-        <v>1063</v>
+        <v>1027</v>
       </c>
       <c r="AI49" s="9" t="s">
-        <v>258</v>
+        <v>146</v>
       </c>
       <c r="AJ49" s="9" t="s">
         <v>83</v>
@@ -14504,28 +14377,28 @@
         <v>117</v>
       </c>
       <c r="AL49" s="9" t="s">
-        <v>1064</v>
+        <v>1028</v>
       </c>
       <c r="AM49" s="9" t="s">
-        <v>1065</v>
+        <v>1029</v>
       </c>
       <c r="AN49" s="9" t="s">
-        <v>1066</v>
+        <v>674</v>
       </c>
       <c r="AO49" s="9" t="s">
-        <v>1067</v>
+        <v>675</v>
       </c>
       <c r="AP49" s="9" t="s">
-        <v>1067</v>
+        <v>675</v>
       </c>
       <c r="AQ49" s="9" t="s">
-        <v>90</v>
+        <v>676</v>
       </c>
       <c r="AR49" s="9" t="s">
-        <v>1068</v>
+        <v>1030</v>
       </c>
       <c r="AS49" s="9" t="s">
-        <v>1069</v>
+        <v>173</v>
       </c>
       <c r="AT49" s="17">
         <v>0.32</v>
@@ -14534,46 +14407,46 @@
         <v>0.32</v>
       </c>
       <c r="AV49" s="9" t="s">
-        <v>1070</v>
+        <v>1031</v>
       </c>
       <c r="AW49" s="9">
-        <v>106</v>
+        <v>168</v>
       </c>
       <c r="AX49" s="9">
-        <v>2</v>
-      </c>
-      <c r="AY49" s="18">
-        <v>0.38140000000000002</v>
+        <v>5</v>
+      </c>
+      <c r="AY49" s="9" t="s">
+        <v>1032</v>
       </c>
       <c r="AZ49" s="18">
-        <v>0.38140000000000002</v>
+        <v>0.4556</v>
       </c>
       <c r="BA49" s="9" t="s">
-        <v>907</v>
+        <v>1033</v>
       </c>
       <c r="BB49" s="9">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BC49" s="9" t="s">
-        <v>1071</v>
+        <v>1034</v>
       </c>
       <c r="BD49" s="9" t="s">
-        <v>1072</v>
+        <v>96</v>
       </c>
       <c r="BE49" s="11" t="s">
-        <v>155</v>
+        <v>581</v>
       </c>
       <c r="BF49" s="19">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="BG49" s="9" t="s">
         <v>98</v>
       </c>
       <c r="BH49" s="9" t="s">
-        <v>1073</v>
+        <v>1035</v>
       </c>
       <c r="BI49" s="9">
-        <v>602.07000000000005</v>
+        <v>961.25</v>
       </c>
       <c r="BJ49" s="9" t="s">
         <v>100</v>
@@ -14581,60 +14454,103 @@
       <c r="BK49" s="9" t="s">
         <v>867</v>
       </c>
+      <c r="BL49" s="9" t="s">
+        <v>102</v>
+      </c>
       <c r="BM49" s="9" t="s">
         <v>102</v>
       </c>
       <c r="BN49" s="9" t="s">
-        <v>1074</v>
+        <v>1036</v>
       </c>
       <c r="BO49" s="9" t="s">
-        <v>764</v>
+        <v>584</v>
       </c>
       <c r="BP49" s="9" t="s">
-        <v>102</v>
+        <v>1037</v>
       </c>
       <c r="BQ49" s="9" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
     </row>
-    <row r="50" spans="1:69">
+    <row r="50" spans="1:69" ht="19">
       <c r="A50" s="10">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="B50" s="11" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="C50" s="9" t="s">
-        <v>1107</v>
+        <v>1038</v>
       </c>
       <c r="D50" s="12" t="str">
-        <f>CONCATENATE(A50," ",C50)</f>
-        <v>506 和煦隆陞</v>
+        <f t="shared" si="0"/>
+        <v>504 竹城宇治</v>
       </c>
       <c r="E50" s="12" t="s">
-        <v>1108</v>
-      </c>
-      <c r="F50" s="20" t="s">
-        <v>1109</v>
-      </c>
-      <c r="G50" s="19">
-        <v>32.270000000000003</v>
-      </c>
-      <c r="H50" s="22">
-        <v>28.56</v>
-      </c>
-      <c r="I50" s="19">
-        <v>33.619999999999997</v>
-      </c>
-      <c r="J50" s="19">
-        <v>26.99</v>
+        <v>1039</v>
+      </c>
+      <c r="F50" s="13" t="s">
+        <v>1040</v>
+      </c>
+      <c r="G50" s="14"/>
+      <c r="H50" s="13">
+        <v>24.13</v>
+      </c>
+      <c r="I50" s="14">
+        <v>29.39</v>
+      </c>
+      <c r="J50" s="14">
+        <v>22.11</v>
+      </c>
+      <c r="K50" s="9" t="s">
+        <v>1041</v>
+      </c>
+      <c r="L50" s="15">
+        <v>30</v>
+      </c>
+      <c r="M50" s="15">
+        <v>30</v>
+      </c>
+      <c r="N50" s="15">
+        <f>(L50+M50)/2</f>
+        <v>30</v>
+      </c>
+      <c r="O50" s="15">
+        <f>M50-N50</f>
+        <v>0</v>
       </c>
       <c r="P50" s="9" t="s">
-        <v>1110</v>
+        <v>1041</v>
+      </c>
+      <c r="Q50" s="15">
+        <v>30</v>
+      </c>
+      <c r="R50" s="15">
+        <v>30</v>
+      </c>
+      <c r="S50" s="15">
+        <f>R50-Q50</f>
+        <v>0</v>
       </c>
       <c r="T50" s="15">
-        <f>(Q50+R50)/2</f>
-        <v>0</v>
+        <f t="shared" si="4"/>
+        <v>30</v>
+      </c>
+      <c r="U50" s="15" t="s">
+        <v>138</v>
+      </c>
+      <c r="Y50" s="9" t="s">
+        <v>1042</v>
+      </c>
+      <c r="Z50" s="16">
+        <v>170</v>
+      </c>
+      <c r="AA50" s="16">
+        <v>185</v>
+      </c>
+      <c r="AB50" s="9" t="s">
+        <v>112</v>
       </c>
       <c r="AC50" s="9" t="s">
         <v>898</v>
@@ -14643,16 +14559,16 @@
         <v>143</v>
       </c>
       <c r="AE50" s="10">
-        <v>2021</v>
+        <v>2019</v>
       </c>
       <c r="AF50" s="9" t="s">
-        <v>1111</v>
+        <v>144</v>
       </c>
       <c r="AG50" s="9" t="s">
         <v>80</v>
       </c>
       <c r="AH50" s="9" t="s">
-        <v>1112</v>
+        <v>1043</v>
       </c>
       <c r="AI50" s="9" t="s">
         <v>146</v>
@@ -14661,52 +14577,79 @@
         <v>83</v>
       </c>
       <c r="AK50" s="9" t="s">
-        <v>259</v>
+        <v>117</v>
       </c>
       <c r="AL50" s="9" t="s">
-        <v>1113</v>
+        <v>1044</v>
+      </c>
+      <c r="AM50" s="9" t="s">
+        <v>1044</v>
+      </c>
+      <c r="AN50" s="9" t="s">
+        <v>1045</v>
       </c>
       <c r="AO50" s="9" t="s">
-        <v>1114</v>
+        <v>675</v>
+      </c>
+      <c r="AP50" s="9" t="s">
+        <v>675</v>
       </c>
       <c r="AQ50" s="9" t="s">
-        <v>1115</v>
+        <v>1046</v>
       </c>
       <c r="AR50" s="9" t="s">
-        <v>1115</v>
+        <v>1045</v>
+      </c>
+      <c r="AS50" s="9" t="s">
+        <v>1047</v>
       </c>
       <c r="AT50" s="18">
-        <v>0.32700000000000001</v>
+        <v>0.315</v>
       </c>
       <c r="AU50" s="18">
-        <v>0.32700000000000001</v>
+        <v>0.315</v>
       </c>
       <c r="AV50" s="9" t="s">
-        <v>1116</v>
+        <v>1048</v>
       </c>
       <c r="AW50" s="9">
-        <v>22</v>
+        <v>103</v>
+      </c>
+      <c r="AX50" s="9">
+        <v>6</v>
       </c>
       <c r="AY50" s="18">
-        <v>0.5897</v>
+        <v>0.45700000000000002</v>
       </c>
       <c r="AZ50" s="18">
-        <v>0.5897</v>
+        <v>0.45700000000000002</v>
       </c>
       <c r="BA50" s="9" t="s">
-        <v>1117</v>
+        <v>1049</v>
       </c>
       <c r="BB50" s="9">
-        <v>8</v>
+        <v>13</v>
+      </c>
+      <c r="BC50" s="18" t="s">
+        <v>1050</v>
       </c>
       <c r="BD50" s="9" t="s">
-        <v>1118</v>
+        <v>459</v>
+      </c>
+      <c r="BE50" s="11" t="s">
+        <v>1051</v>
+      </c>
+      <c r="BF50" s="19">
+        <v>0.75</v>
+      </c>
+      <c r="BG50" s="9" t="s">
+        <v>98</v>
       </c>
       <c r="BH50" s="9" t="s">
-        <v>1119</v>
-      </c>
-      <c r="BI50" s="19">
-        <v>394.41</v>
+        <v>1052</v>
+      </c>
+      <c r="BI50" s="9">
+        <v>638.13</v>
       </c>
       <c r="BJ50" s="9" t="s">
         <v>100</v>
@@ -14714,87 +14657,102 @@
       <c r="BK50" s="9" t="s">
         <v>867</v>
       </c>
-      <c r="BM50" s="9" t="s">
-        <v>1120</v>
+      <c r="BN50" s="27" t="s">
+        <v>1053</v>
+      </c>
+      <c r="BO50" s="9" t="s">
+        <v>1021</v>
+      </c>
+      <c r="BP50" s="9" t="s">
+        <v>1054</v>
       </c>
       <c r="BQ50" s="9" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="51" spans="1:69">
       <c r="A51" s="10">
-        <v>511</v>
+        <v>505</v>
       </c>
       <c r="B51" s="11" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="C51" s="9" t="s">
-        <v>1075</v>
+        <v>1055</v>
       </c>
       <c r="D51" s="12" t="str">
-        <f>CONCATENATE(A51," ",C51)</f>
-        <v>511 遠雄文青</v>
+        <f t="shared" si="0"/>
+        <v>505 櫻花澍</v>
       </c>
       <c r="E51" s="12" t="s">
-        <v>1076</v>
+        <v>1056</v>
       </c>
       <c r="F51" s="20" t="s">
-        <v>1077</v>
+        <v>1057</v>
       </c>
       <c r="G51" s="21">
-        <v>22.77</v>
+        <v>26.2</v>
       </c>
       <c r="H51" s="22">
-        <v>22.81</v>
+        <v>26.09</v>
       </c>
       <c r="I51" s="21">
-        <v>30.56</v>
+        <v>28.35</v>
       </c>
       <c r="J51" s="21">
-        <v>11.84</v>
+        <v>24.04</v>
       </c>
       <c r="K51" s="9" t="s">
-        <v>1078</v>
+        <v>1058</v>
       </c>
       <c r="L51" s="15">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="M51" s="15">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="N51" s="15">
         <f>(L51+M51)/2</f>
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="O51" s="15">
         <f>M51-N51</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P51" s="9" t="s">
-        <v>1078</v>
+        <v>1058</v>
       </c>
       <c r="Q51" s="15">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="R51" s="15">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="S51" s="15">
         <f>R51-Q51</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T51" s="15">
-        <f>(Q51+R51)/2</f>
-        <v>15</v>
+        <f t="shared" si="4"/>
+        <v>30</v>
       </c>
       <c r="U51" s="15" t="s">
         <v>138</v>
       </c>
       <c r="V51" s="9" t="s">
-        <v>1079</v>
+        <v>1059</v>
       </c>
       <c r="W51" s="20" t="s">
-        <v>1080</v>
+        <v>1060</v>
+      </c>
+      <c r="Y51" s="9" t="s">
+        <v>1061</v>
+      </c>
+      <c r="Z51" s="16">
+        <v>165</v>
+      </c>
+      <c r="AA51" s="16">
+        <v>195</v>
       </c>
       <c r="AB51" s="9" t="s">
         <v>112</v>
@@ -14803,19 +14761,22 @@
         <v>898</v>
       </c>
       <c r="AD51" s="9" t="s">
-        <v>143</v>
+        <v>752</v>
       </c>
       <c r="AE51" s="10">
-        <v>2016</v>
+        <v>2022</v>
       </c>
       <c r="AF51" s="9" t="s">
-        <v>1081</v>
+        <v>79</v>
       </c>
       <c r="AG51" s="9" t="s">
         <v>80</v>
       </c>
+      <c r="AH51" s="9" t="s">
+        <v>1062</v>
+      </c>
       <c r="AI51" s="9" t="s">
-        <v>146</v>
+        <v>258</v>
       </c>
       <c r="AJ51" s="9" t="s">
         <v>83</v>
@@ -14824,110 +14785,137 @@
         <v>117</v>
       </c>
       <c r="AL51" s="9" t="s">
-        <v>1082</v>
+        <v>1063</v>
       </c>
       <c r="AM51" s="9" t="s">
-        <v>1082</v>
+        <v>1064</v>
+      </c>
+      <c r="AN51" s="9" t="s">
+        <v>1065</v>
       </c>
       <c r="AO51" s="9" t="s">
-        <v>830</v>
+        <v>1066</v>
       </c>
       <c r="AP51" s="9" t="s">
-        <v>830</v>
+        <v>1066</v>
+      </c>
+      <c r="AQ51" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="AR51" s="9" t="s">
+        <v>1067</v>
+      </c>
+      <c r="AS51" s="9" t="s">
+        <v>1068</v>
+      </c>
+      <c r="AT51" s="17">
+        <v>0.32</v>
+      </c>
+      <c r="AU51" s="18">
+        <v>0.32</v>
+      </c>
+      <c r="AV51" s="9" t="s">
+        <v>1069</v>
       </c>
       <c r="AW51" s="9">
-        <v>1272</v>
+        <v>106</v>
+      </c>
+      <c r="AX51" s="9">
+        <v>2</v>
+      </c>
+      <c r="AY51" s="18">
+        <v>0.38140000000000002</v>
+      </c>
+      <c r="AZ51" s="18">
+        <v>0.38140000000000002</v>
+      </c>
+      <c r="BA51" s="9" t="s">
+        <v>907</v>
+      </c>
+      <c r="BB51" s="9">
+        <v>14</v>
+      </c>
+      <c r="BC51" s="9" t="s">
+        <v>1070</v>
+      </c>
+      <c r="BD51" s="9" t="s">
+        <v>1071</v>
+      </c>
+      <c r="BE51" s="11" t="s">
+        <v>155</v>
+      </c>
+      <c r="BF51" s="19">
+        <v>1</v>
       </c>
       <c r="BG51" s="9" t="s">
         <v>98</v>
       </c>
+      <c r="BH51" s="9" t="s">
+        <v>1072</v>
+      </c>
+      <c r="BI51" s="9">
+        <v>602.07000000000005</v>
+      </c>
       <c r="BJ51" s="9" t="s">
         <v>100</v>
       </c>
       <c r="BK51" s="9" t="s">
         <v>867</v>
       </c>
+      <c r="BM51" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="BN51" s="9" t="s">
+        <v>1073</v>
+      </c>
+      <c r="BO51" s="9" t="s">
+        <v>764</v>
+      </c>
+      <c r="BP51" s="9" t="s">
+        <v>102</v>
+      </c>
       <c r="BQ51" s="9" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="52" spans="1:69">
       <c r="A52" s="10">
-        <v>512</v>
+        <v>506</v>
       </c>
       <c r="B52" s="11" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="C52" s="9" t="s">
-        <v>1083</v>
+        <v>1106</v>
       </c>
       <c r="D52" s="12" t="str">
-        <f>CONCATENATE(A52," ",C52)</f>
-        <v>512 皇翔歡喜城</v>
+        <f t="shared" si="0"/>
+        <v>506 和煦隆陞</v>
       </c>
       <c r="E52" s="12" t="s">
-        <v>1084</v>
+        <v>1107</v>
       </c>
       <c r="F52" s="20" t="s">
-        <v>1085</v>
-      </c>
-      <c r="G52" s="21">
-        <v>22.67</v>
+        <v>1108</v>
+      </c>
+      <c r="G52" s="19">
+        <v>32.270000000000003</v>
       </c>
       <c r="H52" s="22">
-        <v>22.7</v>
-      </c>
-      <c r="I52" s="21">
-        <v>28.54</v>
-      </c>
-      <c r="J52" s="21">
-        <v>12.94</v>
-      </c>
-      <c r="K52" s="9" t="s">
-        <v>1086</v>
-      </c>
-      <c r="L52" s="15">
-        <v>15</v>
-      </c>
-      <c r="M52" s="15">
-        <v>15</v>
-      </c>
-      <c r="N52" s="15">
-        <f>(L52+M52)/2</f>
-        <v>15</v>
-      </c>
-      <c r="O52" s="15">
-        <f>M52-N52</f>
+        <v>28.56</v>
+      </c>
+      <c r="I52" s="19">
+        <v>33.619999999999997</v>
+      </c>
+      <c r="J52" s="19">
+        <v>26.99</v>
+      </c>
+      <c r="P52" s="9" t="s">
+        <v>1109</v>
+      </c>
+      <c r="T52" s="15">
+        <f t="shared" si="4"/>
         <v>0</v>
-      </c>
-      <c r="P52" s="9" t="s">
-        <v>1086</v>
-      </c>
-      <c r="Q52" s="15">
-        <v>15</v>
-      </c>
-      <c r="R52" s="15">
-        <v>15</v>
-      </c>
-      <c r="S52" s="15">
-        <f>R52-Q52</f>
-        <v>0</v>
-      </c>
-      <c r="T52" s="15">
-        <f>(Q52+R52)/2</f>
-        <v>15</v>
-      </c>
-      <c r="U52" s="15" t="s">
-        <v>138</v>
-      </c>
-      <c r="V52" s="9" t="s">
-        <v>1087</v>
-      </c>
-      <c r="W52" s="20" t="s">
-        <v>1088</v>
-      </c>
-      <c r="AB52" s="9" t="s">
-        <v>112</v>
       </c>
       <c r="AC52" s="9" t="s">
         <v>898</v>
@@ -14936,14 +14924,17 @@
         <v>143</v>
       </c>
       <c r="AE52" s="10">
-        <v>2016</v>
+        <v>2021</v>
       </c>
       <c r="AF52" s="9" t="s">
-        <v>1081</v>
+        <v>1110</v>
       </c>
       <c r="AG52" s="9" t="s">
         <v>80</v>
       </c>
+      <c r="AH52" s="9" t="s">
+        <v>1111</v>
+      </c>
       <c r="AI52" s="9" t="s">
         <v>146</v>
       </c>
@@ -14951,22 +14942,52 @@
         <v>83</v>
       </c>
       <c r="AK52" s="9" t="s">
-        <v>117</v>
+        <v>259</v>
       </c>
       <c r="AL52" s="9" t="s">
-        <v>1089</v>
+        <v>1112</v>
       </c>
       <c r="AO52" s="9" t="s">
-        <v>1090</v>
-      </c>
-      <c r="AP52" s="9" t="s">
-        <v>1090</v>
+        <v>1113</v>
+      </c>
+      <c r="AQ52" s="9" t="s">
+        <v>1114</v>
+      </c>
+      <c r="AR52" s="9" t="s">
+        <v>1114</v>
+      </c>
+      <c r="AT52" s="18">
+        <v>0.32700000000000001</v>
+      </c>
+      <c r="AU52" s="18">
+        <v>0.32700000000000001</v>
+      </c>
+      <c r="AV52" s="9" t="s">
+        <v>1115</v>
       </c>
       <c r="AW52" s="9">
-        <v>1780</v>
-      </c>
-      <c r="BG52" s="9" t="s">
-        <v>98</v>
+        <v>22</v>
+      </c>
+      <c r="AY52" s="18">
+        <v>0.5897</v>
+      </c>
+      <c r="AZ52" s="18">
+        <v>0.5897</v>
+      </c>
+      <c r="BA52" s="9" t="s">
+        <v>1116</v>
+      </c>
+      <c r="BB52" s="9">
+        <v>8</v>
+      </c>
+      <c r="BD52" s="9" t="s">
+        <v>1117</v>
+      </c>
+      <c r="BH52" s="9" t="s">
+        <v>1118</v>
+      </c>
+      <c r="BI52" s="19">
+        <v>394.41</v>
       </c>
       <c r="BJ52" s="9" t="s">
         <v>100</v>
@@ -14974,44 +14995,47 @@
       <c r="BK52" s="9" t="s">
         <v>867</v>
       </c>
+      <c r="BM52" s="9" t="s">
+        <v>1119</v>
+      </c>
       <c r="BQ52" s="9" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="53" spans="1:69">
       <c r="A53" s="10">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="B53" s="11" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="C53" s="9" t="s">
-        <v>1091</v>
+        <v>1074</v>
       </c>
       <c r="D53" s="12" t="str">
-        <f>CONCATENATE(A53," ",C53)</f>
-        <v>513 名軒快樂家</v>
+        <f t="shared" si="0"/>
+        <v>511 遠雄文青</v>
       </c>
       <c r="E53" s="12" t="s">
-        <v>1092</v>
+        <v>1075</v>
       </c>
       <c r="F53" s="20" t="s">
-        <v>1093</v>
+        <v>1076</v>
       </c>
       <c r="G53" s="21">
-        <v>22.41</v>
+        <v>22.77</v>
       </c>
       <c r="H53" s="22">
-        <v>22.48</v>
+        <v>22.81</v>
       </c>
       <c r="I53" s="21">
-        <v>27.8</v>
+        <v>30.56</v>
       </c>
       <c r="J53" s="21">
-        <v>13.62</v>
+        <v>11.84</v>
       </c>
       <c r="K53" s="9" t="s">
-        <v>1094</v>
+        <v>1077</v>
       </c>
       <c r="L53" s="15">
         <v>15</v>
@@ -15028,7 +15052,7 @@
         <v>0</v>
       </c>
       <c r="P53" s="9" t="s">
-        <v>1094</v>
+        <v>1077</v>
       </c>
       <c r="Q53" s="15">
         <v>15</v>
@@ -15041,17 +15065,17 @@
         <v>0</v>
       </c>
       <c r="T53" s="15">
-        <f>(Q53+R53)/2</f>
+        <f t="shared" si="4"/>
         <v>15</v>
       </c>
       <c r="U53" s="15" t="s">
         <v>138</v>
       </c>
       <c r="V53" s="9" t="s">
-        <v>1095</v>
+        <v>1078</v>
       </c>
       <c r="W53" s="20" t="s">
-        <v>1096</v>
+        <v>1079</v>
       </c>
       <c r="AB53" s="9" t="s">
         <v>112</v>
@@ -15066,7 +15090,7 @@
         <v>2016</v>
       </c>
       <c r="AF53" s="9" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="AG53" s="9" t="s">
         <v>80</v>
@@ -15081,16 +15105,19 @@
         <v>117</v>
       </c>
       <c r="AL53" s="9" t="s">
-        <v>1097</v>
+        <v>1081</v>
+      </c>
+      <c r="AM53" s="9" t="s">
+        <v>1081</v>
       </c>
       <c r="AO53" s="9" t="s">
-        <v>1098</v>
+        <v>830</v>
       </c>
       <c r="AP53" s="9" t="s">
-        <v>1098</v>
+        <v>830</v>
       </c>
       <c r="AW53" s="9">
-        <v>514</v>
+        <v>1272</v>
       </c>
       <c r="BG53" s="9" t="s">
         <v>98</v>
@@ -15102,43 +15129,43 @@
         <v>867</v>
       </c>
       <c r="BQ53" s="9" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="54" spans="1:69">
       <c r="A54" s="10">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="B54" s="11" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="C54" s="9" t="s">
-        <v>1099</v>
+        <v>1082</v>
       </c>
       <c r="D54" s="12" t="str">
-        <f>CONCATENATE(A54," ",C54)</f>
-        <v>514 麗寶快樂家</v>
+        <f t="shared" si="0"/>
+        <v>512 皇翔歡喜城</v>
       </c>
       <c r="E54" s="12" t="s">
-        <v>1100</v>
+        <v>1083</v>
       </c>
       <c r="F54" s="20" t="s">
-        <v>1101</v>
+        <v>1084</v>
       </c>
       <c r="G54" s="21">
-        <v>22.58</v>
+        <v>22.67</v>
       </c>
       <c r="H54" s="22">
-        <v>22.58</v>
+        <v>22.7</v>
       </c>
       <c r="I54" s="21">
-        <v>28.38</v>
+        <v>28.54</v>
       </c>
       <c r="J54" s="21">
-        <v>14.83</v>
+        <v>12.94</v>
       </c>
       <c r="K54" s="9" t="s">
-        <v>1102</v>
+        <v>1085</v>
       </c>
       <c r="L54" s="15">
         <v>15</v>
@@ -15155,7 +15182,7 @@
         <v>0</v>
       </c>
       <c r="P54" s="9" t="s">
-        <v>1102</v>
+        <v>1085</v>
       </c>
       <c r="Q54" s="15">
         <v>15</v>
@@ -15168,17 +15195,17 @@
         <v>0</v>
       </c>
       <c r="T54" s="15">
-        <f>(Q54+R54)/2</f>
+        <f t="shared" si="4"/>
         <v>15</v>
       </c>
       <c r="U54" s="15" t="s">
         <v>138</v>
       </c>
       <c r="V54" s="9" t="s">
-        <v>1103</v>
+        <v>1086</v>
       </c>
       <c r="W54" s="20" t="s">
-        <v>1104</v>
+        <v>1087</v>
       </c>
       <c r="AB54" s="9" t="s">
         <v>112</v>
@@ -15193,7 +15220,7 @@
         <v>2016</v>
       </c>
       <c r="AF54" s="9" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="AG54" s="9" t="s">
         <v>80</v>
@@ -15208,16 +15235,16 @@
         <v>117</v>
       </c>
       <c r="AL54" s="9" t="s">
-        <v>1105</v>
+        <v>1088</v>
       </c>
       <c r="AO54" s="9" t="s">
-        <v>1106</v>
+        <v>1089</v>
       </c>
       <c r="AP54" s="9" t="s">
-        <v>1106</v>
+        <v>1089</v>
       </c>
       <c r="AW54" s="9">
-        <v>897</v>
+        <v>1780</v>
       </c>
       <c r="BG54" s="9" t="s">
         <v>98</v>
@@ -15229,79 +15256,334 @@
         <v>867</v>
       </c>
       <c r="BQ54" s="9" t="s">
-        <v>1001</v>
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="55" spans="1:69">
+      <c r="A55" s="10">
+        <v>513</v>
+      </c>
+      <c r="B55" s="11" t="s">
+        <v>985</v>
+      </c>
+      <c r="C55" s="9" t="s">
+        <v>1090</v>
+      </c>
+      <c r="D55" s="12" t="str">
+        <f t="shared" si="0"/>
+        <v>513 名軒快樂家</v>
+      </c>
+      <c r="E55" s="12" t="s">
+        <v>1091</v>
+      </c>
+      <c r="F55" s="20" t="s">
+        <v>1092</v>
+      </c>
+      <c r="G55" s="21">
+        <v>22.41</v>
+      </c>
+      <c r="H55" s="22">
+        <v>22.48</v>
+      </c>
+      <c r="I55" s="21">
+        <v>27.8</v>
+      </c>
+      <c r="J55" s="21">
+        <v>13.62</v>
+      </c>
+      <c r="K55" s="9" t="s">
+        <v>1093</v>
+      </c>
+      <c r="L55" s="15">
+        <v>15</v>
+      </c>
+      <c r="M55" s="15">
+        <v>15</v>
+      </c>
+      <c r="N55" s="15">
+        <f>(L55+M55)/2</f>
+        <v>15</v>
+      </c>
+      <c r="O55" s="15">
+        <f>M55-N55</f>
+        <v>0</v>
+      </c>
+      <c r="P55" s="9" t="s">
+        <v>1093</v>
+      </c>
+      <c r="Q55" s="15">
+        <v>15</v>
+      </c>
+      <c r="R55" s="15">
+        <v>15</v>
+      </c>
+      <c r="S55" s="15">
+        <f>R55-Q55</f>
+        <v>0</v>
+      </c>
+      <c r="T55" s="15">
+        <f t="shared" si="4"/>
+        <v>15</v>
+      </c>
+      <c r="U55" s="15" t="s">
+        <v>138</v>
+      </c>
+      <c r="V55" s="9" t="s">
+        <v>1094</v>
+      </c>
+      <c r="W55" s="20" t="s">
+        <v>1095</v>
+      </c>
+      <c r="AB55" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="AC55" s="9" t="s">
+        <v>898</v>
+      </c>
+      <c r="AD55" s="9" t="s">
+        <v>143</v>
+      </c>
+      <c r="AE55" s="10">
+        <v>2016</v>
+      </c>
+      <c r="AF55" s="9" t="s">
+        <v>1080</v>
+      </c>
+      <c r="AG55" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="AI55" s="9" t="s">
+        <v>146</v>
+      </c>
+      <c r="AJ55" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="AK55" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="AL55" s="9" t="s">
+        <v>1096</v>
+      </c>
+      <c r="AO55" s="9" t="s">
+        <v>1097</v>
+      </c>
+      <c r="AP55" s="9" t="s">
+        <v>1097</v>
+      </c>
+      <c r="AW55" s="9">
+        <v>514</v>
+      </c>
+      <c r="BG55" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="BJ55" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="BK55" s="9" t="s">
+        <v>867</v>
+      </c>
+      <c r="BQ55" s="9" t="s">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="56" spans="1:69">
+      <c r="A56" s="10">
+        <v>514</v>
+      </c>
+      <c r="B56" s="11" t="s">
+        <v>985</v>
+      </c>
+      <c r="C56" s="9" t="s">
+        <v>1098</v>
+      </c>
+      <c r="D56" s="12" t="str">
+        <f t="shared" si="0"/>
+        <v>514 麗寶快樂家</v>
+      </c>
+      <c r="E56" s="12" t="s">
+        <v>1099</v>
+      </c>
+      <c r="F56" s="20" t="s">
+        <v>1100</v>
+      </c>
+      <c r="G56" s="21">
+        <v>22.58</v>
+      </c>
+      <c r="H56" s="22">
+        <v>22.58</v>
+      </c>
+      <c r="I56" s="21">
+        <v>28.38</v>
+      </c>
+      <c r="J56" s="21">
+        <v>14.83</v>
+      </c>
+      <c r="K56" s="9" t="s">
+        <v>1101</v>
+      </c>
+      <c r="L56" s="15">
+        <v>15</v>
+      </c>
+      <c r="M56" s="15">
+        <v>15</v>
+      </c>
+      <c r="N56" s="15">
+        <f>(L56+M56)/2</f>
+        <v>15</v>
+      </c>
+      <c r="O56" s="15">
+        <f>M56-N56</f>
+        <v>0</v>
+      </c>
+      <c r="P56" s="9" t="s">
+        <v>1101</v>
+      </c>
+      <c r="Q56" s="15">
+        <v>15</v>
+      </c>
+      <c r="R56" s="15">
+        <v>15</v>
+      </c>
+      <c r="S56" s="15">
+        <f>R56-Q56</f>
+        <v>0</v>
+      </c>
+      <c r="T56" s="15">
+        <f t="shared" si="4"/>
+        <v>15</v>
+      </c>
+      <c r="U56" s="15" t="s">
+        <v>138</v>
+      </c>
+      <c r="V56" s="9" t="s">
+        <v>1102</v>
+      </c>
+      <c r="W56" s="20" t="s">
+        <v>1103</v>
+      </c>
+      <c r="AB56" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="AC56" s="9" t="s">
+        <v>898</v>
+      </c>
+      <c r="AD56" s="9" t="s">
+        <v>143</v>
+      </c>
+      <c r="AE56" s="10">
+        <v>2016</v>
+      </c>
+      <c r="AF56" s="9" t="s">
+        <v>1080</v>
+      </c>
+      <c r="AG56" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="AI56" s="9" t="s">
+        <v>146</v>
+      </c>
+      <c r="AJ56" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="AK56" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="AL56" s="9" t="s">
+        <v>1104</v>
+      </c>
+      <c r="AO56" s="9" t="s">
+        <v>1105</v>
+      </c>
+      <c r="AP56" s="9" t="s">
+        <v>1105</v>
+      </c>
+      <c r="AW56" s="9">
+        <v>897</v>
+      </c>
+      <c r="BG56" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="BJ56" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="BK56" s="9" t="s">
+        <v>867</v>
+      </c>
+      <c r="BQ56" s="9" t="s">
+        <v>1000</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="F28" r:id="rId1" xr:uid="{7E97BBF5-58CC-1E49-850E-ABDBC3FF7D3B}"/>
-    <hyperlink ref="F14" r:id="rId2" xr:uid="{AC104403-A3BA-8A4B-8D6B-3A9B9019ACD9}"/>
-    <hyperlink ref="F29" r:id="rId3" xr:uid="{930F6CE4-C809-784B-892A-59D067CB4DCD}"/>
-    <hyperlink ref="F8" r:id="rId4" xr:uid="{324E08C4-B858-7440-87BC-603810EC826B}"/>
-    <hyperlink ref="F34" r:id="rId5" xr:uid="{C503C63A-E4A7-E041-B531-9CD7DF7E5735}"/>
-    <hyperlink ref="F21" r:id="rId6" xr:uid="{D0F9F22C-F5C5-7643-A329-AF2DB4A2E67E}"/>
-    <hyperlink ref="F5" r:id="rId7" xr:uid="{CC8C6F7E-38FB-6A4F-9445-3B0BFDCE7143}"/>
-    <hyperlink ref="F23" r:id="rId8" xr:uid="{6147E58E-73AC-3141-BF6F-820F72C4B7C8}"/>
-    <hyperlink ref="F12" r:id="rId9" xr:uid="{479111DF-7019-C741-90FF-3CDA989390FA}"/>
-    <hyperlink ref="F38" r:id="rId10" xr:uid="{FF069BF9-E329-B045-A7B0-A7FB389D585A}"/>
-    <hyperlink ref="F7" r:id="rId11" xr:uid="{522F1A4D-27FF-A74D-8BD3-B03DCE8A6F16}"/>
-    <hyperlink ref="F30" r:id="rId12" xr:uid="{36BEB424-FB22-E440-BA95-538886A85695}"/>
-    <hyperlink ref="F31" r:id="rId13" xr:uid="{26BC46B0-F0BD-F843-9508-757D5F58388D}"/>
-    <hyperlink ref="F3" r:id="rId14" xr:uid="{628A2FDD-F350-9C45-A43A-A52F38FBE2FE}"/>
-    <hyperlink ref="F15" r:id="rId15" xr:uid="{D308E28B-67D0-854A-BB7F-0B0C31E4AF1C}"/>
-    <hyperlink ref="F4" r:id="rId16" xr:uid="{64DF6D49-C84B-1546-A96E-1FDFEB90B4F5}"/>
-    <hyperlink ref="F11" r:id="rId17" xr:uid="{5A19BA4B-3248-B141-9537-55BE94CC42CC}"/>
-    <hyperlink ref="F19" r:id="rId18" xr:uid="{7C1A5F09-03BF-5F4E-B199-03E88F3F0721}"/>
-    <hyperlink ref="F33" r:id="rId19" xr:uid="{663FC33D-33F4-814C-9EE8-494E143897F3}"/>
-    <hyperlink ref="F47" r:id="rId20" xr:uid="{D610CC74-8387-BA4A-AB54-300E7968E85B}"/>
-    <hyperlink ref="F18" r:id="rId21" xr:uid="{17CFE591-299F-DA47-8D1F-97437B9EF873}"/>
-    <hyperlink ref="F10" r:id="rId22" xr:uid="{F240F5DB-5C4B-4E45-BCA6-11129C71D221}"/>
-    <hyperlink ref="F39" r:id="rId23" xr:uid="{B96FA78B-C02C-6549-8FD2-330D318BD44B}"/>
-    <hyperlink ref="F2" r:id="rId24" xr:uid="{6B51A339-BE5F-584E-BB0B-BC16F689854E}"/>
-    <hyperlink ref="F6" r:id="rId25" xr:uid="{1197BAD5-CDF3-5940-B616-AA86EBCA8A95}"/>
-    <hyperlink ref="F17" r:id="rId26" xr:uid="{107C96AB-CFA3-9947-9D3E-78FE6829FF2E}"/>
-    <hyperlink ref="F25" r:id="rId27" xr:uid="{23BE4DD6-0826-B640-963D-632F1F3C3EB7}"/>
-    <hyperlink ref="F37" r:id="rId28" xr:uid="{04B7468A-95DE-6243-BB31-4AD5F69154D7}"/>
-    <hyperlink ref="F36" r:id="rId29" xr:uid="{99B7FDDD-3613-EE44-964C-053F4871D33F}"/>
-    <hyperlink ref="F32" r:id="rId30" xr:uid="{C0337781-B016-024E-A6C2-376C219AF39E}"/>
-    <hyperlink ref="F35" r:id="rId31" xr:uid="{725D2B97-D927-9D4A-BF75-D9501D47A4F0}"/>
-    <hyperlink ref="F45" r:id="rId32" xr:uid="{43BCD948-8B63-B146-BD0A-23A2192C8106}"/>
-    <hyperlink ref="F46" r:id="rId33" xr:uid="{C969BD44-9A46-1E4E-9E3A-0DDF21F38126}"/>
-    <hyperlink ref="F22" r:id="rId34" xr:uid="{6A5D8839-79EC-E34D-87B4-256951BFFF9D}"/>
-    <hyperlink ref="F20" r:id="rId35" xr:uid="{3C5D575B-A475-1A44-B46B-95929DA4B9E6}"/>
-    <hyperlink ref="F27" r:id="rId36" xr:uid="{957261BE-7F04-3E4F-B0D8-952056D958DD}"/>
-    <hyperlink ref="F26" r:id="rId37" xr:uid="{5148A679-6532-AC4B-B5B7-7F4B46C047FF}"/>
-    <hyperlink ref="F16" r:id="rId38" xr:uid="{E12AD518-E9AB-2D4B-9DF5-242D271226AC}"/>
-    <hyperlink ref="F40" r:id="rId39" xr:uid="{2B0A72CF-5317-0A47-87E4-05BFF1DE2920}"/>
-    <hyperlink ref="F49" r:id="rId40" xr:uid="{F75F2C24-0C94-954A-A548-5CB5262C5FC6}"/>
-    <hyperlink ref="F48" r:id="rId41" xr:uid="{D9D3650D-9D3C-F24A-84EB-4ABF9ABF9C77}"/>
-    <hyperlink ref="F51" r:id="rId42" xr:uid="{D3F2EAF3-A0A8-484D-B56B-2E0CED4FE669}"/>
-    <hyperlink ref="F52" r:id="rId43" xr:uid="{C488CA03-7142-8645-A8BA-A1C0842FB7E3}"/>
-    <hyperlink ref="F53" r:id="rId44" xr:uid="{739B4590-DA09-1A40-9E11-0D89166670A2}"/>
-    <hyperlink ref="F54" r:id="rId45" xr:uid="{15FC3207-B5D1-4749-A189-8319E51FF7DF}"/>
-    <hyperlink ref="F41" r:id="rId46" xr:uid="{AED1D5DB-F2D4-3546-887D-04ECB76B4B09}"/>
-    <hyperlink ref="W54" r:id="rId47" xr:uid="{FAC110FD-D411-2842-A034-82402B099BF6}"/>
-    <hyperlink ref="W53" r:id="rId48" xr:uid="{1CBA8D4D-ECAA-0D42-A34C-5EC32F9268D5}"/>
-    <hyperlink ref="W52" r:id="rId49" xr:uid="{9C579664-03FA-ED46-AB23-6EEAB82E96D4}"/>
-    <hyperlink ref="W51" r:id="rId50" xr:uid="{EF522D4E-090E-3641-88C8-E5A2AC3C0506}"/>
-    <hyperlink ref="W49" r:id="rId51" xr:uid="{0CB53662-22AF-E446-BDE6-E8BA5693BDEF}"/>
-    <hyperlink ref="W33" r:id="rId52" xr:uid="{4AEA7673-20E9-DE45-9ACC-5FA56A63F082}"/>
-    <hyperlink ref="W29" r:id="rId53" xr:uid="{AF6FF3C4-212B-D24C-A243-2498ABB9A37A}"/>
-    <hyperlink ref="W28" r:id="rId54" xr:uid="{E4EAE70B-EB76-DE4C-A87A-48E2AFAA5962}"/>
-    <hyperlink ref="W25" r:id="rId55" xr:uid="{5ED27C4A-E55A-7847-89B5-ED38CE6627A5}"/>
-    <hyperlink ref="W21" r:id="rId56" xr:uid="{E808176A-D5B1-9243-896D-FDEF072F249D}"/>
-    <hyperlink ref="W20" r:id="rId57" xr:uid="{690350C4-8B5F-CF46-9593-3B6C0E4DF31D}"/>
-    <hyperlink ref="W14" r:id="rId58" xr:uid="{B1DB42C2-6B88-AA44-9A7C-5D66F9744C26}"/>
-    <hyperlink ref="W13" r:id="rId59" xr:uid="{2BA33602-A18E-D34F-970A-23EE9AB31C13}"/>
-    <hyperlink ref="W8" r:id="rId60" xr:uid="{34FEFC4B-7E69-BB4A-B5D2-80E12FF78C03}"/>
-    <hyperlink ref="W5" r:id="rId61" xr:uid="{E6501597-2102-5C4A-B3EA-A83F435711A7}"/>
-    <hyperlink ref="W4" r:id="rId62" xr:uid="{56E71FDE-71BC-904C-B8C3-59C7F2D51EFE}"/>
-    <hyperlink ref="F42" r:id="rId63" xr:uid="{0BB0A4EA-A7BA-B447-AC5F-763EB62498B2}"/>
-    <hyperlink ref="F43" r:id="rId64" xr:uid="{5C8809E4-2E65-6C4E-8C36-39CF0BCDDDA0}"/>
-    <hyperlink ref="F44" r:id="rId65" xr:uid="{9B12BA0F-FFD2-C747-9E1D-811D28D1FFD7}"/>
-    <hyperlink ref="F9" r:id="rId66" xr:uid="{A8D39917-EFA3-F643-857D-7165822301CC}"/>
-    <hyperlink ref="F50" r:id="rId67" xr:uid="{C2B0C36E-88FA-5C40-AF01-90F36D8339E2}"/>
+    <hyperlink ref="F29" r:id="rId1" xr:uid="{157ABE99-A2FB-0440-AA30-D18A462E1CFE}"/>
+    <hyperlink ref="F14" r:id="rId2" xr:uid="{C1C6F2DA-8C39-4A41-AC5A-8D4042CD82E2}"/>
+    <hyperlink ref="F30" r:id="rId3" xr:uid="{14CD224C-D507-8544-B5B0-F9485E7EADD4}"/>
+    <hyperlink ref="F8" r:id="rId4" xr:uid="{D6BB588A-0598-5344-A73F-E3B347DF3F28}"/>
+    <hyperlink ref="F35" r:id="rId5" xr:uid="{60EC4BA6-2F6F-F04D-B290-240CF8C62322}"/>
+    <hyperlink ref="F21" r:id="rId6" xr:uid="{F16D9EB3-F4EC-D945-93DF-08D2A7A3864A}"/>
+    <hyperlink ref="F5" r:id="rId7" xr:uid="{F60D9E1E-0792-D246-986A-829271525FCE}"/>
+    <hyperlink ref="F23" r:id="rId8" xr:uid="{ED14C2AB-7C33-B243-B44C-CAF64408C1CF}"/>
+    <hyperlink ref="F12" r:id="rId9" xr:uid="{F20CCC9D-6612-0D4E-9102-C4FB702EF9F1}"/>
+    <hyperlink ref="F39" r:id="rId10" xr:uid="{4A82A7A4-7728-6E4C-85C7-04F3D281CDE8}"/>
+    <hyperlink ref="F7" r:id="rId11" xr:uid="{180B2D53-6C80-374E-BD2E-420BCA5A5C3D}"/>
+    <hyperlink ref="F31" r:id="rId12" xr:uid="{AB88406E-98AA-164F-B7D1-3CCE4D76ED40}"/>
+    <hyperlink ref="F32" r:id="rId13" xr:uid="{F6FD03DD-70CE-9442-8230-9D1E07A842D9}"/>
+    <hyperlink ref="F3" r:id="rId14" xr:uid="{565FB8A8-6ABB-8B4C-A4DB-B0F2B8462905}"/>
+    <hyperlink ref="F15" r:id="rId15" xr:uid="{5AAADDD7-1BCD-8043-9858-B05D252C83A4}"/>
+    <hyperlink ref="F4" r:id="rId16" xr:uid="{CACD3290-657F-3245-ADCF-EA0DCDDF62E7}"/>
+    <hyperlink ref="F11" r:id="rId17" xr:uid="{026BD39A-FBA0-F34B-9942-9BA4A9108E5E}"/>
+    <hyperlink ref="F19" r:id="rId18" xr:uid="{8D74885C-2D85-A14C-AC9C-F2D3A632DEEF}"/>
+    <hyperlink ref="F34" r:id="rId19" xr:uid="{2EF651A1-A5CC-2343-BEF8-9EB02276CE7E}"/>
+    <hyperlink ref="F49" r:id="rId20" xr:uid="{10E58388-50CF-C24C-8558-C42CD55D392E}"/>
+    <hyperlink ref="F18" r:id="rId21" xr:uid="{317A5C37-B0D1-054D-853E-B45BA54E79E8}"/>
+    <hyperlink ref="F10" r:id="rId22" xr:uid="{B8E384B0-1C19-0641-BC64-9B025489BC73}"/>
+    <hyperlink ref="F40" r:id="rId23" xr:uid="{0297B810-E8A7-9F4F-A1DF-2DC2FD9CAD58}"/>
+    <hyperlink ref="F2" r:id="rId24" xr:uid="{DB7AE95F-1A5B-A947-BB9C-5AFE940F01C6}"/>
+    <hyperlink ref="F6" r:id="rId25" xr:uid="{BD32F7E6-14AF-4846-B45A-135801EF66FD}"/>
+    <hyperlink ref="F17" r:id="rId26" xr:uid="{17AF1D91-F737-7049-A0B1-8CBE6EAE2731}"/>
+    <hyperlink ref="F25" r:id="rId27" xr:uid="{AB1DF39A-79DD-1D49-BB3B-8FCF74E3BB1B}"/>
+    <hyperlink ref="F38" r:id="rId28" xr:uid="{7DA58C6F-B4E1-BF4C-B72D-C453F86FF441}"/>
+    <hyperlink ref="F37" r:id="rId29" xr:uid="{0CD54E4F-BE3F-394C-92A9-B6263FF7A035}"/>
+    <hyperlink ref="F33" r:id="rId30" xr:uid="{CEE458E9-8036-0C42-9F63-FD98A878F938}"/>
+    <hyperlink ref="F36" r:id="rId31" xr:uid="{006F8A27-A92E-D64A-A9FE-2AC6CCFEFC8C}"/>
+    <hyperlink ref="F47" r:id="rId32" xr:uid="{E69803C2-7C3A-E842-8EC4-F26ABA2F4F71}"/>
+    <hyperlink ref="F48" r:id="rId33" xr:uid="{AF8C33CF-BBF6-514E-847C-B813484FDC84}"/>
+    <hyperlink ref="F22" r:id="rId34" xr:uid="{2DA563E0-820A-CD40-A478-057112A6CCC6}"/>
+    <hyperlink ref="F20" r:id="rId35" xr:uid="{7FB37CA2-257B-E344-9F80-5F46AC0AD669}"/>
+    <hyperlink ref="F27" r:id="rId36" xr:uid="{90F02F31-6FE9-1F46-B629-90C007EF11EB}"/>
+    <hyperlink ref="F26" r:id="rId37" xr:uid="{38296C72-A454-AD4D-9902-A1D1EAA2E6EF}"/>
+    <hyperlink ref="F16" r:id="rId38" xr:uid="{D9971F84-130E-DA4F-986A-340C7B198692}"/>
+    <hyperlink ref="F41" r:id="rId39" xr:uid="{869CC27C-6AB3-BD4B-8CB7-40A8854616E6}"/>
+    <hyperlink ref="F51" r:id="rId40" xr:uid="{3C036DD2-1C9D-434B-9C1B-3507EF213098}"/>
+    <hyperlink ref="F50" r:id="rId41" xr:uid="{A14981B5-E2A6-1147-807C-837523048C67}"/>
+    <hyperlink ref="F53" r:id="rId42" xr:uid="{823C3139-E806-2648-A705-7820086C13F0}"/>
+    <hyperlink ref="F54" r:id="rId43" xr:uid="{8B45B23E-BED9-0547-98CE-32A6BA4A8D3B}"/>
+    <hyperlink ref="F55" r:id="rId44" xr:uid="{B501110A-1321-BA49-9DAE-642323CF3D5C}"/>
+    <hyperlink ref="F56" r:id="rId45" xr:uid="{4FB6F175-460F-F747-89C9-C0AC4A9AD4D6}"/>
+    <hyperlink ref="F42" r:id="rId46" xr:uid="{0BF335F6-0BCF-0547-AA2E-C7E0E9C4B567}"/>
+    <hyperlink ref="W56" r:id="rId47" xr:uid="{E8ECC72D-523F-3B4F-9B29-0CA13FC000F3}"/>
+    <hyperlink ref="W55" r:id="rId48" xr:uid="{04763D82-B655-2649-818C-9FF4B81505A5}"/>
+    <hyperlink ref="W54" r:id="rId49" xr:uid="{46604610-8566-2347-898E-E47B36CA7BCB}"/>
+    <hyperlink ref="W53" r:id="rId50" xr:uid="{11397E5A-8D0F-F049-A6E2-6C2F5F4C70FF}"/>
+    <hyperlink ref="W51" r:id="rId51" xr:uid="{E8E161C7-0BBA-534C-8A47-A9C6601E4602}"/>
+    <hyperlink ref="W34" r:id="rId52" xr:uid="{9F7D9221-772C-6543-8F5D-64D60B7891D3}"/>
+    <hyperlink ref="W30" r:id="rId53" xr:uid="{5D9A1886-872F-1D4C-96A2-38A3D8E221FA}"/>
+    <hyperlink ref="W29" r:id="rId54" xr:uid="{0CA654E0-ED3D-CA48-841B-3E4BEF14DCA1}"/>
+    <hyperlink ref="W25" r:id="rId55" xr:uid="{BEFF434A-B9DF-5C4D-B92C-D674270C946F}"/>
+    <hyperlink ref="W21" r:id="rId56" xr:uid="{16854C3F-E050-C44B-8ABF-C6FD355075A6}"/>
+    <hyperlink ref="W20" r:id="rId57" xr:uid="{BAF33518-D0C5-BF43-891E-215C887EE530}"/>
+    <hyperlink ref="W14" r:id="rId58" xr:uid="{EBA10D19-AFB6-C644-8D37-D8B122B49974}"/>
+    <hyperlink ref="W13" r:id="rId59" xr:uid="{D1E84B04-BC25-A44D-B8B6-F41EF7D6C8A1}"/>
+    <hyperlink ref="W8" r:id="rId60" xr:uid="{A79EBC76-44DF-5448-89DE-2F1C9AC4A027}"/>
+    <hyperlink ref="W5" r:id="rId61" xr:uid="{4A65B4D8-0647-774B-9E0C-FB30F79CF9C8}"/>
+    <hyperlink ref="W4" r:id="rId62" xr:uid="{51CBE6FB-8641-BC48-A116-ED0B9852AF2C}"/>
+    <hyperlink ref="F43" r:id="rId63" xr:uid="{AD5F4398-C515-4348-A8F1-C94596F8E999}"/>
+    <hyperlink ref="F44" r:id="rId64" xr:uid="{ED4CE85D-0A6F-424B-94F0-E2C03BB9FEF8}"/>
+    <hyperlink ref="F45" r:id="rId65" xr:uid="{D02F3456-2CA3-0747-B090-E8157B776FF6}"/>
+    <hyperlink ref="F9" r:id="rId66" xr:uid="{8783B552-ADF8-084E-A4AD-9E2666874F7A}"/>
+    <hyperlink ref="F52" r:id="rId67" xr:uid="{C5830C64-9ABE-6042-8A7E-E8DF958DD580}"/>
+    <hyperlink ref="F46" r:id="rId68" xr:uid="{B2D11C37-9E29-D148-B15B-CC9046040414}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
